--- a/chung_cu_data.xlsx
+++ b/chung_cu_data.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Toa Do (Map)" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Danh Sach BDS'!$A$1:$K$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Danh Sach BDS'!$A$1:$K$60</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -39,7 +39,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -88,6 +88,18 @@
         <bgColor rgb="00E0F2F1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3E5F5"/>
+        <bgColor rgb="00F3E5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFEBE9"/>
+        <bgColor rgb="00EFEBE9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -115,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -150,6 +162,16 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -516,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K54"/>
+  <dimension ref="A1:K60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3400,8 +3422,338 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="20" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="21" t="inlineStr">
+        <is>
+          <t>The Origami (Vinhomes Grand Park)</t>
+        </is>
+      </c>
+      <c r="C55" s="21" t="inlineStr">
+        <is>
+          <t>Chung cu</t>
+        </is>
+      </c>
+      <c r="D55" s="21" t="inlineStr">
+        <is>
+          <t>3.3-4.9 ty</t>
+        </is>
+      </c>
+      <c r="E55" s="21" t="inlineStr">
+        <is>
+          <t>59-90m2</t>
+        </is>
+      </c>
+      <c r="F55" s="20" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="G55" s="20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H55" s="21" t="inlineStr">
+        <is>
+          <t>Long Binh, TP.Thu Duc (Q.9 cu)</t>
+        </is>
+      </c>
+      <c r="I55" s="21" t="inlineStr">
+        <is>
+          <t>Q.9</t>
+        </is>
+      </c>
+      <c r="J55" s="21" t="inlineStr">
+        <is>
+          <t>Vinhomes, view vuon Nhat, ho ca Koi</t>
+        </is>
+      </c>
+      <c r="K55" s="22" t="inlineStr">
+        <is>
+          <t>Xem BDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="20" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="21" t="inlineStr">
+        <is>
+          <t>Lumiere Boulevard</t>
+        </is>
+      </c>
+      <c r="C56" s="21" t="inlineStr">
+        <is>
+          <t>Chung cu</t>
+        </is>
+      </c>
+      <c r="D56" s="21" t="inlineStr">
+        <is>
+          <t>4.6-4.7 ty</t>
+        </is>
+      </c>
+      <c r="E56" s="21" t="inlineStr">
+        <is>
+          <t>74m2</t>
+        </is>
+      </c>
+      <c r="F56" s="20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G56" s="20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H56" s="21" t="inlineStr">
+        <is>
+          <t>Long Binh, TP.Thu Duc (Q.9 cu)</t>
+        </is>
+      </c>
+      <c r="I56" s="21" t="inlineStr">
+        <is>
+          <t>Q.9</t>
+        </is>
+      </c>
+      <c r="J56" s="21" t="inlineStr">
+        <is>
+          <t>Masterise Homes, trong Vinhomes GP</t>
+        </is>
+      </c>
+      <c r="K56" s="22" t="inlineStr">
+        <is>
+          <t>Xem BDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="23" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="24" t="inlineStr">
+        <is>
+          <t>Mizuki Park</t>
+        </is>
+      </c>
+      <c r="C57" s="24" t="inlineStr">
+        <is>
+          <t>Chung cu</t>
+        </is>
+      </c>
+      <c r="D57" s="24" t="inlineStr">
+        <is>
+          <t>3.6-4.2 ty</t>
+        </is>
+      </c>
+      <c r="E57" s="24" t="inlineStr">
+        <is>
+          <t>58-95m2</t>
+        </is>
+      </c>
+      <c r="F57" s="23" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="G57" s="23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H57" s="24" t="inlineStr">
+        <is>
+          <t>Nguyen Van Linh, X.Binh Hung, Binh Chanh</t>
+        </is>
+      </c>
+      <c r="I57" s="24" t="inlineStr">
+        <is>
+          <t>Binh Chanh</t>
+        </is>
+      </c>
+      <c r="J57" s="24" t="inlineStr">
+        <is>
+          <t>Nam Long, view song, khu do thi</t>
+        </is>
+      </c>
+      <c r="K57" s="25" t="inlineStr">
+        <is>
+          <t>Xem BDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="23" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="24" t="inlineStr">
+        <is>
+          <t>Trellia Cove (Mizuki Park)</t>
+        </is>
+      </c>
+      <c r="C58" s="24" t="inlineStr">
+        <is>
+          <t>Chung cu</t>
+        </is>
+      </c>
+      <c r="D58" s="24" t="inlineStr">
+        <is>
+          <t>3.9-5 ty</t>
+        </is>
+      </c>
+      <c r="E58" s="24" t="inlineStr">
+        <is>
+          <t>59-79m2</t>
+        </is>
+      </c>
+      <c r="F58" s="23" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="G58" s="23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H58" s="24" t="inlineStr">
+        <is>
+          <t>Nguyen Van Linh, X.Binh Hung, Binh Chanh</t>
+        </is>
+      </c>
+      <c r="I58" s="24" t="inlineStr">
+        <is>
+          <t>Binh Chanh</t>
+        </is>
+      </c>
+      <c r="J58" s="24" t="inlineStr">
+        <is>
+          <t>Nam Long, phan khu moi Mizuki Park</t>
+        </is>
+      </c>
+      <c r="K58" s="25" t="inlineStr">
+        <is>
+          <t>Xem BDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="23" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="24" t="inlineStr">
+        <is>
+          <t>Westgate An Gia</t>
+        </is>
+      </c>
+      <c r="C59" s="24" t="inlineStr">
+        <is>
+          <t>Chung cu</t>
+        </is>
+      </c>
+      <c r="D59" s="24" t="inlineStr">
+        <is>
+          <t>3.2-4.5 ty</t>
+        </is>
+      </c>
+      <c r="E59" s="24" t="inlineStr">
+        <is>
+          <t>59-113m2</t>
+        </is>
+      </c>
+      <c r="F59" s="23" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="G59" s="23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H59" s="24" t="inlineStr">
+        <is>
+          <t>Nguyen Van Linh, TT.Tan Tuc, Binh Chanh</t>
+        </is>
+      </c>
+      <c r="I59" s="24" t="inlineStr">
+        <is>
+          <t>Binh Chanh</t>
+        </is>
+      </c>
+      <c r="J59" s="24" t="inlineStr">
+        <is>
+          <t>An Gia Investment, so hong</t>
+        </is>
+      </c>
+      <c r="K59" s="25" t="inlineStr">
+        <is>
+          <t>Xem BDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="23" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="24" t="inlineStr">
+        <is>
+          <t>Sai Gon Mia</t>
+        </is>
+      </c>
+      <c r="C60" s="24" t="inlineStr">
+        <is>
+          <t>Chung cu</t>
+        </is>
+      </c>
+      <c r="D60" s="24" t="inlineStr">
+        <is>
+          <t>3.4-5 ty</t>
+        </is>
+      </c>
+      <c r="E60" s="24" t="inlineStr">
+        <is>
+          <t>66-78m2</t>
+        </is>
+      </c>
+      <c r="F60" s="23" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="G60" s="23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H60" s="24" t="inlineStr">
+        <is>
+          <t>Trung Son, X.Binh Hung, Binh Chanh</t>
+        </is>
+      </c>
+      <c r="I60" s="24" t="inlineStr">
+        <is>
+          <t>Binh Chanh</t>
+        </is>
+      </c>
+      <c r="J60" s="24" t="inlineStr">
+        <is>
+          <t>Hung Thinh, full noi that, view song</t>
+        </is>
+      </c>
+      <c r="K60" s="25" t="inlineStr">
+        <is>
+          <t>Xem BDS</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K54"/>
+  <autoFilter ref="A1:K60"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -3456,6 +3808,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K52" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K53" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K60" r:id="rId59"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3467,7 +3825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3511,1486 +3869,1654 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="20" t="inlineStr">
+      <c r="A2" s="26" t="inlineStr">
         <is>
           <t>Topaz Elite</t>
         </is>
       </c>
-      <c r="B2" s="20" t="inlineStr">
+      <c r="B2" s="26" t="inlineStr">
         <is>
           <t>Q.8</t>
         </is>
       </c>
-      <c r="C2" s="20" t="n">
+      <c r="C2" s="26" t="n">
         <v>10.7392189</v>
       </c>
-      <c r="D2" s="20" t="n">
+      <c r="D2" s="26" t="n">
         <v>106.6797322</v>
       </c>
-      <c r="E2" s="20" t="inlineStr">
+      <c r="E2" s="26" t="inlineStr">
         <is>
           <t>3.2-4.8 ty</t>
         </is>
       </c>
-      <c r="F2" s="20" t="inlineStr">
+      <c r="F2" s="26" t="inlineStr">
         <is>
           <t>Cao Lo, P.4, Q.8</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="20" t="inlineStr">
+      <c r="A3" s="26" t="inlineStr">
         <is>
           <t>Topaz City</t>
         </is>
       </c>
-      <c r="B3" s="20" t="inlineStr">
+      <c r="B3" s="26" t="inlineStr">
         <is>
           <t>Q.8</t>
         </is>
       </c>
-      <c r="C3" s="20" t="n">
+      <c r="C3" s="26" t="n">
         <v>10.7386</v>
       </c>
-      <c r="D3" s="20" t="n">
+      <c r="D3" s="26" t="n">
         <v>106.6798</v>
       </c>
-      <c r="E3" s="20" t="inlineStr">
+      <c r="E3" s="26" t="inlineStr">
         <is>
           <t>3.0-4.5 ty</t>
         </is>
       </c>
-      <c r="F3" s="20" t="inlineStr">
+      <c r="F3" s="26" t="inlineStr">
         <is>
           <t>Ta Quang Buu, P.5, Q.8</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="20" t="inlineStr">
+      <c r="A4" s="26" t="inlineStr">
         <is>
           <t>The Pegasuite</t>
         </is>
       </c>
-      <c r="B4" s="20" t="inlineStr">
+      <c r="B4" s="26" t="inlineStr">
         <is>
           <t>Q.8</t>
         </is>
       </c>
-      <c r="C4" s="20" t="n">
+      <c r="C4" s="26" t="n">
         <v>10.7342516</v>
       </c>
-      <c r="D4" s="20" t="n">
+      <c r="D4" s="26" t="n">
         <v>106.6533069</v>
       </c>
-      <c r="E4" s="20" t="inlineStr">
+      <c r="E4" s="26" t="inlineStr">
         <is>
           <t>3.0-4.5 ty</t>
         </is>
       </c>
-      <c r="F4" s="20" t="inlineStr">
+      <c r="F4" s="26" t="inlineStr">
         <is>
           <t>Ta Quang Buu, P.6, Q.8</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="20" t="inlineStr">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>The Pegasuite 2</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>Q.8</t>
         </is>
       </c>
-      <c r="C5" s="20" t="n">
+      <c r="C5" s="26" t="n">
         <v>10.7327</v>
       </c>
-      <c r="D5" s="20" t="n">
+      <c r="D5" s="26" t="n">
         <v>106.6501</v>
       </c>
-      <c r="E5" s="20" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t>3.2-5.0 ty</t>
         </is>
       </c>
-      <c r="F5" s="20" t="inlineStr">
+      <c r="F5" s="26" t="inlineStr">
         <is>
           <t>Ta Quang Buu, P.6, Q.8</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="inlineStr">
+      <c r="A6" s="26" t="inlineStr">
         <is>
           <t>D-Aqua</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>Q.8</t>
         </is>
       </c>
-      <c r="C6" s="20" t="n">
+      <c r="C6" s="26" t="n">
         <v>10.7402309</v>
       </c>
-      <c r="D6" s="20" t="n">
+      <c r="D6" s="26" t="n">
         <v>106.645793</v>
       </c>
-      <c r="E6" s="20" t="inlineStr">
+      <c r="E6" s="26" t="inlineStr">
         <is>
           <t>3.5-5.0 ty</t>
         </is>
       </c>
-      <c r="F6" s="20" t="inlineStr">
+      <c r="F6" s="26" t="inlineStr">
         <is>
           <t>Ben Binh Dong, P.14, Q.8</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="A7" s="26" t="inlineStr">
         <is>
           <t>Aurora Residences</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="26" t="inlineStr">
         <is>
           <t>Q.8</t>
         </is>
       </c>
-      <c r="C7" s="20" t="n">
+      <c r="C7" s="26" t="n">
         <v>10.7429092</v>
       </c>
-      <c r="D7" s="20" t="n">
+      <c r="D7" s="26" t="n">
         <v>106.6508679</v>
       </c>
-      <c r="E7" s="20" t="inlineStr">
+      <c r="E7" s="26" t="inlineStr">
         <is>
           <t>3.0-4.5 ty</t>
         </is>
       </c>
-      <c r="F7" s="20" t="inlineStr">
+      <c r="F7" s="26" t="inlineStr">
         <is>
           <t>Ben Binh Dong, P.13, Q.8</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="26" t="inlineStr">
         <is>
           <t>Green River</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>Q.8</t>
         </is>
       </c>
-      <c r="C8" s="20" t="n">
+      <c r="C8" s="26" t="n">
         <v>10.7335</v>
       </c>
-      <c r="D8" s="20" t="n">
+      <c r="D8" s="26" t="n">
         <v>106.6442</v>
       </c>
-      <c r="E8" s="20" t="inlineStr">
+      <c r="E8" s="26" t="inlineStr">
         <is>
           <t>3.0-3.8 ty</t>
         </is>
       </c>
-      <c r="F8" s="20" t="inlineStr">
+      <c r="F8" s="26" t="inlineStr">
         <is>
           <t>Pham The Hien, P.7, Q.8</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="A9" s="26" t="inlineStr">
         <is>
           <t>Tara Residence</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="26" t="inlineStr">
         <is>
           <t>Q.8</t>
         </is>
       </c>
-      <c r="C9" s="20" t="n">
+      <c r="C9" s="26" t="n">
         <v>10.7325</v>
       </c>
-      <c r="D9" s="20" t="n">
+      <c r="D9" s="26" t="n">
         <v>106.6531</v>
       </c>
-      <c r="E9" s="20" t="inlineStr">
+      <c r="E9" s="26" t="inlineStr">
         <is>
           <t>3.0-4.2 ty</t>
         </is>
       </c>
-      <c r="F9" s="20" t="inlineStr">
+      <c r="F9" s="26" t="inlineStr">
         <is>
           <t>Ta Quang Buu, P.6, Q.8</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="inlineStr">
+      <c r="A10" s="26" t="inlineStr">
         <is>
           <t>Saigon Skyview</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="26" t="inlineStr">
         <is>
           <t>Q.8</t>
         </is>
       </c>
-      <c r="C10" s="20" t="n">
+      <c r="C10" s="26" t="n">
         <v>10.7328855</v>
       </c>
-      <c r="D10" s="20" t="n">
+      <c r="D10" s="26" t="n">
         <v>106.6557022</v>
       </c>
-      <c r="E10" s="20" t="inlineStr">
+      <c r="E10" s="26" t="inlineStr">
         <is>
           <t>3.0-4.5 ty</t>
         </is>
       </c>
-      <c r="F10" s="20" t="inlineStr">
+      <c r="F10" s="26" t="inlineStr">
         <is>
           <t>Ta Quang Buu, P.6, Q.8</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="A11" s="26" t="inlineStr">
         <is>
           <t>Central Premium</t>
         </is>
       </c>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="26" t="inlineStr">
         <is>
           <t>Q.8</t>
         </is>
       </c>
-      <c r="C11" s="20" t="n">
+      <c r="C11" s="26" t="n">
         <v>10.7369</v>
       </c>
-      <c r="D11" s="20" t="n">
+      <c r="D11" s="26" t="n">
         <v>106.6691</v>
       </c>
-      <c r="E11" s="20" t="inlineStr">
+      <c r="E11" s="26" t="inlineStr">
         <is>
           <t>3.5-5.0 ty</t>
         </is>
       </c>
-      <c r="F11" s="20" t="inlineStr">
+      <c r="F11" s="26" t="inlineStr">
         <is>
           <t>Ta Quang Buu, P.1, Q.8</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="inlineStr">
+      <c r="A12" s="26" t="inlineStr">
         <is>
           <t>CC Bong Sao</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B12" s="26" t="inlineStr">
         <is>
           <t>Q.8</t>
         </is>
       </c>
-      <c r="C12" s="20" t="n">
+      <c r="C12" s="26" t="n">
         <v>10.7368621</v>
       </c>
-      <c r="D12" s="20" t="n">
+      <c r="D12" s="26" t="n">
         <v>106.6613181</v>
       </c>
-      <c r="E12" s="20" t="inlineStr">
+      <c r="E12" s="26" t="inlineStr">
         <is>
           <t>3.0-3.5 ty</t>
         </is>
       </c>
-      <c r="F12" s="20" t="inlineStr">
+      <c r="F12" s="26" t="inlineStr">
         <is>
           <t>Ta Quang Buu, P.5, Q.8</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="20" t="inlineStr">
+      <c r="A13" s="26" t="inlineStr">
         <is>
           <t>Diamond Riverside</t>
         </is>
       </c>
-      <c r="B13" s="20" t="inlineStr">
+      <c r="B13" s="26" t="inlineStr">
         <is>
           <t>Q.8</t>
         </is>
       </c>
-      <c r="C13" s="20" t="n">
+      <c r="C13" s="26" t="n">
         <v>10.7302</v>
       </c>
-      <c r="D13" s="20" t="n">
+      <c r="D13" s="26" t="n">
         <v>106.6248</v>
       </c>
-      <c r="E13" s="20" t="inlineStr">
+      <c r="E13" s="26" t="inlineStr">
         <is>
           <t>3.0-4.0 ty</t>
         </is>
       </c>
-      <c r="F13" s="20" t="inlineStr">
+      <c r="F13" s="26" t="inlineStr">
         <is>
           <t>Vo Van Kiet, P.16, Q.8</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="inlineStr">
+      <c r="A14" s="26" t="inlineStr">
         <is>
           <t>Conic Riverside</t>
         </is>
       </c>
-      <c r="B14" s="20" t="inlineStr">
+      <c r="B14" s="26" t="inlineStr">
         <is>
           <t>Q.8</t>
         </is>
       </c>
-      <c r="C14" s="20" t="n">
+      <c r="C14" s="26" t="n">
         <v>10.7184884</v>
       </c>
-      <c r="D14" s="20" t="n">
+      <c r="D14" s="26" t="n">
         <v>106.6371053</v>
       </c>
-      <c r="E14" s="20" t="inlineStr">
+      <c r="E14" s="26" t="inlineStr">
         <is>
           <t>3.0-4.2 ty</t>
         </is>
       </c>
-      <c r="F14" s="20" t="inlineStr">
+      <c r="F14" s="26" t="inlineStr">
         <is>
           <t>Ta Quang Buu, P.7, Q.8</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="20" t="inlineStr">
+      <c r="A15" s="26" t="inlineStr">
         <is>
           <t>Asiana Capella</t>
         </is>
       </c>
-      <c r="B15" s="20" t="inlineStr">
+      <c r="B15" s="26" t="inlineStr">
         <is>
           <t>Q.6</t>
         </is>
       </c>
-      <c r="C15" s="20" t="n">
+      <c r="C15" s="26" t="n">
         <v>10.7398895</v>
       </c>
-      <c r="D15" s="20" t="n">
+      <c r="D15" s="26" t="n">
         <v>106.6280712</v>
       </c>
-      <c r="E15" s="20" t="inlineStr">
+      <c r="E15" s="26" t="inlineStr">
         <is>
           <t>3.5-5.0 ty</t>
         </is>
       </c>
-      <c r="F15" s="20" t="inlineStr">
+      <c r="F15" s="26" t="inlineStr">
         <is>
           <t>Tran Van Kieu, P.10, Q.6</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="20" t="inlineStr">
+      <c r="A16" s="26" t="inlineStr">
         <is>
           <t>Him Lam Cho Lon</t>
         </is>
       </c>
-      <c r="B16" s="20" t="inlineStr">
+      <c r="B16" s="26" t="inlineStr">
         <is>
           <t>Q.6</t>
         </is>
       </c>
-      <c r="C16" s="20" t="n">
+      <c r="C16" s="26" t="n">
         <v>10.7466</v>
       </c>
-      <c r="D16" s="20" t="n">
+      <c r="D16" s="26" t="n">
         <v>106.6379</v>
       </c>
-      <c r="E16" s="20" t="inlineStr">
+      <c r="E16" s="26" t="inlineStr">
         <is>
           <t>3.0-4.5 ty</t>
         </is>
       </c>
-      <c r="F16" s="20" t="inlineStr">
+      <c r="F16" s="26" t="inlineStr">
         <is>
           <t>Dai lo Dong Tay, P.11, Q.6</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="20" t="inlineStr">
+      <c r="A17" s="26" t="inlineStr">
         <is>
           <t>Viva Riverside</t>
         </is>
       </c>
-      <c r="B17" s="20" t="inlineStr">
+      <c r="B17" s="26" t="inlineStr">
         <is>
           <t>Q.6</t>
         </is>
       </c>
-      <c r="C17" s="20" t="n">
+      <c r="C17" s="26" t="n">
         <v>10.7427112</v>
       </c>
-      <c r="D17" s="20" t="n">
+      <c r="D17" s="26" t="n">
         <v>106.6474475</v>
       </c>
-      <c r="E17" s="20" t="inlineStr">
+      <c r="E17" s="26" t="inlineStr">
         <is>
           <t>3.0-4.5 ty</t>
         </is>
       </c>
-      <c r="F17" s="20" t="inlineStr">
+      <c r="F17" s="26" t="inlineStr">
         <is>
           <t>Vo Van Kiet, P.1, Q.6</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="20" t="inlineStr">
+      <c r="A18" s="26" t="inlineStr">
         <is>
           <t>Saigon Asiana</t>
         </is>
       </c>
-      <c r="B18" s="20" t="inlineStr">
+      <c r="B18" s="26" t="inlineStr">
         <is>
           <t>Q.6</t>
         </is>
       </c>
-      <c r="C18" s="20" t="n">
+      <c r="C18" s="26" t="n">
         <v>10.7501021</v>
       </c>
-      <c r="D18" s="20" t="n">
+      <c r="D18" s="26" t="n">
         <v>106.6367849</v>
       </c>
-      <c r="E18" s="20" t="inlineStr">
+      <c r="E18" s="26" t="inlineStr">
         <is>
           <t>3.0-4.2 ty</t>
         </is>
       </c>
-      <c r="F18" s="20" t="inlineStr">
+      <c r="F18" s="26" t="inlineStr">
         <is>
           <t>NV Luong, P.12, Q.6</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="20" t="inlineStr">
+      <c r="A19" s="26" t="inlineStr">
         <is>
           <t>D-Homme</t>
         </is>
       </c>
-      <c r="B19" s="20" t="inlineStr">
+      <c r="B19" s="26" t="inlineStr">
         <is>
           <t>Q.6</t>
         </is>
       </c>
-      <c r="C19" s="20" t="n">
+      <c r="C19" s="26" t="n">
         <v>10.7537</v>
       </c>
-      <c r="D19" s="20" t="n">
+      <c r="D19" s="26" t="n">
         <v>106.6446</v>
       </c>
-      <c r="E19" s="20" t="inlineStr">
+      <c r="E19" s="26" t="inlineStr">
         <is>
           <t>3.8-5.0 ty</t>
         </is>
       </c>
-      <c r="F19" s="20" t="inlineStr">
+      <c r="F19" s="26" t="inlineStr">
         <is>
           <t>Hong Bang, P.12, Q.6</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="inlineStr">
+      <c r="A20" s="26" t="inlineStr">
         <is>
           <t>Summer Square</t>
         </is>
       </c>
-      <c r="B20" s="20" t="inlineStr">
+      <c r="B20" s="26" t="inlineStr">
         <is>
           <t>Q.6</t>
         </is>
       </c>
-      <c r="C20" s="20" t="n">
+      <c r="C20" s="26" t="n">
         <v>10.7593879</v>
       </c>
-      <c r="D20" s="20" t="n">
+      <c r="D20" s="26" t="n">
         <v>106.6259582</v>
       </c>
-      <c r="E20" s="20" t="inlineStr">
+      <c r="E20" s="26" t="inlineStr">
         <is>
           <t>3.0-3.8 ty</t>
         </is>
       </c>
-      <c r="F20" s="20" t="inlineStr">
+      <c r="F20" s="26" t="inlineStr">
         <is>
           <t>Tan Hoa Dong, P.14, Q.6</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="20" t="inlineStr">
+      <c r="A21" s="26" t="inlineStr">
         <is>
           <t>CHCC 155 Nguyen Chi Thanh</t>
         </is>
       </c>
-      <c r="B21" s="20" t="inlineStr">
+      <c r="B21" s="26" t="inlineStr">
         <is>
           <t>Q.5</t>
         </is>
       </c>
-      <c r="C21" s="20" t="n">
+      <c r="C21" s="26" t="n">
         <v>10.7811842</v>
       </c>
-      <c r="D21" s="20" t="n">
+      <c r="D21" s="26" t="n">
         <v>106.7060405</v>
       </c>
-      <c r="E21" s="20" t="inlineStr">
+      <c r="E21" s="26" t="inlineStr">
         <is>
           <t>4.3 ty</t>
         </is>
       </c>
-      <c r="F21" s="20" t="inlineStr">
+      <c r="F21" s="26" t="inlineStr">
         <is>
           <t>155 Nguyen Chi Thanh, P.9, Q.5</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="20" t="inlineStr">
+      <c r="A22" s="26" t="inlineStr">
         <is>
           <t>Chung cu Hung Vuong (Tan Da)</t>
         </is>
       </c>
-      <c r="B22" s="20" t="inlineStr">
+      <c r="B22" s="26" t="inlineStr">
         <is>
           <t>Q.5</t>
         </is>
       </c>
-      <c r="C22" s="20" t="n">
+      <c r="C22" s="26" t="n">
         <v>10.7538946</v>
       </c>
-      <c r="D22" s="20" t="n">
+      <c r="D22" s="26" t="n">
         <v>106.6653437</v>
       </c>
-      <c r="E22" s="20" t="inlineStr">
+      <c r="E22" s="26" t="inlineStr">
         <is>
           <t>3.05-3.2 ty</t>
         </is>
       </c>
-      <c r="F22" s="20" t="inlineStr">
+      <c r="F22" s="26" t="inlineStr">
         <is>
           <t>Tan Da, P.11, Q.5</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="20" t="inlineStr">
+      <c r="A23" s="26" t="inlineStr">
         <is>
           <t>Chung cu Nguyen Trai</t>
         </is>
       </c>
-      <c r="B23" s="20" t="inlineStr">
+      <c r="B23" s="26" t="inlineStr">
         <is>
           <t>Q.5</t>
         </is>
       </c>
-      <c r="C23" s="20" t="n">
+      <c r="C23" s="26" t="n">
         <v>10.7557827</v>
       </c>
-      <c r="D23" s="20" t="n">
+      <c r="D23" s="26" t="n">
         <v>106.6690391</v>
       </c>
-      <c r="E23" s="20" t="inlineStr">
+      <c r="E23" s="26" t="inlineStr">
         <is>
           <t>3.25 ty</t>
         </is>
       </c>
-      <c r="F23" s="20" t="inlineStr">
+      <c r="F23" s="26" t="inlineStr">
         <is>
           <t>Nguyen Trai, P.1, Q.5</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="20" t="inlineStr">
+      <c r="A24" s="26" t="inlineStr">
         <is>
           <t>The Everrich Infinity</t>
         </is>
       </c>
-      <c r="B24" s="20" t="inlineStr">
+      <c r="B24" s="26" t="inlineStr">
         <is>
           <t>Q.5</t>
         </is>
       </c>
-      <c r="C24" s="20" t="n">
+      <c r="C24" s="26" t="n">
         <v>10.760861</v>
       </c>
-      <c r="D24" s="20" t="n">
+      <c r="D24" s="26" t="n">
         <v>106.6806479</v>
       </c>
-      <c r="E24" s="20" t="inlineStr">
+      <c r="E24" s="26" t="inlineStr">
         <is>
           <t>3.3-4.5 ty</t>
         </is>
       </c>
-      <c r="F24" s="20" t="inlineStr">
+      <c r="F24" s="26" t="inlineStr">
         <is>
           <t>An Duong Vuong, P.4, Q.5</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="20" t="inlineStr">
+      <c r="A25" s="26" t="inlineStr">
         <is>
           <t>Can ho Lakai</t>
         </is>
       </c>
-      <c r="B25" s="20" t="inlineStr">
+      <c r="B25" s="26" t="inlineStr">
         <is>
           <t>Q.5</t>
         </is>
       </c>
-      <c r="C25" s="20" t="n">
+      <c r="C25" s="26" t="n">
         <v>10.7540121</v>
       </c>
-      <c r="D25" s="20" t="n">
+      <c r="D25" s="26" t="n">
         <v>106.6697165</v>
       </c>
-      <c r="E25" s="20" t="inlineStr">
+      <c r="E25" s="26" t="inlineStr">
         <is>
           <t>4.4 ty</t>
         </is>
       </c>
-      <c r="F25" s="20" t="inlineStr">
+      <c r="F25" s="26" t="inlineStr">
         <is>
           <t>Nguyen Tri Phuong, P.8, Q.5</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="20" t="inlineStr">
+      <c r="A26" s="26" t="inlineStr">
         <is>
           <t>Legacy 66 Tan Thanh</t>
         </is>
       </c>
-      <c r="B26" s="20" t="inlineStr">
+      <c r="B26" s="26" t="inlineStr">
         <is>
           <t>Q.5</t>
         </is>
       </c>
-      <c r="C26" s="20" t="n">
+      <c r="C26" s="26" t="n">
         <v>10.7564974</v>
       </c>
-      <c r="D26" s="20" t="n">
+      <c r="D26" s="26" t="n">
         <v>106.6565336</v>
       </c>
-      <c r="E26" s="20" t="inlineStr">
+      <c r="E26" s="26" t="inlineStr">
         <is>
           <t>4.5 ty</t>
         </is>
       </c>
-      <c r="F26" s="20" t="inlineStr">
+      <c r="F26" s="26" t="inlineStr">
         <is>
           <t>Tan Thanh, P.12, Q.5</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="20" t="inlineStr">
+      <c r="A27" s="26" t="inlineStr">
         <is>
           <t>CC Phan Van Tri Q5</t>
         </is>
       </c>
-      <c r="B27" s="20" t="inlineStr">
+      <c r="B27" s="26" t="inlineStr">
         <is>
           <t>Q.5</t>
         </is>
       </c>
-      <c r="C27" s="20" t="n">
+      <c r="C27" s="26" t="n">
         <v>10.7535</v>
       </c>
-      <c r="D27" s="20" t="n">
+      <c r="D27" s="26" t="n">
         <v>106.6723</v>
       </c>
-      <c r="E27" s="20" t="inlineStr">
+      <c r="E27" s="26" t="inlineStr">
         <is>
           <t>3.15 ty</t>
         </is>
       </c>
-      <c r="F27" s="20" t="inlineStr">
+      <c r="F27" s="26" t="inlineStr">
         <is>
           <t>Phan Van Tri, P.2, Q.5</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="20" t="inlineStr">
+      <c r="A28" s="26" t="inlineStr">
         <is>
           <t>Chung cu Phuc Thinh</t>
         </is>
       </c>
-      <c r="B28" s="20" t="inlineStr">
+      <c r="B28" s="26" t="inlineStr">
         <is>
           <t>Q.5</t>
         </is>
       </c>
-      <c r="C28" s="20" t="n">
+      <c r="C28" s="26" t="n">
         <v>10.7534138</v>
       </c>
-      <c r="D28" s="20" t="n">
+      <c r="D28" s="26" t="n">
         <v>106.6802515</v>
       </c>
-      <c r="E28" s="20" t="inlineStr">
+      <c r="E28" s="26" t="inlineStr">
         <is>
           <t>3.75-4.6 ty</t>
         </is>
       </c>
-      <c r="F28" s="20" t="inlineStr">
+      <c r="F28" s="26" t="inlineStr">
         <is>
           <t>Cao Dat, P.1, Q.5</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="20" t="inlineStr">
+      <c r="A29" s="26" t="inlineStr">
         <is>
           <t>CC Dao Tan Q5</t>
         </is>
       </c>
-      <c r="B29" s="20" t="inlineStr">
+      <c r="B29" s="26" t="inlineStr">
         <is>
           <t>Q.5</t>
         </is>
       </c>
-      <c r="C29" s="20" t="n">
+      <c r="C29" s="26" t="n">
         <v>10.752</v>
       </c>
-      <c r="D29" s="20" t="n">
+      <c r="D29" s="26" t="n">
         <v>106.6697</v>
       </c>
-      <c r="E29" s="20" t="inlineStr">
+      <c r="E29" s="26" t="inlineStr">
         <is>
           <t>4.66 ty</t>
         </is>
       </c>
-      <c r="F29" s="20" t="inlineStr">
+      <c r="F29" s="26" t="inlineStr">
         <is>
           <t>Dao Tan, P.5, Q.5</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="20" t="inlineStr">
+      <c r="A30" s="26" t="inlineStr">
         <is>
           <t>CC Nguyen Bieu Q5</t>
         </is>
       </c>
-      <c r="B30" s="20" t="inlineStr">
+      <c r="B30" s="26" t="inlineStr">
         <is>
           <t>Q.5</t>
         </is>
       </c>
-      <c r="C30" s="20" t="n">
+      <c r="C30" s="26" t="n">
         <v>10.7556705</v>
       </c>
-      <c r="D30" s="20" t="n">
+      <c r="D30" s="26" t="n">
         <v>106.6732042</v>
       </c>
-      <c r="E30" s="20" t="inlineStr">
+      <c r="E30" s="26" t="inlineStr">
         <is>
           <t>3 ty</t>
         </is>
       </c>
-      <c r="F30" s="20" t="inlineStr">
+      <c r="F30" s="26" t="inlineStr">
         <is>
           <t>Nguyen Bieu, P.1, Q.5</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="20" t="inlineStr">
+      <c r="A31" s="26" t="inlineStr">
         <is>
           <t>Chung cu Le Thi Rieng</t>
         </is>
       </c>
-      <c r="B31" s="20" t="inlineStr">
+      <c r="B31" s="26" t="inlineStr">
         <is>
           <t>Q.10</t>
         </is>
       </c>
-      <c r="C31" s="20" t="n">
+      <c r="C31" s="26" t="n">
         <v>10.7811901</v>
       </c>
-      <c r="D31" s="20" t="n">
+      <c r="D31" s="26" t="n">
         <v>106.6630125</v>
       </c>
-      <c r="E31" s="20" t="inlineStr">
+      <c r="E31" s="26" t="inlineStr">
         <is>
           <t>3.8 ty</t>
         </is>
       </c>
-      <c r="F31" s="20" t="inlineStr">
+      <c r="F31" s="26" t="inlineStr">
         <is>
           <t>Le Thi Rieng, P.15, Q.10</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="20" t="inlineStr">
+      <c r="A32" s="26" t="inlineStr">
         <is>
           <t>CC Ly Thuong Kiet Q10</t>
         </is>
       </c>
-      <c r="B32" s="20" t="inlineStr">
+      <c r="B32" s="26" t="inlineStr">
         <is>
           <t>Q.10</t>
         </is>
       </c>
-      <c r="C32" s="20" t="n">
+      <c r="C32" s="26" t="n">
         <v>10.768769</v>
       </c>
-      <c r="D32" s="20" t="n">
+      <c r="D32" s="26" t="n">
         <v>106.6617061</v>
       </c>
-      <c r="E32" s="20" t="inlineStr">
+      <c r="E32" s="26" t="inlineStr">
         <is>
           <t>3 ty</t>
         </is>
       </c>
-      <c r="F32" s="20" t="inlineStr">
+      <c r="F32" s="26" t="inlineStr">
         <is>
           <t>Ly Thuong Kiet, P.7, Q.10</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="20" t="inlineStr">
+      <c r="A33" s="26" t="inlineStr">
         <is>
           <t>Cao oc Ngo Gia Tu</t>
         </is>
       </c>
-      <c r="B33" s="20" t="inlineStr">
+      <c r="B33" s="26" t="inlineStr">
         <is>
           <t>Q.10</t>
         </is>
       </c>
-      <c r="C33" s="20" t="n">
+      <c r="C33" s="26" t="n">
         <v>10.7638244</v>
       </c>
-      <c r="D33" s="20" t="n">
+      <c r="D33" s="26" t="n">
         <v>106.6716585</v>
       </c>
-      <c r="E33" s="20" t="inlineStr">
+      <c r="E33" s="26" t="inlineStr">
         <is>
           <t>3.9 ty</t>
         </is>
       </c>
-      <c r="F33" s="20" t="inlineStr">
+      <c r="F33" s="26" t="inlineStr">
         <is>
           <t>Ngo Gia Tu, P.3, Q.10</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="20" t="inlineStr">
+      <c r="A34" s="26" t="inlineStr">
         <is>
           <t>Chung cu Nguyen Kim</t>
         </is>
       </c>
-      <c r="B34" s="20" t="inlineStr">
+      <c r="B34" s="26" t="inlineStr">
         <is>
           <t>Q.10</t>
         </is>
       </c>
-      <c r="C34" s="20" t="n">
+      <c r="C34" s="26" t="n">
         <v>10.7613175</v>
       </c>
-      <c r="D34" s="20" t="n">
+      <c r="D34" s="26" t="n">
         <v>106.6618954</v>
       </c>
-      <c r="E34" s="20" t="inlineStr">
+      <c r="E34" s="26" t="inlineStr">
         <is>
           <t>3.45 ty</t>
         </is>
       </c>
-      <c r="F34" s="20" t="inlineStr">
+      <c r="F34" s="26" t="inlineStr">
         <is>
           <t>Nguyen Kim, P.7, Q.10</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="20" t="inlineStr">
+      <c r="A35" s="26" t="inlineStr">
         <is>
           <t>Hoa Sen - Lotus Apartment</t>
         </is>
       </c>
-      <c r="B35" s="20" t="inlineStr">
+      <c r="B35" s="26" t="inlineStr">
         <is>
           <t>Q.11</t>
         </is>
       </c>
-      <c r="C35" s="20" t="n">
+      <c r="C35" s="26" t="n">
         <v>10.7660078</v>
       </c>
-      <c r="D35" s="20" t="n">
+      <c r="D35" s="26" t="n">
         <v>106.6427565</v>
       </c>
-      <c r="E35" s="20" t="inlineStr">
+      <c r="E35" s="26" t="inlineStr">
         <is>
           <t>4.3 ty</t>
         </is>
       </c>
-      <c r="F35" s="20" t="inlineStr">
+      <c r="F35" s="26" t="inlineStr">
         <is>
           <t>Lac Long Quan, P.10, Q.11</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="20" t="inlineStr">
+      <c r="A36" s="26" t="inlineStr">
         <is>
           <t>CC Ly Thuong Kiet Q11</t>
         </is>
       </c>
-      <c r="B36" s="20" t="inlineStr">
+      <c r="B36" s="26" t="inlineStr">
         <is>
           <t>Q.11</t>
         </is>
       </c>
-      <c r="C36" s="20" t="n">
+      <c r="C36" s="26" t="n">
         <v>10.7683972</v>
       </c>
-      <c r="D36" s="20" t="n">
+      <c r="D36" s="26" t="n">
         <v>106.6618361</v>
       </c>
-      <c r="E36" s="20" t="inlineStr">
+      <c r="E36" s="26" t="inlineStr">
         <is>
           <t>3.2 ty</t>
         </is>
       </c>
-      <c r="F36" s="20" t="inlineStr">
+      <c r="F36" s="26" t="inlineStr">
         <is>
           <t>Ly Thuong Kiet, P.7, Q.11</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="20" t="inlineStr">
+      <c r="A37" s="26" t="inlineStr">
         <is>
           <t>CC Lac Long Quan Q11</t>
         </is>
       </c>
-      <c r="B37" s="20" t="inlineStr">
+      <c r="B37" s="26" t="inlineStr">
         <is>
           <t>Q.11</t>
         </is>
       </c>
-      <c r="C37" s="20" t="n">
+      <c r="C37" s="26" t="n">
         <v>10.7706699</v>
       </c>
-      <c r="D37" s="20" t="n">
+      <c r="D37" s="26" t="n">
         <v>106.6443301</v>
       </c>
-      <c r="E37" s="20" t="inlineStr">
+      <c r="E37" s="26" t="inlineStr">
         <is>
           <t>3.63 ty</t>
         </is>
       </c>
-      <c r="F37" s="20" t="inlineStr">
+      <c r="F37" s="26" t="inlineStr">
         <is>
           <t>Lac Long Quan, P.5, Q.11</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="20" t="inlineStr">
+      <c r="A38" s="26" t="inlineStr">
         <is>
           <t>Res 11</t>
         </is>
       </c>
-      <c r="B38" s="20" t="inlineStr">
+      <c r="B38" s="26" t="inlineStr">
         <is>
           <t>Q.11</t>
         </is>
       </c>
-      <c r="C38" s="20" t="n">
+      <c r="C38" s="26" t="n">
         <v>10.763534</v>
       </c>
-      <c r="D38" s="20" t="n">
+      <c r="D38" s="26" t="n">
         <v>106.6419219</v>
       </c>
-      <c r="E38" s="20" t="inlineStr">
+      <c r="E38" s="26" t="inlineStr">
         <is>
           <t>3.55-5 ty</t>
         </is>
       </c>
-      <c r="F38" s="20" t="inlineStr">
+      <c r="F38" s="26" t="inlineStr">
         <is>
           <t>Lac Long Quan, P.3, Q.11</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="20" t="inlineStr">
+      <c r="A39" s="26" t="inlineStr">
         <is>
           <t>Chung cu 312 Lac Long Quan</t>
         </is>
       </c>
-      <c r="B39" s="20" t="inlineStr">
+      <c r="B39" s="26" t="inlineStr">
         <is>
           <t>Q.11</t>
         </is>
       </c>
-      <c r="C39" s="20" t="n">
+      <c r="C39" s="26" t="n">
         <v>10.7686327</v>
       </c>
-      <c r="D39" s="20" t="n">
+      <c r="D39" s="26" t="n">
         <v>106.644232</v>
       </c>
-      <c r="E39" s="20" t="inlineStr">
+      <c r="E39" s="26" t="inlineStr">
         <is>
           <t>3.4 ty</t>
         </is>
       </c>
-      <c r="F39" s="20" t="inlineStr">
+      <c r="F39" s="26" t="inlineStr">
         <is>
           <t>312 Lac Long Quan, P.5, Q.11</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="20" t="inlineStr">
+      <c r="A40" s="26" t="inlineStr">
         <is>
           <t>Chung cu Phu Tho Q11</t>
         </is>
       </c>
-      <c r="B40" s="20" t="inlineStr">
+      <c r="B40" s="26" t="inlineStr">
         <is>
           <t>Q.11</t>
         </is>
       </c>
-      <c r="C40" s="20" t="n">
+      <c r="C40" s="26" t="n">
         <v>10.7698821</v>
       </c>
-      <c r="D40" s="20" t="n">
+      <c r="D40" s="26" t="n">
         <v>106.6534079</v>
       </c>
-      <c r="E40" s="20" t="inlineStr">
+      <c r="E40" s="26" t="inlineStr">
         <is>
           <t>3.7 ty</t>
         </is>
       </c>
-      <c r="F40" s="20" t="inlineStr">
+      <c r="F40" s="26" t="inlineStr">
         <is>
           <t>Nguyen Thi Nho, P.15, Q.11</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="20" t="inlineStr">
+      <c r="A41" s="26" t="inlineStr">
         <is>
           <t>H3 Hoang Dieu</t>
         </is>
       </c>
-      <c r="B41" s="20" t="inlineStr">
+      <c r="B41" s="26" t="inlineStr">
         <is>
           <t>Q.4</t>
         </is>
       </c>
-      <c r="C41" s="20" t="n">
+      <c r="C41" s="26" t="n">
         <v>10.7603234</v>
       </c>
-      <c r="D41" s="20" t="n">
+      <c r="D41" s="26" t="n">
         <v>106.6990936</v>
       </c>
-      <c r="E41" s="20" t="inlineStr">
+      <c r="E41" s="26" t="inlineStr">
         <is>
           <t>4.3 ty</t>
         </is>
       </c>
-      <c r="F41" s="20" t="inlineStr">
+      <c r="F41" s="26" t="inlineStr">
         <is>
           <t>Hoang Dieu, P. Khanh Hoi, Q.4</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="20" t="inlineStr">
+      <c r="A42" s="26" t="inlineStr">
         <is>
           <t>Saigon Royal Residence</t>
         </is>
       </c>
-      <c r="B42" s="20" t="inlineStr">
+      <c r="B42" s="26" t="inlineStr">
         <is>
           <t>Q.4</t>
         </is>
       </c>
-      <c r="C42" s="20" t="n">
+      <c r="C42" s="26" t="n">
         <v>10.7670153</v>
       </c>
-      <c r="D42" s="20" t="n">
+      <c r="D42" s="26" t="n">
         <v>106.7038674</v>
       </c>
-      <c r="E42" s="20" t="inlineStr">
+      <c r="E42" s="26" t="inlineStr">
         <is>
           <t>4.3 ty</t>
         </is>
       </c>
-      <c r="F42" s="20" t="inlineStr">
+      <c r="F42" s="26" t="inlineStr">
         <is>
           <t>Ben Van Don, P. Xom Chieu, Q.4</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="20" t="inlineStr">
+      <c r="A43" s="26" t="inlineStr">
         <is>
           <t>The Gold View</t>
         </is>
       </c>
-      <c r="B43" s="20" t="inlineStr">
+      <c r="B43" s="26" t="inlineStr">
         <is>
           <t>Q.4</t>
         </is>
       </c>
-      <c r="C43" s="20" t="n">
+      <c r="C43" s="26" t="n">
         <v>10.756248</v>
       </c>
-      <c r="D43" s="20" t="n">
+      <c r="D43" s="26" t="n">
         <v>106.6918721</v>
       </c>
-      <c r="E43" s="20" t="inlineStr">
+      <c r="E43" s="26" t="inlineStr">
         <is>
           <t>3.2 ty</t>
         </is>
       </c>
-      <c r="F43" s="20" t="inlineStr">
+      <c r="F43" s="26" t="inlineStr">
         <is>
           <t>Ben Van Don, P. Vinh Hoi, Q.4</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="20" t="inlineStr">
+      <c r="A44" s="26" t="inlineStr">
         <is>
           <t>River Gate</t>
         </is>
       </c>
-      <c r="B44" s="20" t="inlineStr">
+      <c r="B44" s="26" t="inlineStr">
         <is>
           <t>Q.4</t>
         </is>
       </c>
-      <c r="C44" s="20" t="n">
+      <c r="C44" s="26" t="n">
         <v>10.7626586</v>
       </c>
-      <c r="D44" s="20" t="n">
+      <c r="D44" s="26" t="n">
         <v>106.6991882</v>
       </c>
-      <c r="E44" s="20" t="inlineStr">
+      <c r="E44" s="26" t="inlineStr">
         <is>
           <t>3-4 ty</t>
         </is>
       </c>
-      <c r="F44" s="20" t="inlineStr">
+      <c r="F44" s="26" t="inlineStr">
         <is>
           <t>Ben Van Don, P. Khanh Hoi, Q.4</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="20" t="inlineStr">
+      <c r="A45" s="26" t="inlineStr">
         <is>
           <t>The Tresor</t>
         </is>
       </c>
-      <c r="B45" s="20" t="inlineStr">
+      <c r="B45" s="26" t="inlineStr">
         <is>
           <t>Q.4</t>
         </is>
       </c>
-      <c r="C45" s="20" t="n">
+      <c r="C45" s="26" t="n">
         <v>10.766733</v>
       </c>
-      <c r="D45" s="20" t="n">
+      <c r="D45" s="26" t="n">
         <v>106.7032221</v>
       </c>
-      <c r="E45" s="20" t="inlineStr">
+      <c r="E45" s="26" t="inlineStr">
         <is>
           <t>3.4 ty</t>
         </is>
       </c>
-      <c r="F45" s="20" t="inlineStr">
+      <c r="F45" s="26" t="inlineStr">
         <is>
           <t>Ben Van Don, P. Xom Chieu, Q.4</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="20" t="inlineStr">
+      <c r="A46" s="26" t="inlineStr">
         <is>
           <t>Q7 Saigon Riverside</t>
         </is>
       </c>
-      <c r="B46" s="20" t="inlineStr">
+      <c r="B46" s="26" t="inlineStr">
         <is>
           <t>Q.7</t>
         </is>
       </c>
-      <c r="C46" s="20" t="n">
+      <c r="C46" s="26" t="n">
         <v>10.7229238</v>
       </c>
-      <c r="D46" s="20" t="n">
+      <c r="D46" s="26" t="n">
         <v>106.7415437</v>
       </c>
-      <c r="E46" s="20" t="inlineStr">
+      <c r="E46" s="26" t="inlineStr">
         <is>
           <t>3.1-3.6 ty</t>
         </is>
       </c>
-      <c r="F46" s="20" t="inlineStr">
+      <c r="F46" s="26" t="inlineStr">
         <is>
           <t>Dao Tri, P. Phu Thuan, Q.7</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="20" t="inlineStr">
+      <c r="A47" s="26" t="inlineStr">
         <is>
           <t>Luxcity</t>
         </is>
       </c>
-      <c r="B47" s="20" t="inlineStr">
+      <c r="B47" s="26" t="inlineStr">
         <is>
           <t>Q.7</t>
         </is>
       </c>
-      <c r="C47" s="20" t="n">
+      <c r="C47" s="26" t="n">
         <v>10.7387122</v>
       </c>
-      <c r="D47" s="20" t="n">
+      <c r="D47" s="26" t="n">
         <v>106.7299709</v>
       </c>
-      <c r="E47" s="20" t="inlineStr">
+      <c r="E47" s="26" t="inlineStr">
         <is>
           <t>4.3-5 ty</t>
         </is>
       </c>
-      <c r="F47" s="20" t="inlineStr">
+      <c r="F47" s="26" t="inlineStr">
         <is>
           <t>Huynh Tan Phat, P. Binh Thuan, Q.7</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="20" t="inlineStr">
+      <c r="A48" s="26" t="inlineStr">
         <is>
           <t>River Panorama</t>
         </is>
       </c>
-      <c r="B48" s="20" t="inlineStr">
+      <c r="B48" s="26" t="inlineStr">
         <is>
           <t>Q.7</t>
         </is>
       </c>
-      <c r="C48" s="20" t="n">
+      <c r="C48" s="26" t="n">
         <v>10.7145604</v>
       </c>
-      <c r="D48" s="20" t="n">
+      <c r="D48" s="26" t="n">
         <v>106.7415783</v>
       </c>
-      <c r="E48" s="20" t="inlineStr">
+      <c r="E48" s="26" t="inlineStr">
         <is>
           <t>3.9-4.7 ty</t>
         </is>
       </c>
-      <c r="F48" s="20" t="inlineStr">
+      <c r="F48" s="26" t="inlineStr">
         <is>
           <t>Hoang Quoc Viet, P. Phu Thuan, Q.7</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="20" t="inlineStr">
+      <c r="A49" s="26" t="inlineStr">
         <is>
           <t>Q7 Boulevard</t>
         </is>
       </c>
-      <c r="B49" s="20" t="inlineStr">
+      <c r="B49" s="26" t="inlineStr">
         <is>
           <t>Q.7</t>
         </is>
       </c>
-      <c r="C49" s="20" t="n">
+      <c r="C49" s="26" t="n">
         <v>10.7078219</v>
       </c>
-      <c r="D49" s="20" t="n">
+      <c r="D49" s="26" t="n">
         <v>106.7329454</v>
       </c>
-      <c r="E49" s="20" t="inlineStr">
+      <c r="E49" s="26" t="inlineStr">
         <is>
           <t>3.3-3.9 ty</t>
         </is>
       </c>
-      <c r="F49" s="20" t="inlineStr">
+      <c r="F49" s="26" t="inlineStr">
         <is>
           <t>Nguyen Luong Bang, P. Phu My, Q.7</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="20" t="inlineStr">
+      <c r="A50" s="26" t="inlineStr">
         <is>
           <t>Sunshine Sky City</t>
         </is>
       </c>
-      <c r="B50" s="20" t="inlineStr">
+      <c r="B50" s="26" t="inlineStr">
         <is>
           <t>Q.7</t>
         </is>
       </c>
-      <c r="C50" s="20" t="n">
+      <c r="C50" s="26" t="n">
         <v>10.7295023</v>
       </c>
-      <c r="D50" s="20" t="n">
+      <c r="D50" s="26" t="n">
         <v>106.7304584</v>
       </c>
-      <c r="E50" s="20" t="inlineStr">
+      <c r="E50" s="26" t="inlineStr">
         <is>
           <t>4.2 ty</t>
         </is>
       </c>
-      <c r="F50" s="20" t="inlineStr">
+      <c r="F50" s="26" t="inlineStr">
         <is>
           <t>Phu Thuan, P. Tan Phu, Q.7</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="20" t="inlineStr">
+      <c r="A51" s="26" t="inlineStr">
         <is>
           <t>Eco Green Sai Gon</t>
         </is>
       </c>
-      <c r="B51" s="20" t="inlineStr">
+      <c r="B51" s="26" t="inlineStr">
         <is>
           <t>Q.7</t>
         </is>
       </c>
-      <c r="C51" s="20" t="n">
+      <c r="C51" s="26" t="n">
         <v>10.7487183</v>
       </c>
-      <c r="D51" s="20" t="n">
+      <c r="D51" s="26" t="n">
         <v>106.723741</v>
       </c>
-      <c r="E51" s="20" t="inlineStr">
+      <c r="E51" s="26" t="inlineStr">
         <is>
           <t>4.8-5 ty</t>
         </is>
       </c>
-      <c r="F51" s="20" t="inlineStr">
+      <c r="F51" s="26" t="inlineStr">
         <is>
           <t>Nguyen Van Linh, P. Tan Thuan Tay, Q.7</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="20" t="inlineStr">
+      <c r="A52" s="26" t="inlineStr">
         <is>
           <t>Jamona City</t>
         </is>
       </c>
-      <c r="B52" s="20" t="inlineStr">
+      <c r="B52" s="26" t="inlineStr">
         <is>
           <t>Q.7</t>
         </is>
       </c>
-      <c r="C52" s="20" t="n">
+      <c r="C52" s="26" t="n">
         <v>10.737552</v>
       </c>
-      <c r="D52" s="20" t="n">
+      <c r="D52" s="26" t="n">
         <v>106.7374244</v>
       </c>
-      <c r="E52" s="20" t="inlineStr">
+      <c r="E52" s="26" t="inlineStr">
         <is>
           <t>3-3.4 ty</t>
         </is>
       </c>
-      <c r="F52" s="20" t="inlineStr">
+      <c r="F52" s="26" t="inlineStr">
         <is>
           <t>Dao Tri, P. Phu Thuan, Q.7</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="20" t="inlineStr">
+      <c r="A53" s="26" t="inlineStr">
         <is>
           <t>Sunrise City</t>
         </is>
       </c>
-      <c r="B53" s="20" t="inlineStr">
+      <c r="B53" s="26" t="inlineStr">
         <is>
           <t>Q.7</t>
         </is>
       </c>
-      <c r="C53" s="20" t="n">
+      <c r="C53" s="26" t="n">
         <v>10.7437289</v>
       </c>
-      <c r="D53" s="20" t="n">
+      <c r="D53" s="26" t="n">
         <v>106.7011024</v>
       </c>
-      <c r="E53" s="20" t="inlineStr">
+      <c r="E53" s="26" t="inlineStr">
         <is>
           <t>3.3 ty</t>
         </is>
       </c>
-      <c r="F53" s="20" t="inlineStr">
+      <c r="F53" s="26" t="inlineStr">
         <is>
           <t>Nguyen Huu Tho, P. Tan Hung, Q.7</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="20" t="inlineStr">
+      <c r="A54" s="26" t="inlineStr">
         <is>
           <t>The Era Town</t>
         </is>
       </c>
-      <c r="B54" s="20" t="inlineStr">
+      <c r="B54" s="26" t="inlineStr">
         <is>
           <t>Q.7</t>
         </is>
       </c>
-      <c r="C54" s="20" t="n">
+      <c r="C54" s="26" t="n">
         <v>10.7000497</v>
       </c>
-      <c r="D54" s="20" t="n">
+      <c r="D54" s="26" t="n">
         <v>106.7330581</v>
       </c>
-      <c r="E54" s="20" t="inlineStr">
+      <c r="E54" s="26" t="inlineStr">
         <is>
           <t>3.3 ty</t>
         </is>
       </c>
-      <c r="F54" s="20" t="inlineStr">
+      <c r="F54" s="26" t="inlineStr">
         <is>
           <t>P. Phu My, Q.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="26" t="inlineStr">
+        <is>
+          <t>The Origami (Vinhomes Grand Park)</t>
+        </is>
+      </c>
+      <c r="B55" s="26" t="inlineStr">
+        <is>
+          <t>Q.9</t>
+        </is>
+      </c>
+      <c r="C55" s="26" t="n">
+        <v>10.8452092</v>
+      </c>
+      <c r="D55" s="26" t="n">
+        <v>106.8378812</v>
+      </c>
+      <c r="E55" s="26" t="inlineStr">
+        <is>
+          <t>3.3-4.9 ty</t>
+        </is>
+      </c>
+      <c r="F55" s="26" t="inlineStr">
+        <is>
+          <t>Long Binh, TP.Thu Duc (Q.9 cu)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="26" t="inlineStr">
+        <is>
+          <t>Lumiere Boulevard</t>
+        </is>
+      </c>
+      <c r="B56" s="26" t="inlineStr">
+        <is>
+          <t>Q.9</t>
+        </is>
+      </c>
+      <c r="C56" s="26" t="n">
+        <v>10.8394996</v>
+      </c>
+      <c r="D56" s="26" t="n">
+        <v>106.8392649</v>
+      </c>
+      <c r="E56" s="26" t="inlineStr">
+        <is>
+          <t>4.6-4.7 ty</t>
+        </is>
+      </c>
+      <c r="F56" s="26" t="inlineStr">
+        <is>
+          <t>Long Binh, TP.Thu Duc (Q.9 cu)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="26" t="inlineStr">
+        <is>
+          <t>Mizuki Park</t>
+        </is>
+      </c>
+      <c r="B57" s="26" t="inlineStr">
+        <is>
+          <t>Binh Chanh</t>
+        </is>
+      </c>
+      <c r="C57" s="26" t="n">
+        <v>10.7152713</v>
+      </c>
+      <c r="D57" s="26" t="n">
+        <v>106.6634002</v>
+      </c>
+      <c r="E57" s="26" t="inlineStr">
+        <is>
+          <t>3.6-4.2 ty</t>
+        </is>
+      </c>
+      <c r="F57" s="26" t="inlineStr">
+        <is>
+          <t>Nguyen Van Linh, X.Binh Hung, Binh Chanh</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="26" t="inlineStr">
+        <is>
+          <t>Trellia Cove (Mizuki Park)</t>
+        </is>
+      </c>
+      <c r="B58" s="26" t="inlineStr">
+        <is>
+          <t>Binh Chanh</t>
+        </is>
+      </c>
+      <c r="C58" s="26" t="n">
+        <v>10.7128997</v>
+      </c>
+      <c r="D58" s="26" t="n">
+        <v>106.6607158</v>
+      </c>
+      <c r="E58" s="26" t="inlineStr">
+        <is>
+          <t>3.9-5 ty</t>
+        </is>
+      </c>
+      <c r="F58" s="26" t="inlineStr">
+        <is>
+          <t>Nguyen Van Linh, X.Binh Hung, Binh Chanh</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="26" t="inlineStr">
+        <is>
+          <t>Westgate An Gia</t>
+        </is>
+      </c>
+      <c r="B59" s="26" t="inlineStr">
+        <is>
+          <t>Binh Chanh</t>
+        </is>
+      </c>
+      <c r="C59" s="26" t="n">
+        <v>10.6892919</v>
+      </c>
+      <c r="D59" s="26" t="n">
+        <v>106.5857392</v>
+      </c>
+      <c r="E59" s="26" t="inlineStr">
+        <is>
+          <t>3.2-4.5 ty</t>
+        </is>
+      </c>
+      <c r="F59" s="26" t="inlineStr">
+        <is>
+          <t>Nguyen Van Linh, TT.Tan Tuc, Binh Chanh</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="26" t="inlineStr">
+        <is>
+          <t>Sai Gon Mia</t>
+        </is>
+      </c>
+      <c r="B60" s="26" t="inlineStr">
+        <is>
+          <t>Binh Chanh</t>
+        </is>
+      </c>
+      <c r="C60" s="26" t="n">
+        <v>10.7326451</v>
+      </c>
+      <c r="D60" s="26" t="n">
+        <v>106.688988</v>
+      </c>
+      <c r="E60" s="26" t="inlineStr">
+        <is>
+          <t>3.4-5 ty</t>
+        </is>
+      </c>
+      <c r="F60" s="26" t="inlineStr">
+        <is>
+          <t>Trung Son, X.Binh Hung, Binh Chanh</t>
         </is>
       </c>
     </row>

--- a/chung_cu_data.xlsx
+++ b/chung_cu_data.xlsx
@@ -796,7 +796,7 @@
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>Phu 4 Sai Gon Intela</t>
+          <t>Sai Gon Intela</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>Phu 4 Lovera Vista</t>
+          <t>Lovera Vista</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Thanh Investco Babylon</t>
+          <t>Investco Babylon</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Phu 4 Terra Luxury</t>
+          <t>Terra Luxury</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="B35" s="17" t="inlineStr">
         <is>
-          <t>Res 11</t>
+          <t>RES 11</t>
         </is>
       </c>
       <c r="C35" s="17" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Thanh 70</t>
+          <t>70</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Ky Diamond Alnata</t>
+          <t>Diamond Alnata</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Ky Tanibuilding Son Ky 2</t>
+          <t>Tanibuilding Son Ky 2</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="B57" s="10" t="inlineStr">
         <is>
-          <t>Hung 1 Mizuki Park</t>
+          <t>Mizuki Park</t>
         </is>
       </c>
       <c r="C57" s="10" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t>Hung 1 Trellia Cove</t>
+          <t>Trellia Cove</t>
         </is>
       </c>
       <c r="C58" s="10" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Ky 70</t>
+          <t>70</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t>Hung 1 Sai Gon Mia</t>
+          <t>Sai Gon Mia</t>
         </is>
       </c>
       <c r="C66" s="10" t="inlineStr">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>Tho Hoa Fortuna Vuon Lai</t>
+          <t>Fortuna Vuon Lai</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -5997,7 +5997,7 @@
       </c>
       <c r="B81" s="10" t="inlineStr">
         <is>
-          <t>Phu Tay Hqc Plaza</t>
+          <t>HQC Plaza</t>
         </is>
       </c>
       <c r="C81" s="10" t="inlineStr">
@@ -6255,10 +6255,10 @@
         </is>
       </c>
       <c r="C2" s="20" t="n">
-        <v>10.7729244</v>
+        <v>10.7727625</v>
       </c>
       <c r="D2" s="20" t="n">
-        <v>106.6257607</v>
+        <v>106.6267493</v>
       </c>
       <c r="E2" s="20" t="inlineStr">
         <is>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="C3" s="20" t="n">
-        <v>10.8085</v>
+        <v>10.813</v>
       </c>
       <c r="D3" s="20" t="n">
-        <v>106.6588411764706</v>
+        <v>106.65884</v>
       </c>
       <c r="E3" s="20" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
     <row r="4">
       <c r="A4" s="20" t="inlineStr">
         <is>
-          <t>Phu 4 Sai Gon Intela</t>
+          <t>Sai Gon Intela</t>
         </is>
       </c>
       <c r="B4" s="20" t="inlineStr">
@@ -6311,10 +6311,10 @@
         </is>
       </c>
       <c r="C4" s="20" t="n">
-        <v>10.72137647058823</v>
+        <v>10.7243911</v>
       </c>
       <c r="D4" s="20" t="n">
-        <v>106.5953529411765</v>
+        <v>106.5986942</v>
       </c>
       <c r="E4" s="20" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
     <row r="5">
       <c r="A5" s="20" t="inlineStr">
         <is>
-          <t>Phu 4 Lovera Vista</t>
+          <t>Lovera Vista</t>
         </is>
       </c>
       <c r="B5" s="20" t="inlineStr">
@@ -6339,10 +6339,10 @@
         </is>
       </c>
       <c r="C5" s="20" t="n">
-        <v>10.72137647058823</v>
+        <v>10.6919182</v>
       </c>
       <c r="D5" s="20" t="n">
-        <v>106.5953529411765</v>
+        <v>106.6422011</v>
       </c>
       <c r="E5" s="20" t="inlineStr">
         <is>
@@ -6367,10 +6367,10 @@
         </is>
       </c>
       <c r="C6" s="20" t="n">
-        <v>10.72137647058823</v>
+        <v>10.7210978</v>
       </c>
       <c r="D6" s="20" t="n">
-        <v>106.5953529411765</v>
+        <v>106.5926648</v>
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
@@ -6498,7 +6498,7 @@
     <row r="11">
       <c r="A11" s="20" t="inlineStr">
         <is>
-          <t>Thanh Investco Babylon</t>
+          <t>Investco Babylon</t>
         </is>
       </c>
       <c r="B11" s="20" t="inlineStr">
@@ -6507,10 +6507,10 @@
         </is>
       </c>
       <c r="C11" s="20" t="n">
-        <v>10.78728571428571</v>
+        <v>10.7889462</v>
       </c>
       <c r="D11" s="20" t="n">
-        <v>106.6278904761905</v>
+        <v>106.6398628</v>
       </c>
       <c r="E11" s="20" t="inlineStr">
         <is>
@@ -6535,10 +6535,10 @@
         </is>
       </c>
       <c r="C12" s="20" t="n">
-        <v>10.8085</v>
+        <v>10.8109666</v>
       </c>
       <c r="D12" s="20" t="n">
-        <v>106.6588411764706</v>
+        <v>106.6599382</v>
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
@@ -6563,10 +6563,10 @@
         </is>
       </c>
       <c r="C13" s="20" t="n">
-        <v>10.8085</v>
+        <v>10.805859</v>
       </c>
       <c r="D13" s="20" t="n">
-        <v>106.6588411764706</v>
+        <v>106.6594014</v>
       </c>
       <c r="E13" s="20" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
     <row r="14">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>Phu 4 Terra Luxury</t>
+          <t>Terra Luxury</t>
         </is>
       </c>
       <c r="B14" s="20" t="inlineStr">
@@ -6591,10 +6591,10 @@
         </is>
       </c>
       <c r="C14" s="20" t="n">
-        <v>10.72137647058823</v>
+        <v>10.7222143</v>
       </c>
       <c r="D14" s="20" t="n">
-        <v>106.5953529411765</v>
+        <v>106.5979179</v>
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
@@ -6619,10 +6619,10 @@
         </is>
       </c>
       <c r="C15" s="20" t="n">
-        <v>10.72137647058823</v>
+        <v>10.7209096</v>
       </c>
       <c r="D15" s="20" t="n">
-        <v>106.5953529411765</v>
+        <v>106.5998253</v>
       </c>
       <c r="E15" s="20" t="inlineStr">
         <is>
@@ -6647,10 +6647,10 @@
         </is>
       </c>
       <c r="C16" s="20" t="n">
-        <v>10.72137647058823</v>
+        <v>10.7227706</v>
       </c>
       <c r="D16" s="20" t="n">
-        <v>106.5953529411765</v>
+        <v>106.5910702</v>
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
@@ -6731,10 +6731,10 @@
         </is>
       </c>
       <c r="C19" s="20" t="n">
-        <v>10.8085</v>
+        <v>10.8149357</v>
       </c>
       <c r="D19" s="20" t="n">
-        <v>106.6588411764706</v>
+        <v>106.6662829</v>
       </c>
       <c r="E19" s="20" t="inlineStr">
         <is>
@@ -6759,10 +6759,10 @@
         </is>
       </c>
       <c r="C20" s="20" t="n">
-        <v>10.8085</v>
+        <v>10.8080296</v>
       </c>
       <c r="D20" s="20" t="n">
-        <v>106.6588411764706</v>
+        <v>106.6633153</v>
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
@@ -6787,10 +6787,10 @@
         </is>
       </c>
       <c r="C21" s="20" t="n">
-        <v>10.8085</v>
+        <v>10.8040983</v>
       </c>
       <c r="D21" s="20" t="n">
-        <v>106.6588411764706</v>
+        <v>106.6579044</v>
       </c>
       <c r="E21" s="20" t="inlineStr">
         <is>
@@ -6815,10 +6815,10 @@
         </is>
       </c>
       <c r="C22" s="20" t="n">
-        <v>10.8085</v>
+        <v>10.8082178</v>
       </c>
       <c r="D22" s="20" t="n">
-        <v>106.6588411764706</v>
+        <v>106.6561548</v>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
@@ -6843,10 +6843,10 @@
         </is>
       </c>
       <c r="C23" s="20" t="n">
-        <v>10.8085</v>
+        <v>10.7965292</v>
       </c>
       <c r="D23" s="20" t="n">
-        <v>106.6588411764706</v>
+        <v>106.6416853</v>
       </c>
       <c r="E23" s="20" t="inlineStr">
         <is>
@@ -7170,7 +7170,7 @@
     <row r="35">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t>Res 11</t>
+          <t>RES 11</t>
         </is>
       </c>
       <c r="B35" s="20" t="inlineStr">
@@ -7347,10 +7347,10 @@
         </is>
       </c>
       <c r="C41" s="20" t="n">
-        <v>10.8009934</v>
+        <v>10.8025753</v>
       </c>
       <c r="D41" s="20" t="n">
-        <v>106.6129628</v>
+        <v>106.6147837</v>
       </c>
       <c r="E41" s="20" t="inlineStr">
         <is>
@@ -7375,10 +7375,10 @@
         </is>
       </c>
       <c r="C42" s="20" t="n">
-        <v>10.7961217</v>
+        <v>10.7963806</v>
       </c>
       <c r="D42" s="20" t="n">
-        <v>106.6366525</v>
+        <v>106.6370621</v>
       </c>
       <c r="E42" s="20" t="inlineStr">
         <is>
@@ -7403,10 +7403,10 @@
         </is>
       </c>
       <c r="C43" s="20" t="n">
-        <v>10.7742711</v>
+        <v>10.7736303</v>
       </c>
       <c r="D43" s="20" t="n">
-        <v>106.6357158</v>
+        <v>106.6356264</v>
       </c>
       <c r="E43" s="20" t="inlineStr">
         <is>
@@ -7431,10 +7431,10 @@
         </is>
       </c>
       <c r="C44" s="20" t="n">
-        <v>10.7776469</v>
+        <v>10.7776072</v>
       </c>
       <c r="D44" s="20" t="n">
-        <v>106.6369297</v>
+        <v>106.63697</v>
       </c>
       <c r="E44" s="20" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
     <row r="46">
       <c r="A46" s="20" t="inlineStr">
         <is>
-          <t>Thanh 70</t>
+          <t>70</t>
         </is>
       </c>
       <c r="B46" s="20" t="inlineStr">
@@ -7487,10 +7487,10 @@
         </is>
       </c>
       <c r="C46" s="20" t="n">
-        <v>10.78728571428571</v>
+        <v>10.7838094</v>
       </c>
       <c r="D46" s="20" t="n">
-        <v>106.6278904761905</v>
+        <v>106.6369877</v>
       </c>
       <c r="E46" s="20" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
     <row r="47">
       <c r="A47" s="20" t="inlineStr">
         <is>
-          <t>Ky Diamond Alnata</t>
+          <t>Diamond Alnata</t>
         </is>
       </c>
       <c r="B47" s="20" t="inlineStr">
@@ -7515,10 +7515,10 @@
         </is>
       </c>
       <c r="C47" s="20" t="n">
-        <v>10.78728571428571</v>
+        <v>10.8028969</v>
       </c>
       <c r="D47" s="20" t="n">
-        <v>106.6278904761905</v>
+        <v>106.6155408</v>
       </c>
       <c r="E47" s="20" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
     <row r="48">
       <c r="A48" s="20" t="inlineStr">
         <is>
-          <t>Ky Tanibuilding Son Ky 2</t>
+          <t>Tanibuilding Son Ky 2</t>
         </is>
       </c>
       <c r="B48" s="20" t="inlineStr">
@@ -7543,10 +7543,10 @@
         </is>
       </c>
       <c r="C48" s="20" t="n">
-        <v>10.78728571428571</v>
+        <v>10.7832356</v>
       </c>
       <c r="D48" s="20" t="n">
-        <v>106.6278904761905</v>
+        <v>106.6259375</v>
       </c>
       <c r="E48" s="20" t="inlineStr">
         <is>
@@ -7571,10 +7571,10 @@
         </is>
       </c>
       <c r="C49" s="20" t="n">
-        <v>10.8085</v>
+        <v>10.80625</v>
       </c>
       <c r="D49" s="20" t="n">
-        <v>106.6588411764706</v>
+        <v>106.6549429</v>
       </c>
       <c r="E49" s="20" t="inlineStr">
         <is>
@@ -7599,10 +7599,10 @@
         </is>
       </c>
       <c r="C50" s="20" t="n">
-        <v>10.8085</v>
+        <v>10.8053756</v>
       </c>
       <c r="D50" s="20" t="n">
-        <v>106.6588411764706</v>
+        <v>106.6469127</v>
       </c>
       <c r="E50" s="20" t="inlineStr">
         <is>
@@ -7627,10 +7627,10 @@
         </is>
       </c>
       <c r="C51" s="20" t="n">
-        <v>10.72137647058823</v>
+        <v>10.72003</v>
       </c>
       <c r="D51" s="20" t="n">
-        <v>106.5953529411765</v>
+        <v>106.5976883</v>
       </c>
       <c r="E51" s="20" t="inlineStr">
         <is>
@@ -7655,10 +7655,10 @@
         </is>
       </c>
       <c r="C52" s="20" t="n">
-        <v>10.72137647058823</v>
+        <v>10.7177394</v>
       </c>
       <c r="D52" s="20" t="n">
-        <v>106.5953529411765</v>
+        <v>106.597995</v>
       </c>
       <c r="E52" s="20" t="inlineStr">
         <is>
@@ -7683,10 +7683,10 @@
         </is>
       </c>
       <c r="C53" s="20" t="n">
-        <v>10.72137647058823</v>
+        <v>10.718739</v>
       </c>
       <c r="D53" s="20" t="n">
-        <v>106.5953529411765</v>
+        <v>106.5959114</v>
       </c>
       <c r="E53" s="20" t="inlineStr">
         <is>
@@ -7711,10 +7711,10 @@
         </is>
       </c>
       <c r="C54" s="20" t="n">
-        <v>10.72137647058823</v>
+        <v>10.7191957</v>
       </c>
       <c r="D54" s="20" t="n">
-        <v>106.5953529411765</v>
+        <v>106.593763</v>
       </c>
       <c r="E54" s="20" t="inlineStr">
         <is>
@@ -7786,7 +7786,7 @@
     <row r="57">
       <c r="A57" s="20" t="inlineStr">
         <is>
-          <t>Hung 1 Mizuki Park</t>
+          <t>Mizuki Park</t>
         </is>
       </c>
       <c r="B57" s="20" t="inlineStr">
@@ -7795,10 +7795,10 @@
         </is>
       </c>
       <c r="C57" s="20" t="n">
-        <v>10.72137647058823</v>
+        <v>10.7143025</v>
       </c>
       <c r="D57" s="20" t="n">
-        <v>106.5953529411765</v>
+        <v>106.6624699</v>
       </c>
       <c r="E57" s="20" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
     <row r="58">
       <c r="A58" s="20" t="inlineStr">
         <is>
-          <t>Hung 1 Trellia Cove</t>
+          <t>Trellia Cove</t>
         </is>
       </c>
       <c r="B58" s="20" t="inlineStr">
@@ -7823,10 +7823,10 @@
         </is>
       </c>
       <c r="C58" s="20" t="n">
-        <v>10.72137647058823</v>
+        <v>10.7139913</v>
       </c>
       <c r="D58" s="20" t="n">
-        <v>106.5953529411765</v>
+        <v>106.6623822</v>
       </c>
       <c r="E58" s="20" t="inlineStr">
         <is>
@@ -7851,10 +7851,10 @@
         </is>
       </c>
       <c r="C59" s="20" t="n">
-        <v>10.8022839</v>
+        <v>10.8021735</v>
       </c>
       <c r="D59" s="20" t="n">
-        <v>106.6158704</v>
+        <v>106.615341</v>
       </c>
       <c r="E59" s="20" t="inlineStr">
         <is>
@@ -7879,10 +7879,10 @@
         </is>
       </c>
       <c r="C60" s="20" t="n">
-        <v>10.8053889</v>
+        <v>10.8019565</v>
       </c>
       <c r="D60" s="20" t="n">
-        <v>106.6148485</v>
+        <v>106.6146748</v>
       </c>
       <c r="E60" s="20" t="inlineStr">
         <is>
@@ -7907,10 +7907,10 @@
         </is>
       </c>
       <c r="C61" s="20" t="n">
-        <v>10.8028716</v>
+        <v>10.8026957</v>
       </c>
       <c r="D61" s="20" t="n">
-        <v>106.615476</v>
+        <v>106.6147149</v>
       </c>
       <c r="E61" s="20" t="inlineStr">
         <is>
@@ -7935,10 +7935,10 @@
         </is>
       </c>
       <c r="C62" s="20" t="n">
-        <v>10.7896245</v>
+        <v>10.7895653</v>
       </c>
       <c r="D62" s="20" t="n">
-        <v>106.6394598</v>
+        <v>106.6393649</v>
       </c>
       <c r="E62" s="20" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
     <row r="63">
       <c r="A63" s="20" t="inlineStr">
         <is>
-          <t>Ky 70</t>
+          <t>70</t>
         </is>
       </c>
       <c r="B63" s="20" t="inlineStr">
@@ -7963,10 +7963,10 @@
         </is>
       </c>
       <c r="C63" s="20" t="n">
-        <v>10.78728571428571</v>
+        <v>10.7838094</v>
       </c>
       <c r="D63" s="20" t="n">
-        <v>106.6278904761905</v>
+        <v>106.6369877</v>
       </c>
       <c r="E63" s="20" t="inlineStr">
         <is>
@@ -7991,10 +7991,10 @@
         </is>
       </c>
       <c r="C64" s="20" t="n">
-        <v>10.8085</v>
+        <v>10.8062382</v>
       </c>
       <c r="D64" s="20" t="n">
-        <v>106.6588411764706</v>
+        <v>106.6662711</v>
       </c>
       <c r="E64" s="20" t="inlineStr">
         <is>
@@ -8019,10 +8019,10 @@
         </is>
       </c>
       <c r="C65" s="20" t="n">
-        <v>10.8085</v>
+        <v>10.8000536</v>
       </c>
       <c r="D65" s="20" t="n">
-        <v>106.6588411764706</v>
+        <v>106.6651001</v>
       </c>
       <c r="E65" s="20" t="inlineStr">
         <is>
@@ -8038,7 +8038,7 @@
     <row r="66">
       <c r="A66" s="20" t="inlineStr">
         <is>
-          <t>Hung 1 Sai Gon Mia</t>
+          <t>Sai Gon Mia</t>
         </is>
       </c>
       <c r="B66" s="20" t="inlineStr">
@@ -8047,10 +8047,10 @@
         </is>
       </c>
       <c r="C66" s="20" t="n">
-        <v>10.72137647058823</v>
+        <v>10.7231867</v>
       </c>
       <c r="D66" s="20" t="n">
-        <v>106.5953529411765</v>
+        <v>106.5933435</v>
       </c>
       <c r="E66" s="20" t="inlineStr">
         <is>
@@ -8243,10 +8243,10 @@
         </is>
       </c>
       <c r="C73" s="20" t="n">
-        <v>10.803599</v>
+        <v>10.8025777</v>
       </c>
       <c r="D73" s="20" t="n">
-        <v>106.6188954</v>
+        <v>106.614893</v>
       </c>
       <c r="E73" s="20" t="inlineStr">
         <is>
@@ -8271,10 +8271,10 @@
         </is>
       </c>
       <c r="C74" s="20" t="n">
-        <v>10.803923</v>
+        <v>10.8020962</v>
       </c>
       <c r="D74" s="20" t="n">
-        <v>106.6152349</v>
+        <v>106.614808</v>
       </c>
       <c r="E74" s="20" t="inlineStr">
         <is>
@@ -8299,10 +8299,10 @@
         </is>
       </c>
       <c r="C75" s="20" t="n">
-        <v>10.8020447</v>
+        <v>10.8023127</v>
       </c>
       <c r="D75" s="20" t="n">
-        <v>106.6145601</v>
+        <v>106.6142934</v>
       </c>
       <c r="E75" s="20" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
     <row r="76">
       <c r="A76" s="20" t="inlineStr">
         <is>
-          <t>Tho Hoa Fortuna Vuon Lai</t>
+          <t>Fortuna Vuon Lai</t>
         </is>
       </c>
       <c r="B76" s="20" t="inlineStr">
@@ -8327,10 +8327,10 @@
         </is>
       </c>
       <c r="C76" s="20" t="n">
-        <v>10.78728571428571</v>
+        <v>10.7883906</v>
       </c>
       <c r="D76" s="20" t="n">
-        <v>106.6278904761905</v>
+        <v>106.6244178</v>
       </c>
       <c r="E76" s="20" t="inlineStr">
         <is>
@@ -8355,10 +8355,10 @@
         </is>
       </c>
       <c r="C77" s="20" t="n">
-        <v>10.78728571428571</v>
+        <v>10.7900957</v>
       </c>
       <c r="D77" s="20" t="n">
-        <v>106.6278904761905</v>
+        <v>106.6243718</v>
       </c>
       <c r="E77" s="20" t="inlineStr">
         <is>
@@ -8383,10 +8383,10 @@
         </is>
       </c>
       <c r="C78" s="20" t="n">
-        <v>10.8085</v>
+        <v>10.8115758</v>
       </c>
       <c r="D78" s="20" t="n">
-        <v>106.6588411764706</v>
+        <v>106.669586</v>
       </c>
       <c r="E78" s="20" t="inlineStr">
         <is>
@@ -8411,10 +8411,10 @@
         </is>
       </c>
       <c r="C79" s="20" t="n">
-        <v>10.8085</v>
+        <v>10.7909</v>
       </c>
       <c r="D79" s="20" t="n">
-        <v>106.6588411764706</v>
+        <v>106.6457395</v>
       </c>
       <c r="E79" s="20" t="inlineStr">
         <is>
@@ -8439,10 +8439,10 @@
         </is>
       </c>
       <c r="C80" s="20" t="n">
-        <v>10.8085</v>
+        <v>10.812611</v>
       </c>
       <c r="D80" s="20" t="n">
-        <v>106.6588411764706</v>
+        <v>106.6570097</v>
       </c>
       <c r="E80" s="20" t="inlineStr">
         <is>
@@ -8458,7 +8458,7 @@
     <row r="81">
       <c r="A81" s="20" t="inlineStr">
         <is>
-          <t>Phu Tay Hqc Plaza</t>
+          <t>HQC Plaza</t>
         </is>
       </c>
       <c r="B81" s="20" t="inlineStr">
@@ -8467,10 +8467,10 @@
         </is>
       </c>
       <c r="C81" s="20" t="n">
-        <v>10.72137647058823</v>
+        <v>10.6945666</v>
       </c>
       <c r="D81" s="20" t="n">
-        <v>106.5953529411765</v>
+        <v>106.6063942</v>
       </c>
       <c r="E81" s="20" t="inlineStr">
         <is>
@@ -8495,10 +8495,10 @@
         </is>
       </c>
       <c r="C82" s="20" t="n">
-        <v>10.72137647058823</v>
+        <v>10.725491</v>
       </c>
       <c r="D82" s="20" t="n">
-        <v>106.5953529411765</v>
+        <v>106.5935197</v>
       </c>
       <c r="E82" s="20" t="inlineStr">
         <is>

--- a/chung_cu_data.xlsx
+++ b/chung_cu_data.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Toa Do (Map)" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Danh Sach BDS'!$A$1:$Q$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Danh Sach BDS'!$A$1:$Q$119</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -42,7 +42,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -99,8 +99,38 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00E8F4FD"/>
+        <bgColor rgb="00E8F4FD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3E0"/>
+        <bgColor rgb="00FFF3E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFDE7"/>
+        <bgColor rgb="00FFFDE7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E0F2F1"/>
+        <bgColor rgb="00E0F2F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFCDD2"/>
         <bgColor rgb="00FFCDD2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3E5F5"/>
+        <bgColor rgb="00F3E5F5"/>
       </patternFill>
     </fill>
   </fills>
@@ -130,7 +160,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -166,9 +196,34 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -535,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:Q119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4226,1887 +4281,4336 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="12" t="n">
+      <c r="A55" s="19" t="n">
         <v>54</v>
       </c>
-      <c r="B55" s="13" t="inlineStr">
+      <c r="B55" s="20" t="inlineStr">
+        <is>
+          <t>Topaz Elite</t>
+        </is>
+      </c>
+      <c r="C55" s="20" t="inlineStr">
+        <is>
+          <t>Chung cu</t>
+        </is>
+      </c>
+      <c r="D55" s="20" t="inlineStr">
+        <is>
+          <t>3.2-4.8 ty</t>
+        </is>
+      </c>
+      <c r="E55" s="19" t="inlineStr">
+        <is>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="F55" s="14" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="G55" s="19" t="inlineStr"/>
+      <c r="H55" s="20" t="inlineStr"/>
+      <c r="I55" s="20" t="inlineStr">
+        <is>
+          <t>60-92m2</t>
+        </is>
+      </c>
+      <c r="J55" s="19" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="K55" s="19" t="inlineStr"/>
+      <c r="L55" s="20" t="inlineStr">
+        <is>
+          <t>Cao Lo, P.4, Q.8</t>
+        </is>
+      </c>
+      <c r="M55" s="20" t="inlineStr">
+        <is>
+          <t>Q.8</t>
+        </is>
+      </c>
+      <c r="N55" s="20" t="inlineStr">
+        <is>
+          <t>Van Thai Land, 3 block</t>
+        </is>
+      </c>
+      <c r="O55" s="19" t="inlineStr"/>
+      <c r="P55" s="20" t="inlineStr"/>
+      <c r="Q55" s="21" t="inlineStr">
+        <is>
+          <t>Xem BDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="19" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="20" t="inlineStr">
+        <is>
+          <t>Topaz City</t>
+        </is>
+      </c>
+      <c r="C56" s="20" t="inlineStr">
+        <is>
+          <t>Chung cu</t>
+        </is>
+      </c>
+      <c r="D56" s="20" t="inlineStr">
+        <is>
+          <t>3.0-4.5 ty</t>
+        </is>
+      </c>
+      <c r="E56" s="19" t="inlineStr">
+        <is>
+          <t>47.5</t>
+        </is>
+      </c>
+      <c r="F56" s="14" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="G56" s="19" t="inlineStr"/>
+      <c r="H56" s="20" t="inlineStr"/>
+      <c r="I56" s="20" t="inlineStr">
+        <is>
+          <t>63-95m2</t>
+        </is>
+      </c>
+      <c r="J56" s="19" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="K56" s="19" t="inlineStr"/>
+      <c r="L56" s="20" t="inlineStr">
+        <is>
+          <t>Ta Quang Buu, P.5, Q.8</t>
+        </is>
+      </c>
+      <c r="M56" s="20" t="inlineStr">
+        <is>
+          <t>Q.8</t>
+        </is>
+      </c>
+      <c r="N56" s="20" t="inlineStr">
+        <is>
+          <t>Van Thai Land</t>
+        </is>
+      </c>
+      <c r="O56" s="19" t="inlineStr"/>
+      <c r="P56" s="20" t="inlineStr"/>
+      <c r="Q56" s="21" t="inlineStr">
+        <is>
+          <t>Xem BDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="19" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="20" t="inlineStr">
+        <is>
+          <t>The Pegasuite</t>
+        </is>
+      </c>
+      <c r="C57" s="20" t="inlineStr">
+        <is>
+          <t>Chung cu</t>
+        </is>
+      </c>
+      <c r="D57" s="20" t="inlineStr">
+        <is>
+          <t>3.0-4.5 ty</t>
+        </is>
+      </c>
+      <c r="E57" s="19" t="inlineStr">
+        <is>
+          <t>48.1</t>
+        </is>
+      </c>
+      <c r="F57" s="14" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="G57" s="19" t="inlineStr"/>
+      <c r="H57" s="20" t="inlineStr"/>
+      <c r="I57" s="20" t="inlineStr">
+        <is>
+          <t>60-96m2</t>
+        </is>
+      </c>
+      <c r="J57" s="19" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="K57" s="19" t="inlineStr"/>
+      <c r="L57" s="20" t="inlineStr">
+        <is>
+          <t>Ta Quang Buu, P.6, Q.8</t>
+        </is>
+      </c>
+      <c r="M57" s="20" t="inlineStr">
+        <is>
+          <t>Q.8</t>
+        </is>
+      </c>
+      <c r="N57" s="20" t="inlineStr">
+        <is>
+          <t>Phu Gia, view song</t>
+        </is>
+      </c>
+      <c r="O57" s="19" t="inlineStr"/>
+      <c r="P57" s="20" t="inlineStr"/>
+      <c r="Q57" s="21" t="inlineStr">
+        <is>
+          <t>Xem BDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="19" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="20" t="inlineStr">
+        <is>
+          <t>The Pegasuite 2</t>
+        </is>
+      </c>
+      <c r="C58" s="20" t="inlineStr">
+        <is>
+          <t>Chung cu</t>
+        </is>
+      </c>
+      <c r="D58" s="20" t="inlineStr">
+        <is>
+          <t>3.2-5.0 ty</t>
+        </is>
+      </c>
+      <c r="E58" s="19" t="inlineStr">
+        <is>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="F58" s="14" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="G58" s="19" t="inlineStr"/>
+      <c r="H58" s="20" t="inlineStr"/>
+      <c r="I58" s="20" t="inlineStr">
+        <is>
+          <t>60-96m2</t>
+        </is>
+      </c>
+      <c r="J58" s="19" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="K58" s="19" t="inlineStr"/>
+      <c r="L58" s="20" t="inlineStr">
+        <is>
+          <t>Ta Quang Buu, P.6, Q.8</t>
+        </is>
+      </c>
+      <c r="M58" s="20" t="inlineStr">
+        <is>
+          <t>Q.8</t>
+        </is>
+      </c>
+      <c r="N58" s="20" t="inlineStr">
+        <is>
+          <t>Phu Gia, moi hon</t>
+        </is>
+      </c>
+      <c r="O58" s="19" t="inlineStr"/>
+      <c r="P58" s="20" t="inlineStr"/>
+      <c r="Q58" s="21" t="inlineStr">
+        <is>
+          <t>Xem BDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="19" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="20" t="inlineStr">
+        <is>
+          <t>D-Aqua</t>
+        </is>
+      </c>
+      <c r="C59" s="20" t="inlineStr">
+        <is>
+          <t>Chung cu</t>
+        </is>
+      </c>
+      <c r="D59" s="20" t="inlineStr">
+        <is>
+          <t>3.5-5.0 ty</t>
+        </is>
+      </c>
+      <c r="E59" s="19" t="inlineStr">
+        <is>
+          <t>62.0</t>
+        </is>
+      </c>
+      <c r="F59" s="14" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="G59" s="19" t="inlineStr"/>
+      <c r="H59" s="20" t="inlineStr"/>
+      <c r="I59" s="20" t="inlineStr">
+        <is>
+          <t>51-86m2</t>
+        </is>
+      </c>
+      <c r="J59" s="19" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="K59" s="19" t="inlineStr"/>
+      <c r="L59" s="20" t="inlineStr">
+        <is>
+          <t>Ben Binh Dong, P.14, Q.8</t>
+        </is>
+      </c>
+      <c r="M59" s="20" t="inlineStr">
+        <is>
+          <t>Q.8</t>
+        </is>
+      </c>
+      <c r="N59" s="20" t="inlineStr">
+        <is>
+          <t>DHA Corp, view kenh</t>
+        </is>
+      </c>
+      <c r="O59" s="19" t="inlineStr"/>
+      <c r="P59" s="20" t="inlineStr"/>
+      <c r="Q59" s="21" t="inlineStr">
+        <is>
+          <t>Xem BDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="19" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="20" t="inlineStr">
+        <is>
+          <t>Aurora Residences</t>
+        </is>
+      </c>
+      <c r="C60" s="20" t="inlineStr">
+        <is>
+          <t>Chung cu</t>
+        </is>
+      </c>
+      <c r="D60" s="20" t="inlineStr">
+        <is>
+          <t>3.0-4.5 ty</t>
+        </is>
+      </c>
+      <c r="E60" s="19" t="inlineStr">
+        <is>
+          <t>52.8</t>
+        </is>
+      </c>
+      <c r="F60" s="14" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="G60" s="19" t="inlineStr"/>
+      <c r="H60" s="20" t="inlineStr"/>
+      <c r="I60" s="20" t="inlineStr">
+        <is>
+          <t>56-86m2</t>
+        </is>
+      </c>
+      <c r="J60" s="19" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="K60" s="19" t="inlineStr"/>
+      <c r="L60" s="20" t="inlineStr">
+        <is>
+          <t>Ben Binh Dong, P.13, Q.8</t>
+        </is>
+      </c>
+      <c r="M60" s="20" t="inlineStr">
+        <is>
+          <t>Q.8</t>
+        </is>
+      </c>
+      <c r="N60" s="20" t="inlineStr">
+        <is>
+          <t>view kenh</t>
+        </is>
+      </c>
+      <c r="O60" s="19" t="inlineStr"/>
+      <c r="P60" s="20" t="inlineStr"/>
+      <c r="Q60" s="21" t="inlineStr">
+        <is>
+          <t>Xem BDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="20" t="inlineStr">
+        <is>
+          <t>Green River</t>
+        </is>
+      </c>
+      <c r="C61" s="20" t="inlineStr">
+        <is>
+          <t>Chung cu</t>
+        </is>
+      </c>
+      <c r="D61" s="20" t="inlineStr">
+        <is>
+          <t>3.0-3.8 ty</t>
+        </is>
+      </c>
+      <c r="E61" s="19" t="inlineStr">
+        <is>
+          <t>50.8</t>
+        </is>
+      </c>
+      <c r="F61" s="14" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="G61" s="19" t="inlineStr"/>
+      <c r="H61" s="20" t="inlineStr"/>
+      <c r="I61" s="20" t="inlineStr">
+        <is>
+          <t>56-78m2</t>
+        </is>
+      </c>
+      <c r="J61" s="19" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="K61" s="19" t="inlineStr"/>
+      <c r="L61" s="20" t="inlineStr">
+        <is>
+          <t>Pham The Hien, P.7, Q.8</t>
+        </is>
+      </c>
+      <c r="M61" s="20" t="inlineStr">
+        <is>
+          <t>Q.8</t>
+        </is>
+      </c>
+      <c r="N61" s="20" t="inlineStr">
+        <is>
+          <t>view song, gia tot</t>
+        </is>
+      </c>
+      <c r="O61" s="19" t="inlineStr"/>
+      <c r="P61" s="20" t="inlineStr"/>
+      <c r="Q61" s="21" t="inlineStr">
+        <is>
+          <t>Xem BDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="19" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="20" t="inlineStr">
+        <is>
+          <t>Tara Residence</t>
+        </is>
+      </c>
+      <c r="C62" s="20" t="inlineStr">
+        <is>
+          <t>Chung cu</t>
+        </is>
+      </c>
+      <c r="D62" s="20" t="inlineStr">
+        <is>
+          <t>3.0-4.2 ty</t>
+        </is>
+      </c>
+      <c r="E62" s="19" t="inlineStr">
+        <is>
+          <t>47.7</t>
+        </is>
+      </c>
+      <c r="F62" s="14" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="G62" s="19" t="inlineStr"/>
+      <c r="H62" s="20" t="inlineStr"/>
+      <c r="I62" s="20" t="inlineStr">
+        <is>
+          <t>56-95m2</t>
+        </is>
+      </c>
+      <c r="J62" s="19" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="K62" s="19" t="inlineStr"/>
+      <c r="L62" s="20" t="inlineStr">
+        <is>
+          <t>Ta Quang Buu, P.6, Q.8</t>
+        </is>
+      </c>
+      <c r="M62" s="20" t="inlineStr">
+        <is>
+          <t>Q.8</t>
+        </is>
+      </c>
+      <c r="N62" s="20" t="inlineStr">
+        <is>
+          <t>gan Pegasuite</t>
+        </is>
+      </c>
+      <c r="O62" s="19" t="inlineStr"/>
+      <c r="P62" s="20" t="inlineStr"/>
+      <c r="Q62" s="21" t="inlineStr">
+        <is>
+          <t>Xem BDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="19" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="20" t="inlineStr">
+        <is>
+          <t>Saigon Skyview</t>
+        </is>
+      </c>
+      <c r="C63" s="20" t="inlineStr">
+        <is>
+          <t>Chung cu</t>
+        </is>
+      </c>
+      <c r="D63" s="20" t="inlineStr">
+        <is>
+          <t>3.0-4.5 ty</t>
+        </is>
+      </c>
+      <c r="E63" s="19" t="inlineStr">
+        <is>
+          <t>48.7</t>
+        </is>
+      </c>
+      <c r="F63" s="14" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="G63" s="19" t="inlineStr"/>
+      <c r="H63" s="20" t="inlineStr"/>
+      <c r="I63" s="20" t="inlineStr">
+        <is>
+          <t>62-92m2</t>
+        </is>
+      </c>
+      <c r="J63" s="19" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="K63" s="19" t="inlineStr"/>
+      <c r="L63" s="20" t="inlineStr">
+        <is>
+          <t>Ta Quang Buu, P.6, Q.8</t>
+        </is>
+      </c>
+      <c r="M63" s="20" t="inlineStr">
+        <is>
+          <t>Q.8</t>
+        </is>
+      </c>
+      <c r="N63" s="20" t="inlineStr">
+        <is>
+          <t>view dep</t>
+        </is>
+      </c>
+      <c r="O63" s="19" t="inlineStr"/>
+      <c r="P63" s="20" t="inlineStr"/>
+      <c r="Q63" s="21" t="inlineStr">
+        <is>
+          <t>Xem BDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="19" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="20" t="inlineStr">
+        <is>
+          <t>Central Premium</t>
+        </is>
+      </c>
+      <c r="C64" s="20" t="inlineStr">
+        <is>
+          <t>Chung cu</t>
+        </is>
+      </c>
+      <c r="D64" s="20" t="inlineStr">
+        <is>
+          <t>3.5-5.0 ty</t>
+        </is>
+      </c>
+      <c r="E64" s="19" t="inlineStr">
+        <is>
+          <t>54.5</t>
+        </is>
+      </c>
+      <c r="F64" s="14" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="G64" s="19" t="inlineStr"/>
+      <c r="H64" s="20" t="inlineStr"/>
+      <c r="I64" s="20" t="inlineStr">
+        <is>
+          <t>58-98m2</t>
+        </is>
+      </c>
+      <c r="J64" s="19" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="K64" s="19" t="inlineStr"/>
+      <c r="L64" s="20" t="inlineStr">
+        <is>
+          <t>Ta Quang Buu, P.1, Q.8</t>
+        </is>
+      </c>
+      <c r="M64" s="20" t="inlineStr">
+        <is>
+          <t>Q.8</t>
+        </is>
+      </c>
+      <c r="N64" s="20" t="inlineStr">
+        <is>
+          <t>gan cau NTP</t>
+        </is>
+      </c>
+      <c r="O64" s="19" t="inlineStr"/>
+      <c r="P64" s="20" t="inlineStr"/>
+      <c r="Q64" s="21" t="inlineStr">
+        <is>
+          <t>Xem BDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="19" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="20" t="inlineStr">
+        <is>
+          <t>CC Bong Sao</t>
+        </is>
+      </c>
+      <c r="C65" s="20" t="inlineStr">
+        <is>
+          <t>Chung cu</t>
+        </is>
+      </c>
+      <c r="D65" s="20" t="inlineStr">
+        <is>
+          <t>3.0-3.5 ty</t>
+        </is>
+      </c>
+      <c r="E65" s="19" t="inlineStr">
+        <is>
+          <t>50.8</t>
+        </is>
+      </c>
+      <c r="F65" s="14" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="G65" s="19" t="inlineStr"/>
+      <c r="H65" s="20" t="inlineStr"/>
+      <c r="I65" s="20" t="inlineStr">
+        <is>
+          <t>60-68m2</t>
+        </is>
+      </c>
+      <c r="J65" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K65" s="19" t="inlineStr"/>
+      <c r="L65" s="20" t="inlineStr">
+        <is>
+          <t>Ta Quang Buu, P.5, Q.8</t>
+        </is>
+      </c>
+      <c r="M65" s="20" t="inlineStr">
+        <is>
+          <t>Q.8</t>
+        </is>
+      </c>
+      <c r="N65" s="20" t="inlineStr">
+        <is>
+          <t>gia re, da ban giao</t>
+        </is>
+      </c>
+      <c r="O65" s="19" t="inlineStr"/>
+      <c r="P65" s="20" t="inlineStr"/>
+      <c r="Q65" s="21" t="inlineStr">
+        <is>
+          <t>Xem BDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="19" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="20" t="inlineStr">
+        <is>
+          <t>Diamond Riverside</t>
+        </is>
+      </c>
+      <c r="C66" s="20" t="inlineStr">
+        <is>
+          <t>Chung cu</t>
+        </is>
+      </c>
+      <c r="D66" s="20" t="inlineStr">
+        <is>
+          <t>3.0-4.0 ty</t>
+        </is>
+      </c>
+      <c r="E66" s="19" t="inlineStr">
+        <is>
+          <t>51.1</t>
+        </is>
+      </c>
+      <c r="F66" s="14" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="G66" s="19" t="inlineStr"/>
+      <c r="H66" s="20" t="inlineStr"/>
+      <c r="I66" s="20" t="inlineStr">
+        <is>
+          <t>55-82m2</t>
+        </is>
+      </c>
+      <c r="J66" s="19" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="K66" s="19" t="inlineStr"/>
+      <c r="L66" s="20" t="inlineStr">
+        <is>
+          <t>Vo Van Kiet, P.16, Q.8</t>
+        </is>
+      </c>
+      <c r="M66" s="20" t="inlineStr">
+        <is>
+          <t>Q.8</t>
+        </is>
+      </c>
+      <c r="N66" s="20" t="inlineStr">
+        <is>
+          <t>City Gate 2</t>
+        </is>
+      </c>
+      <c r="O66" s="19" t="inlineStr"/>
+      <c r="P66" s="20" t="inlineStr"/>
+      <c r="Q66" s="21" t="inlineStr">
+        <is>
+          <t>Xem BDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="19" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="20" t="inlineStr">
+        <is>
+          <t>Conic Riverside</t>
+        </is>
+      </c>
+      <c r="C67" s="20" t="inlineStr">
+        <is>
+          <t>Chung cu</t>
+        </is>
+      </c>
+      <c r="D67" s="20" t="inlineStr">
+        <is>
+          <t>3.0-4.2 ty</t>
+        </is>
+      </c>
+      <c r="E67" s="19" t="inlineStr">
+        <is>
+          <t>56.2</t>
+        </is>
+      </c>
+      <c r="F67" s="14" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="G67" s="19" t="inlineStr"/>
+      <c r="H67" s="20" t="inlineStr"/>
+      <c r="I67" s="20" t="inlineStr">
+        <is>
+          <t>50-78m2</t>
+        </is>
+      </c>
+      <c r="J67" s="19" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="K67" s="19" t="inlineStr"/>
+      <c r="L67" s="20" t="inlineStr">
+        <is>
+          <t>Ta Quang Buu, P.7, Q.8</t>
+        </is>
+      </c>
+      <c r="M67" s="20" t="inlineStr">
+        <is>
+          <t>Q.8</t>
+        </is>
+      </c>
+      <c r="N67" s="20" t="inlineStr">
+        <is>
+          <t>view song, compound</t>
+        </is>
+      </c>
+      <c r="O67" s="19" t="inlineStr"/>
+      <c r="P67" s="20" t="inlineStr"/>
+      <c r="Q67" s="21" t="inlineStr">
+        <is>
+          <t>Xem BDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="22" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="23" t="inlineStr">
+        <is>
+          <t>Asiana Capella</t>
+        </is>
+      </c>
+      <c r="C68" s="23" t="inlineStr">
+        <is>
+          <t>Chung cu</t>
+        </is>
+      </c>
+      <c r="D68" s="23" t="inlineStr">
+        <is>
+          <t>3.5-5.0 ty</t>
+        </is>
+      </c>
+      <c r="E68" s="22" t="inlineStr">
+        <is>
+          <t>59.9</t>
+        </is>
+      </c>
+      <c r="F68" s="14" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="G68" s="22" t="inlineStr"/>
+      <c r="H68" s="23" t="inlineStr"/>
+      <c r="I68" s="23" t="inlineStr">
+        <is>
+          <t>56-86m2</t>
+        </is>
+      </c>
+      <c r="J68" s="22" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="K68" s="22" t="inlineStr"/>
+      <c r="L68" s="23" t="inlineStr">
+        <is>
+          <t>Tran Van Kieu, P.10, Q.6</t>
+        </is>
+      </c>
+      <c r="M68" s="23" t="inlineStr">
+        <is>
+          <t>Q.6</t>
+        </is>
+      </c>
+      <c r="N68" s="23" t="inlineStr">
+        <is>
+          <t>Gotec Land</t>
+        </is>
+      </c>
+      <c r="O68" s="22" t="inlineStr"/>
+      <c r="P68" s="23" t="inlineStr"/>
+      <c r="Q68" s="24" t="inlineStr">
+        <is>
+          <t>Xem BDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="22" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="23" t="inlineStr">
+        <is>
+          <t>Him Lam Cho Lon</t>
+        </is>
+      </c>
+      <c r="C69" s="23" t="inlineStr">
+        <is>
+          <t>Chung cu</t>
+        </is>
+      </c>
+      <c r="D69" s="23" t="inlineStr">
+        <is>
+          <t>3.0-4.5 ty</t>
+        </is>
+      </c>
+      <c r="E69" s="22" t="inlineStr">
+        <is>
+          <t>44.9</t>
+        </is>
+      </c>
+      <c r="F69" s="14" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="G69" s="22" t="inlineStr"/>
+      <c r="H69" s="23" t="inlineStr"/>
+      <c r="I69" s="23" t="inlineStr">
+        <is>
+          <t>65-102m2</t>
+        </is>
+      </c>
+      <c r="J69" s="22" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="K69" s="22" t="inlineStr"/>
+      <c r="L69" s="23" t="inlineStr">
+        <is>
+          <t>Dai lo Dong Tay, P.11, Q.6</t>
+        </is>
+      </c>
+      <c r="M69" s="23" t="inlineStr">
+        <is>
+          <t>Q.6</t>
+        </is>
+      </c>
+      <c r="N69" s="23" t="inlineStr">
+        <is>
+          <t>Him Lam, ho boi</t>
+        </is>
+      </c>
+      <c r="O69" s="22" t="inlineStr"/>
+      <c r="P69" s="23" t="inlineStr"/>
+      <c r="Q69" s="24" t="inlineStr">
+        <is>
+          <t>Xem BDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="22" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="23" t="inlineStr">
+        <is>
+          <t>Viva Riverside</t>
+        </is>
+      </c>
+      <c r="C70" s="23" t="inlineStr">
+        <is>
+          <t>Chung cu</t>
+        </is>
+      </c>
+      <c r="D70" s="23" t="inlineStr">
+        <is>
+          <t>3.0-4.5 ty</t>
+        </is>
+      </c>
+      <c r="E70" s="22" t="inlineStr">
+        <is>
+          <t>49.7</t>
+        </is>
+      </c>
+      <c r="F70" s="14" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="G70" s="22" t="inlineStr"/>
+      <c r="H70" s="23" t="inlineStr"/>
+      <c r="I70" s="23" t="inlineStr">
+        <is>
+          <t>56-95m2</t>
+        </is>
+      </c>
+      <c r="J70" s="22" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="K70" s="22" t="inlineStr"/>
+      <c r="L70" s="23" t="inlineStr">
+        <is>
+          <t>Vo Van Kiet, P.1, Q.6</t>
+        </is>
+      </c>
+      <c r="M70" s="23" t="inlineStr">
+        <is>
+          <t>Q.6</t>
+        </is>
+      </c>
+      <c r="N70" s="23" t="inlineStr">
+        <is>
+          <t>view song, gan TT</t>
+        </is>
+      </c>
+      <c r="O70" s="22" t="inlineStr"/>
+      <c r="P70" s="23" t="inlineStr"/>
+      <c r="Q70" s="24" t="inlineStr">
+        <is>
+          <t>Xem BDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="22" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="23" t="inlineStr">
+        <is>
+          <t>Saigon Asiana</t>
+        </is>
+      </c>
+      <c r="C71" s="23" t="inlineStr">
+        <is>
+          <t>Chung cu</t>
+        </is>
+      </c>
+      <c r="D71" s="23" t="inlineStr">
+        <is>
+          <t>3.0-4.2 ty</t>
+        </is>
+      </c>
+      <c r="E71" s="22" t="inlineStr">
+        <is>
+          <t>55.4</t>
+        </is>
+      </c>
+      <c r="F71" s="14" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="G71" s="22" t="inlineStr"/>
+      <c r="H71" s="23" t="inlineStr"/>
+      <c r="I71" s="23" t="inlineStr">
+        <is>
+          <t>55-75m2</t>
+        </is>
+      </c>
+      <c r="J71" s="22" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="K71" s="22" t="inlineStr"/>
+      <c r="L71" s="23" t="inlineStr">
+        <is>
+          <t>NV Luong, P.12, Q.6</t>
+        </is>
+      </c>
+      <c r="M71" s="23" t="inlineStr">
+        <is>
+          <t>Q.6</t>
+        </is>
+      </c>
+      <c r="N71" s="23" t="inlineStr">
+        <is>
+          <t>Gotec Land</t>
+        </is>
+      </c>
+      <c r="O71" s="22" t="inlineStr"/>
+      <c r="P71" s="23" t="inlineStr"/>
+      <c r="Q71" s="24" t="inlineStr">
+        <is>
+          <t>Xem BDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="22" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="23" t="inlineStr">
+        <is>
+          <t>D-Homme</t>
+        </is>
+      </c>
+      <c r="C72" s="23" t="inlineStr">
+        <is>
+          <t>Chung cu</t>
+        </is>
+      </c>
+      <c r="D72" s="23" t="inlineStr">
+        <is>
+          <t>3.8-5.0 ty</t>
+        </is>
+      </c>
+      <c r="E72" s="22" t="inlineStr">
+        <is>
+          <t>61.1</t>
+        </is>
+      </c>
+      <c r="F72" s="14" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="G72" s="22" t="inlineStr"/>
+      <c r="H72" s="23" t="inlineStr"/>
+      <c r="I72" s="23" t="inlineStr">
+        <is>
+          <t>58-86m2</t>
+        </is>
+      </c>
+      <c r="J72" s="22" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="K72" s="22" t="inlineStr"/>
+      <c r="L72" s="23" t="inlineStr">
+        <is>
+          <t>Hong Bang, P.12, Q.6</t>
+        </is>
+      </c>
+      <c r="M72" s="23" t="inlineStr">
+        <is>
+          <t>Q.6</t>
+        </is>
+      </c>
+      <c r="N72" s="23" t="inlineStr">
+        <is>
+          <t>DHA, mat tien HB</t>
+        </is>
+      </c>
+      <c r="O72" s="22" t="inlineStr"/>
+      <c r="P72" s="23" t="inlineStr"/>
+      <c r="Q72" s="24" t="inlineStr">
+        <is>
+          <t>Xem BDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="22" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="23" t="inlineStr">
+        <is>
+          <t>Summer Square</t>
+        </is>
+      </c>
+      <c r="C73" s="23" t="inlineStr">
+        <is>
+          <t>Chung cu</t>
+        </is>
+      </c>
+      <c r="D73" s="23" t="inlineStr">
+        <is>
+          <t>3.0-3.8 ty</t>
+        </is>
+      </c>
+      <c r="E73" s="22" t="inlineStr">
+        <is>
+          <t>53.5</t>
+        </is>
+      </c>
+      <c r="F73" s="14" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="G73" s="22" t="inlineStr"/>
+      <c r="H73" s="23" t="inlineStr"/>
+      <c r="I73" s="23" t="inlineStr">
+        <is>
+          <t>62-65m2</t>
+        </is>
+      </c>
+      <c r="J73" s="22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K73" s="22" t="inlineStr"/>
+      <c r="L73" s="23" t="inlineStr">
+        <is>
+          <t>Tan Hoa Dong, P.14, Q.6</t>
+        </is>
+      </c>
+      <c r="M73" s="23" t="inlineStr">
+        <is>
+          <t>Q.6</t>
+        </is>
+      </c>
+      <c r="N73" s="23" t="inlineStr">
+        <is>
+          <t>gia tot Q6</t>
+        </is>
+      </c>
+      <c r="O73" s="22" t="inlineStr"/>
+      <c r="P73" s="23" t="inlineStr"/>
+      <c r="Q73" s="24" t="inlineStr">
+        <is>
+          <t>Xem BDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="25" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="26" t="inlineStr">
+        <is>
+          <t>Saigon Royal Residence</t>
+        </is>
+      </c>
+      <c r="C74" s="26" t="inlineStr">
+        <is>
+          <t>Chung cu</t>
+        </is>
+      </c>
+      <c r="D74" s="26" t="inlineStr">
+        <is>
+          <t>4.3 ty</t>
+        </is>
+      </c>
+      <c r="E74" s="25" t="inlineStr">
+        <is>
+          <t>114.7</t>
+        </is>
+      </c>
+      <c r="F74" s="14" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="G74" s="25" t="inlineStr"/>
+      <c r="H74" s="26" t="inlineStr"/>
+      <c r="I74" s="26" t="inlineStr">
+        <is>
+          <t>35-40m2</t>
+        </is>
+      </c>
+      <c r="J74" s="25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K74" s="25" t="inlineStr"/>
+      <c r="L74" s="26" t="inlineStr">
+        <is>
+          <t>Ben Van Don, P. Xom Chieu, Q.4</t>
+        </is>
+      </c>
+      <c r="M74" s="26" t="inlineStr">
+        <is>
+          <t>Q.4</t>
+        </is>
+      </c>
+      <c r="N74" s="26" t="inlineStr">
+        <is>
+          <t>Novaland, view song</t>
+        </is>
+      </c>
+      <c r="O74" s="25" t="inlineStr"/>
+      <c r="P74" s="26" t="inlineStr"/>
+      <c r="Q74" s="27" t="inlineStr">
+        <is>
+          <t>Xem BDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="25" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="26" t="inlineStr">
+        <is>
+          <t>River Gate</t>
+        </is>
+      </c>
+      <c r="C75" s="26" t="inlineStr">
+        <is>
+          <t>Chung cu</t>
+        </is>
+      </c>
+      <c r="D75" s="26" t="inlineStr">
+        <is>
+          <t>3-4 ty</t>
+        </is>
+      </c>
+      <c r="E75" s="25" t="inlineStr">
+        <is>
+          <t>109.4</t>
+        </is>
+      </c>
+      <c r="F75" s="14" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="G75" s="25" t="inlineStr"/>
+      <c r="H75" s="26" t="inlineStr"/>
+      <c r="I75" s="26" t="inlineStr">
+        <is>
+          <t>26-38m2</t>
+        </is>
+      </c>
+      <c r="J75" s="25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K75" s="25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L75" s="26" t="inlineStr">
+        <is>
+          <t>Ben Van Don, P. Khanh Hoi, Q.4</t>
+        </is>
+      </c>
+      <c r="M75" s="26" t="inlineStr">
+        <is>
+          <t>Q.4</t>
+        </is>
+      </c>
+      <c r="N75" s="26" t="inlineStr">
+        <is>
+          <t>Novaland, Officetel</t>
+        </is>
+      </c>
+      <c r="O75" s="25" t="inlineStr"/>
+      <c r="P75" s="26" t="inlineStr"/>
+      <c r="Q75" s="27" t="inlineStr">
+        <is>
+          <t>Xem BDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="25" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="26" t="inlineStr">
+        <is>
+          <t>The Tresor</t>
+        </is>
+      </c>
+      <c r="C76" s="26" t="inlineStr">
+        <is>
+          <t>Chung cu</t>
+        </is>
+      </c>
+      <c r="D76" s="26" t="inlineStr">
+        <is>
+          <t>3.4 ty</t>
+        </is>
+      </c>
+      <c r="E76" s="25" t="inlineStr">
+        <is>
+          <t>103.0</t>
+        </is>
+      </c>
+      <c r="F76" s="14" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="G76" s="25" t="inlineStr"/>
+      <c r="H76" s="26" t="inlineStr"/>
+      <c r="I76" s="26" t="inlineStr">
+        <is>
+          <t>33m2</t>
+        </is>
+      </c>
+      <c r="J76" s="25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K76" s="25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L76" s="26" t="inlineStr">
+        <is>
+          <t>Ben Van Don, P. Xom Chieu, Q.4</t>
+        </is>
+      </c>
+      <c r="M76" s="26" t="inlineStr">
+        <is>
+          <t>Q.4</t>
+        </is>
+      </c>
+      <c r="N76" s="26" t="inlineStr">
+        <is>
+          <t>Novaland, full noi that</t>
+        </is>
+      </c>
+      <c r="O76" s="25" t="inlineStr"/>
+      <c r="P76" s="26" t="inlineStr"/>
+      <c r="Q76" s="27" t="inlineStr">
+        <is>
+          <t>Xem BDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="28" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="29" t="inlineStr">
+        <is>
+          <t>Q7 Saigon Riverside</t>
+        </is>
+      </c>
+      <c r="C77" s="29" t="inlineStr">
+        <is>
+          <t>Chung cu</t>
+        </is>
+      </c>
+      <c r="D77" s="29" t="inlineStr">
+        <is>
+          <t>3.1-3.6 ty</t>
+        </is>
+      </c>
+      <c r="E77" s="28" t="inlineStr">
+        <is>
+          <t>55.4</t>
+        </is>
+      </c>
+      <c r="F77" s="14" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="G77" s="28" t="inlineStr"/>
+      <c r="H77" s="29" t="inlineStr"/>
+      <c r="I77" s="29" t="inlineStr">
+        <is>
+          <t>53-68m2</t>
+        </is>
+      </c>
+      <c r="J77" s="28" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="K77" s="28" t="inlineStr"/>
+      <c r="L77" s="29" t="inlineStr">
+        <is>
+          <t>Dao Tri, P. Phu Thuan, Q.7</t>
+        </is>
+      </c>
+      <c r="M77" s="29" t="inlineStr">
+        <is>
+          <t>Q.7</t>
+        </is>
+      </c>
+      <c r="N77" s="29" t="inlineStr">
+        <is>
+          <t>Hung Thinh, view song</t>
+        </is>
+      </c>
+      <c r="O77" s="28" t="inlineStr"/>
+      <c r="P77" s="29" t="inlineStr"/>
+      <c r="Q77" s="30" t="inlineStr">
+        <is>
+          <t>Xem BDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="28" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="29" t="inlineStr">
+        <is>
+          <t>Luxcity</t>
+        </is>
+      </c>
+      <c r="C78" s="29" t="inlineStr">
+        <is>
+          <t>Chung cu</t>
+        </is>
+      </c>
+      <c r="D78" s="29" t="inlineStr">
+        <is>
+          <t>4.3-5 ty</t>
+        </is>
+      </c>
+      <c r="E78" s="28" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="F78" s="14" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="G78" s="28" t="inlineStr"/>
+      <c r="H78" s="29" t="inlineStr"/>
+      <c r="I78" s="29" t="inlineStr">
+        <is>
+          <t>70-85m2</t>
+        </is>
+      </c>
+      <c r="J78" s="28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K78" s="28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L78" s="29" t="inlineStr">
+        <is>
+          <t>Huynh Tan Phat, P. Binh Thuan, Q.7</t>
+        </is>
+      </c>
+      <c r="M78" s="29" t="inlineStr">
+        <is>
+          <t>Q.7</t>
+        </is>
+      </c>
+      <c r="N78" s="29" t="inlineStr">
+        <is>
+          <t>Dat Xanh Group</t>
+        </is>
+      </c>
+      <c r="O78" s="28" t="inlineStr"/>
+      <c r="P78" s="29" t="inlineStr"/>
+      <c r="Q78" s="30" t="inlineStr">
+        <is>
+          <t>Xem BDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="28" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="29" t="inlineStr">
+        <is>
+          <t>River Panorama</t>
+        </is>
+      </c>
+      <c r="C79" s="29" t="inlineStr">
+        <is>
+          <t>Chung cu</t>
+        </is>
+      </c>
+      <c r="D79" s="29" t="inlineStr">
+        <is>
+          <t>3.9-4.7 ty</t>
+        </is>
+      </c>
+      <c r="E79" s="28" t="inlineStr">
+        <is>
+          <t>71.7</t>
+        </is>
+      </c>
+      <c r="F79" s="14" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="G79" s="28" t="inlineStr"/>
+      <c r="H79" s="29" t="inlineStr"/>
+      <c r="I79" s="29" t="inlineStr">
+        <is>
+          <t>55-65m2</t>
+        </is>
+      </c>
+      <c r="J79" s="28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K79" s="28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L79" s="29" t="inlineStr">
+        <is>
+          <t>Hoang Quoc Viet, P. Phu Thuan, Q.7</t>
+        </is>
+      </c>
+      <c r="M79" s="29" t="inlineStr">
+        <is>
+          <t>Q.7</t>
+        </is>
+      </c>
+      <c r="N79" s="29" t="inlineStr">
+        <is>
+          <t>An Gia, da co so hong</t>
+        </is>
+      </c>
+      <c r="O79" s="28" t="inlineStr"/>
+      <c r="P79" s="29" t="inlineStr"/>
+      <c r="Q79" s="30" t="inlineStr">
+        <is>
+          <t>Xem BDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="28" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="29" t="inlineStr">
+        <is>
+          <t>Q7 Boulevard</t>
+        </is>
+      </c>
+      <c r="C80" s="29" t="inlineStr">
+        <is>
+          <t>Chung cu</t>
+        </is>
+      </c>
+      <c r="D80" s="29" t="inlineStr">
+        <is>
+          <t>3.3-3.9 ty</t>
+        </is>
+      </c>
+      <c r="E80" s="28" t="inlineStr">
+        <is>
+          <t>56.7</t>
+        </is>
+      </c>
+      <c r="F80" s="14" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="G80" s="28" t="inlineStr"/>
+      <c r="H80" s="29" t="inlineStr"/>
+      <c r="I80" s="29" t="inlineStr">
+        <is>
+          <t>57-70m2</t>
+        </is>
+      </c>
+      <c r="J80" s="28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K80" s="28" t="inlineStr"/>
+      <c r="L80" s="29" t="inlineStr">
+        <is>
+          <t>Nguyen Luong Bang, P. Phu My, Q.7</t>
+        </is>
+      </c>
+      <c r="M80" s="29" t="inlineStr">
+        <is>
+          <t>Q.7</t>
+        </is>
+      </c>
+      <c r="N80" s="29" t="inlineStr">
+        <is>
+          <t>Hung Thinh, gan PMH</t>
+        </is>
+      </c>
+      <c r="O80" s="28" t="inlineStr"/>
+      <c r="P80" s="29" t="inlineStr"/>
+      <c r="Q80" s="30" t="inlineStr">
+        <is>
+          <t>Xem BDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="28" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="29" t="inlineStr">
+        <is>
+          <t>Sunshine Sky City</t>
+        </is>
+      </c>
+      <c r="C81" s="29" t="inlineStr">
+        <is>
+          <t>Chung cu</t>
+        </is>
+      </c>
+      <c r="D81" s="29" t="inlineStr">
+        <is>
+          <t>4.2 ty</t>
+        </is>
+      </c>
+      <c r="E81" s="28" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="F81" s="14" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="G81" s="28" t="inlineStr"/>
+      <c r="H81" s="29" t="inlineStr"/>
+      <c r="I81" s="29" t="inlineStr">
+        <is>
+          <t>70m2</t>
+        </is>
+      </c>
+      <c r="J81" s="28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K81" s="28" t="inlineStr"/>
+      <c r="L81" s="29" t="inlineStr">
+        <is>
+          <t>Phu Thuan, P. Tan Phu, Q.7</t>
+        </is>
+      </c>
+      <c r="M81" s="29" t="inlineStr">
+        <is>
+          <t>Q.7</t>
+        </is>
+      </c>
+      <c r="N81" s="29" t="inlineStr">
+        <is>
+          <t>Sunshine Group, gan PMH</t>
+        </is>
+      </c>
+      <c r="O81" s="28" t="inlineStr"/>
+      <c r="P81" s="29" t="inlineStr"/>
+      <c r="Q81" s="30" t="inlineStr">
+        <is>
+          <t>Xem BDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="28" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="29" t="inlineStr">
+        <is>
+          <t>Jamona City</t>
+        </is>
+      </c>
+      <c r="C82" s="29" t="inlineStr">
+        <is>
+          <t>Chung cu</t>
+        </is>
+      </c>
+      <c r="D82" s="29" t="inlineStr">
+        <is>
+          <t>3-3.4 ty</t>
+        </is>
+      </c>
+      <c r="E82" s="28" t="inlineStr">
+        <is>
+          <t>58.7</t>
+        </is>
+      </c>
+      <c r="F82" s="14" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="G82" s="28" t="inlineStr"/>
+      <c r="H82" s="29" t="inlineStr"/>
+      <c r="I82" s="29" t="inlineStr">
+        <is>
+          <t>49-60m2</t>
+        </is>
+      </c>
+      <c r="J82" s="28" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="K82" s="28" t="inlineStr"/>
+      <c r="L82" s="29" t="inlineStr">
+        <is>
+          <t>Dao Tri, P. Phu Thuan, Q.7</t>
+        </is>
+      </c>
+      <c r="M82" s="29" t="inlineStr">
+        <is>
+          <t>Q.7</t>
+        </is>
+      </c>
+      <c r="N82" s="29" t="inlineStr">
+        <is>
+          <t>TTC Land, Dao Kim Cuong</t>
+        </is>
+      </c>
+      <c r="O82" s="28" t="inlineStr"/>
+      <c r="P82" s="29" t="inlineStr"/>
+      <c r="Q82" s="30" t="inlineStr">
+        <is>
+          <t>Xem BDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="28" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="29" t="inlineStr">
+        <is>
+          <t>The Era Town</t>
+        </is>
+      </c>
+      <c r="C83" s="29" t="inlineStr">
+        <is>
+          <t>Chung cu</t>
+        </is>
+      </c>
+      <c r="D83" s="29" t="inlineStr">
+        <is>
+          <t>3.3 ty</t>
+        </is>
+      </c>
+      <c r="E83" s="28" t="inlineStr">
+        <is>
+          <t>49.2</t>
+        </is>
+      </c>
+      <c r="F83" s="14" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="G83" s="28" t="inlineStr"/>
+      <c r="H83" s="29" t="inlineStr"/>
+      <c r="I83" s="29" t="inlineStr">
+        <is>
+          <t>67m2</t>
+        </is>
+      </c>
+      <c r="J83" s="28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K83" s="28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L83" s="29" t="inlineStr">
+        <is>
+          <t>P. Phu My, Q.7</t>
+        </is>
+      </c>
+      <c r="M83" s="29" t="inlineStr">
+        <is>
+          <t>Q.7</t>
+        </is>
+      </c>
+      <c r="N83" s="29" t="inlineStr">
+        <is>
+          <t>Duc Khai, co so hong</t>
+        </is>
+      </c>
+      <c r="O83" s="28" t="inlineStr"/>
+      <c r="P83" s="29" t="inlineStr"/>
+      <c r="Q83" s="30" t="inlineStr">
+        <is>
+          <t>Xem BDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="9" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="10" t="inlineStr">
+        <is>
+          <t>Westgate An Gia</t>
+        </is>
+      </c>
+      <c r="C84" s="10" t="inlineStr">
+        <is>
+          <t>Chung cu</t>
+        </is>
+      </c>
+      <c r="D84" s="10" t="inlineStr">
+        <is>
+          <t>3.2-4.5 ty</t>
+        </is>
+      </c>
+      <c r="E84" s="9" t="inlineStr">
+        <is>
+          <t>44.8</t>
+        </is>
+      </c>
+      <c r="F84" s="14" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="G84" s="9" t="inlineStr"/>
+      <c r="H84" s="10" t="inlineStr"/>
+      <c r="I84" s="10" t="inlineStr">
+        <is>
+          <t>59-113m2</t>
+        </is>
+      </c>
+      <c r="J84" s="9" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="K84" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L84" s="10" t="inlineStr">
+        <is>
+          <t>Nguyen Van Linh, TT.Tan Tuc, Binh Chanh</t>
+        </is>
+      </c>
+      <c r="M84" s="10" t="inlineStr">
+        <is>
+          <t>Binh Chanh</t>
+        </is>
+      </c>
+      <c r="N84" s="10" t="inlineStr">
+        <is>
+          <t>An Gia Investment, so hong</t>
+        </is>
+      </c>
+      <c r="O84" s="9" t="inlineStr"/>
+      <c r="P84" s="10" t="inlineStr"/>
+      <c r="Q84" s="11" t="inlineStr">
+        <is>
+          <t>Xem BDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="12" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="13" t="inlineStr">
         <is>
           <t>The Privia</t>
         </is>
       </c>
-      <c r="C55" s="13" t="inlineStr">
+      <c r="C85" s="13" t="inlineStr">
         <is>
           <t>Chung cu</t>
         </is>
       </c>
-      <c r="D55" s="13" t="inlineStr">
+      <c r="D85" s="13" t="inlineStr">
         <is>
           <t>3.35-5.13 ty</t>
         </is>
       </c>
-      <c r="E55" s="12" t="inlineStr">
+      <c r="E85" s="12" t="inlineStr">
         <is>
           <t>63.3</t>
         </is>
       </c>
-      <c r="F55" s="19" t="inlineStr">
+      <c r="F85" s="31" t="inlineStr">
         <is>
           <t>Thap</t>
         </is>
       </c>
-      <c r="G55" s="12" t="inlineStr">
+      <c r="G85" s="12" t="inlineStr">
         <is>
           <t>VIP KC</t>
         </is>
       </c>
-      <c r="H55" s="13" t="inlineStr">
+      <c r="H85" s="13" t="inlineStr">
         <is>
           <t>Moi gioi pro</t>
         </is>
       </c>
-      <c r="I55" s="13" t="inlineStr">
+      <c r="I85" s="13" t="inlineStr">
         <is>
           <t>51-83m2</t>
         </is>
       </c>
-      <c r="J55" s="12" t="inlineStr">
+      <c r="J85" s="12" t="inlineStr">
         <is>
           <t>2,3,1</t>
         </is>
       </c>
-      <c r="K55" s="12" t="inlineStr">
+      <c r="K85" s="12" t="inlineStr">
         <is>
           <t>2,1</t>
         </is>
       </c>
-      <c r="L55" s="13" t="inlineStr">
+      <c r="L85" s="13" t="inlineStr">
         <is>
           <t>P. An Lac, Q. Binh Tan</t>
         </is>
       </c>
-      <c r="M55" s="13" t="inlineStr">
+      <c r="M85" s="13" t="inlineStr">
         <is>
           <t>Binh Tan</t>
         </is>
       </c>
-      <c r="N55" s="13" t="inlineStr">
+      <c r="N85" s="13" t="inlineStr">
         <is>
           <t>12 bai, top: diamond/broker_pro</t>
         </is>
       </c>
-      <c r="O55" s="12" t="inlineStr"/>
-      <c r="P55" s="13" t="inlineStr"/>
-      <c r="Q55" s="15" t="inlineStr">
+      <c r="O85" s="12" t="inlineStr"/>
+      <c r="P85" s="13" t="inlineStr"/>
+      <c r="Q85" s="15" t="inlineStr">
         <is>
           <t>Xem BDS</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="12" t="n">
-        <v>55</v>
-      </c>
-      <c r="B56" s="13" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="12" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="13" t="inlineStr">
         <is>
           <t>Akari City</t>
         </is>
       </c>
-      <c r="C56" s="13" t="inlineStr">
+      <c r="C86" s="13" t="inlineStr">
         <is>
           <t>Chung cu</t>
         </is>
       </c>
-      <c r="D56" s="13" t="inlineStr">
+      <c r="D86" s="13" t="inlineStr">
         <is>
           <t>3.5-5.2 ty</t>
         </is>
       </c>
-      <c r="E56" s="12" t="inlineStr">
+      <c r="E86" s="12" t="inlineStr">
         <is>
           <t>55.8</t>
         </is>
       </c>
-      <c r="F56" s="19" t="inlineStr">
+      <c r="F86" s="31" t="inlineStr">
         <is>
           <t>Thap</t>
         </is>
       </c>
-      <c r="G56" s="12" t="inlineStr">
+      <c r="G86" s="12" t="inlineStr">
         <is>
           <t>VIP Vang</t>
         </is>
       </c>
-      <c r="H56" s="13" t="inlineStr">
+      <c r="H86" s="13" t="inlineStr">
         <is>
           <t>Moi gioi pro</t>
         </is>
       </c>
-      <c r="I56" s="13" t="inlineStr">
+      <c r="I86" s="13" t="inlineStr">
         <is>
           <t>56-100m2</t>
         </is>
       </c>
-      <c r="J56" s="12" t="inlineStr">
+      <c r="J86" s="12" t="inlineStr">
         <is>
           <t>2,3</t>
         </is>
       </c>
-      <c r="K56" s="12" t="inlineStr">
+      <c r="K86" s="12" t="inlineStr">
         <is>
           <t>1,2</t>
         </is>
       </c>
-      <c r="L56" s="13" t="inlineStr">
+      <c r="L86" s="13" t="inlineStr">
         <is>
           <t>P. An Lac, Q. Binh Tan</t>
         </is>
       </c>
-      <c r="M56" s="13" t="inlineStr">
+      <c r="M86" s="13" t="inlineStr">
         <is>
           <t>Binh Tan</t>
         </is>
       </c>
-      <c r="N56" s="13" t="inlineStr">
+      <c r="N86" s="13" t="inlineStr">
         <is>
           <t>8 bai, top: gold/broker_pro</t>
         </is>
       </c>
-      <c r="O56" s="12" t="inlineStr"/>
-      <c r="P56" s="13" t="inlineStr"/>
-      <c r="Q56" s="15" t="inlineStr">
+      <c r="O86" s="12" t="inlineStr"/>
+      <c r="P86" s="13" t="inlineStr"/>
+      <c r="Q86" s="15" t="inlineStr">
         <is>
           <t>Xem BDS</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="9" t="n">
-        <v>56</v>
-      </c>
-      <c r="B57" s="10" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="9" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="10" t="inlineStr">
         <is>
           <t>Mizuki Park</t>
         </is>
       </c>
-      <c r="C57" s="10" t="inlineStr">
+      <c r="C87" s="10" t="inlineStr">
         <is>
           <t>Chung cu</t>
         </is>
       </c>
-      <c r="D57" s="10" t="inlineStr">
+      <c r="D87" s="10" t="inlineStr">
         <is>
           <t>3.7-4.9 ty</t>
         </is>
       </c>
-      <c r="E57" s="9" t="inlineStr">
+      <c r="E87" s="9" t="inlineStr">
         <is>
           <t>70.5</t>
         </is>
       </c>
-      <c r="F57" s="19" t="inlineStr">
+      <c r="F87" s="31" t="inlineStr">
         <is>
           <t>Thap</t>
         </is>
       </c>
-      <c r="G57" s="9" t="inlineStr">
+      <c r="G87" s="9" t="inlineStr">
         <is>
           <t>VIP KC</t>
         </is>
       </c>
-      <c r="H57" s="10" t="inlineStr"/>
-      <c r="I57" s="10" t="inlineStr">
+      <c r="H87" s="10" t="inlineStr"/>
+      <c r="I87" s="10" t="inlineStr">
         <is>
           <t>61 m²</t>
         </is>
       </c>
-      <c r="J57" s="9" t="inlineStr"/>
-      <c r="K57" s="9" t="inlineStr"/>
-      <c r="L57" s="10" t="inlineStr">
+      <c r="J87" s="9" t="inlineStr"/>
+      <c r="K87" s="9" t="inlineStr"/>
+      <c r="L87" s="10" t="inlineStr">
         <is>
           <t>X. Bình Hưng, Binh Chanh</t>
         </is>
       </c>
-      <c r="M57" s="10" t="inlineStr">
+      <c r="M87" s="10" t="inlineStr">
         <is>
           <t>Binh Chanh</t>
         </is>
       </c>
-      <c r="N57" s="10" t="inlineStr">
+      <c r="N87" s="10" t="inlineStr">
         <is>
           <t>Mizuki Park - Căn hộ view sông Trellia Cove GH trực tiếp CĐT Nam Long - CK đến 14,5% -LH 0932 661 ***</t>
         </is>
       </c>
-      <c r="O57" s="9" t="inlineStr"/>
-      <c r="P57" s="10" t="inlineStr"/>
-      <c r="Q57" s="11" t="inlineStr">
+      <c r="O87" s="9" t="inlineStr"/>
+      <c r="P87" s="10" t="inlineStr"/>
+      <c r="Q87" s="11" t="inlineStr">
         <is>
           <t>Xem BDS</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="9" t="n">
-        <v>57</v>
-      </c>
-      <c r="B58" s="10" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="9" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="10" t="inlineStr">
         <is>
           <t>Trellia Cove</t>
         </is>
       </c>
-      <c r="C58" s="10" t="inlineStr">
+      <c r="C88" s="10" t="inlineStr">
         <is>
           <t>Chung cu</t>
         </is>
       </c>
-      <c r="D58" s="10" t="inlineStr">
+      <c r="D88" s="10" t="inlineStr">
         <is>
           <t>4-5 ty</t>
         </is>
       </c>
-      <c r="E58" s="9" t="inlineStr">
+      <c r="E88" s="9" t="inlineStr">
         <is>
           <t>75.0</t>
         </is>
       </c>
-      <c r="F58" s="19" t="inlineStr">
+      <c r="F88" s="31" t="inlineStr">
         <is>
           <t>Thap</t>
         </is>
       </c>
-      <c r="G58" s="9" t="inlineStr">
+      <c r="G88" s="9" t="inlineStr">
         <is>
           <t>VIP KC</t>
         </is>
       </c>
-      <c r="H58" s="10" t="inlineStr"/>
-      <c r="I58" s="10" t="inlineStr">
+      <c r="H88" s="10" t="inlineStr"/>
+      <c r="I88" s="10" t="inlineStr">
         <is>
           <t>60 m²</t>
         </is>
       </c>
-      <c r="J58" s="9" t="inlineStr"/>
-      <c r="K58" s="9" t="inlineStr"/>
-      <c r="L58" s="10" t="inlineStr">
+      <c r="J88" s="9" t="inlineStr"/>
+      <c r="K88" s="9" t="inlineStr"/>
+      <c r="L88" s="10" t="inlineStr">
         <is>
           <t>X. Bình Hưng, Binh Chanh</t>
         </is>
       </c>
-      <c r="M58" s="10" t="inlineStr">
+      <c r="M88" s="10" t="inlineStr">
         <is>
           <t>Binh Chanh</t>
         </is>
       </c>
-      <c r="N58" s="10" t="inlineStr">
+      <c r="N88" s="10" t="inlineStr">
         <is>
           <t>Mở bán căn hộ Mizuki - Giá gốc từ chủ đầu tư, chiết khấu lên đến 15.5%</t>
         </is>
       </c>
-      <c r="O58" s="9" t="inlineStr"/>
-      <c r="P58" s="10" t="inlineStr"/>
-      <c r="Q58" s="11" t="inlineStr">
+      <c r="O88" s="9" t="inlineStr"/>
+      <c r="P88" s="10" t="inlineStr"/>
+      <c r="Q88" s="11" t="inlineStr">
         <is>
           <t>Xem BDS</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="n">
-        <v>58</v>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
         <is>
           <t>Diamond Brilliant</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr">
+      <c r="C89" s="3" t="inlineStr">
         <is>
           <t>Chung cu</t>
         </is>
       </c>
-      <c r="D59" s="3" t="inlineStr">
+      <c r="D89" s="3" t="inlineStr">
         <is>
           <t>7.8-8.9 ty</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>87.0</t>
         </is>
       </c>
-      <c r="F59" s="19" t="inlineStr">
+      <c r="F89" s="31" t="inlineStr">
         <is>
           <t>Thap</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr">
         <is>
           <t>VIP Bac</t>
         </is>
       </c>
-      <c r="H59" s="3" t="inlineStr">
+      <c r="H89" s="3" t="inlineStr">
         <is>
           <t>Ca nhan</t>
         </is>
       </c>
-      <c r="I59" s="3" t="inlineStr">
+      <c r="I89" s="3" t="inlineStr">
         <is>
           <t>96 m²</t>
         </is>
       </c>
-      <c r="J59" s="2" t="inlineStr">
+      <c r="J89" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K59" s="2" t="inlineStr">
+      <c r="K89" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="L59" s="3" t="inlineStr">
+      <c r="L89" s="3" t="inlineStr">
         <is>
           <t>P. Sơn Kỳ, Tan Phu</t>
         </is>
       </c>
-      <c r="M59" s="3" t="inlineStr">
+      <c r="M89" s="3" t="inlineStr">
         <is>
           <t>Tan Phu</t>
         </is>
       </c>
-      <c r="N59" s="3" t="inlineStr">
+      <c r="N89" s="3" t="inlineStr">
         <is>
           <t>Mình chính chủ cần bán căn góc trệt Diamond Brilliant Celadon Tân Phú 96m2 full nội thất</t>
         </is>
       </c>
-      <c r="O59" s="2" t="inlineStr"/>
-      <c r="P59" s="3" t="inlineStr"/>
-      <c r="Q59" s="5" t="inlineStr">
+      <c r="O89" s="2" t="inlineStr"/>
+      <c r="P89" s="3" t="inlineStr"/>
+      <c r="Q89" s="5" t="inlineStr">
         <is>
           <t>Xem BDS</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
         <is>
           <t>Diamond Centery</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="C90" s="3" t="inlineStr">
         <is>
           <t>Chung cu</t>
         </is>
       </c>
-      <c r="D60" s="3" t="inlineStr">
+      <c r="D90" s="3" t="inlineStr">
         <is>
           <t>6.8-14.88 ty</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>112.9</t>
         </is>
       </c>
-      <c r="F60" s="19" t="inlineStr">
+      <c r="F90" s="31" t="inlineStr">
         <is>
           <t>Thap</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr">
         <is>
           <t>VIP Bac</t>
         </is>
       </c>
-      <c r="H60" s="3" t="inlineStr"/>
-      <c r="I60" s="3" t="inlineStr">
+      <c r="H90" s="3" t="inlineStr"/>
+      <c r="I90" s="3" t="inlineStr">
         <is>
           <t>96 m²</t>
         </is>
       </c>
-      <c r="J60" s="2" t="inlineStr"/>
-      <c r="K60" s="2" t="inlineStr"/>
-      <c r="L60" s="3" t="inlineStr">
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="3" t="inlineStr">
         <is>
           <t>P. Sơn Kỳ, Tan Phu</t>
         </is>
       </c>
-      <c r="M60" s="3" t="inlineStr">
+      <c r="M90" s="3" t="inlineStr">
         <is>
           <t>Tan Phu</t>
         </is>
       </c>
-      <c r="N60" s="3" t="inlineStr">
+      <c r="N90" s="3" t="inlineStr">
         <is>
           <t>Thanh toán 900tr nhận nhà Diamond Centery Celadon City-Tháp C2-96m2 - View biển. LH ngay 0931 280 ***</t>
         </is>
       </c>
-      <c r="O60" s="2" t="inlineStr"/>
-      <c r="P60" s="3" t="inlineStr"/>
-      <c r="Q60" s="5" t="inlineStr">
+      <c r="O90" s="2" t="inlineStr"/>
+      <c r="P90" s="3" t="inlineStr"/>
+      <c r="Q90" s="5" t="inlineStr">
         <is>
           <t>Xem BDS</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="B61" s="3" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
         <is>
           <t>Emerald Celadon City</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr">
+      <c r="C91" s="3" t="inlineStr">
         <is>
           <t>Chung cu</t>
         </is>
       </c>
-      <c r="D61" s="3" t="inlineStr">
+      <c r="D91" s="3" t="inlineStr">
         <is>
           <t>4-13.9 ty</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>126.1</t>
         </is>
       </c>
-      <c r="F61" s="19" t="inlineStr">
+      <c r="F91" s="31" t="inlineStr">
         <is>
           <t>Thap</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr">
         <is>
           <t>VIP Bac</t>
         </is>
       </c>
-      <c r="H61" s="3" t="inlineStr"/>
-      <c r="I61" s="3" t="inlineStr">
+      <c r="H91" s="3" t="inlineStr"/>
+      <c r="I91" s="3" t="inlineStr">
         <is>
           <t>71 m²</t>
         </is>
       </c>
-      <c r="J61" s="2" t="inlineStr">
+      <c r="J91" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K61" s="2" t="inlineStr">
+      <c r="K91" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="L61" s="3" t="inlineStr">
+      <c r="L91" s="3" t="inlineStr">
         <is>
           <t>P. Sơn Kỳ, Tan Phu</t>
         </is>
       </c>
-      <c r="M61" s="3" t="inlineStr">
+      <c r="M91" s="3" t="inlineStr">
         <is>
           <t>Tan Phu</t>
         </is>
       </c>
-      <c r="N61" s="3" t="inlineStr">
+      <c r="N91" s="3" t="inlineStr">
         <is>
           <t>Emerald cập nhật liên tục sản phẩm tốt nhất gửi đến Anh Chị ( 1Pn 4.05 tỷ, 2Pn 5 tỷ, 3Pn 7.6 tỷ )</t>
         </is>
       </c>
-      <c r="O61" s="2" t="inlineStr"/>
-      <c r="P61" s="3" t="inlineStr"/>
-      <c r="Q61" s="5" t="inlineStr">
+      <c r="O91" s="2" t="inlineStr"/>
+      <c r="P91" s="3" t="inlineStr"/>
+      <c r="Q91" s="5" t="inlineStr">
         <is>
           <t>Xem BDS</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="B62" s="3" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
         <is>
           <t>Oriental Plaza</t>
         </is>
       </c>
-      <c r="C62" s="3" t="inlineStr">
+      <c r="C92" s="3" t="inlineStr">
         <is>
           <t>Chung cu</t>
         </is>
       </c>
-      <c r="D62" s="3" t="inlineStr">
+      <c r="D92" s="3" t="inlineStr">
         <is>
           <t>4-5 ty</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>42.5</t>
         </is>
       </c>
-      <c r="F62" s="19" t="inlineStr">
+      <c r="F92" s="31" t="inlineStr">
         <is>
           <t>Thap</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr">
         <is>
           <t>VIP Bac</t>
         </is>
       </c>
-      <c r="H62" s="3" t="inlineStr"/>
-      <c r="I62" s="3" t="inlineStr">
+      <c r="H92" s="3" t="inlineStr"/>
+      <c r="I92" s="3" t="inlineStr">
         <is>
           <t>106 m²</t>
         </is>
       </c>
-      <c r="J62" s="2" t="inlineStr">
+      <c r="J92" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K62" s="2" t="inlineStr">
+      <c r="K92" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="L62" s="3" t="inlineStr">
+      <c r="L92" s="3" t="inlineStr">
         <is>
           <t>P. Tân Thành, Tan Phu</t>
         </is>
       </c>
-      <c r="M62" s="3" t="inlineStr">
+      <c r="M92" s="3" t="inlineStr">
         <is>
           <t>Tan Phu</t>
         </is>
       </c>
-      <c r="N62" s="3" t="inlineStr">
+      <c r="N92" s="3" t="inlineStr">
         <is>
           <t>Bán căn hộ Oriental Plaza 685 Âu Cơ - Tân Phú. Tiện ích: Siêu thị, hồ bơi, thư viện, spa, cafe</t>
         </is>
       </c>
-      <c r="O62" s="2" t="inlineStr"/>
-      <c r="P62" s="3" t="inlineStr"/>
-      <c r="Q62" s="5" t="inlineStr">
+      <c r="O92" s="2" t="inlineStr"/>
+      <c r="P92" s="3" t="inlineStr"/>
+      <c r="Q92" s="5" t="inlineStr">
         <is>
           <t>Xem BDS</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="B63" s="3" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr">
+      <c r="C93" s="3" t="inlineStr">
         <is>
           <t>Chung cu</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr">
+      <c r="D93" s="3" t="inlineStr">
         <is>
           <t>9,65 tỷ</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>80.4</t>
         </is>
       </c>
-      <c r="F63" s="19" t="inlineStr">
+      <c r="F93" s="31" t="inlineStr">
         <is>
           <t>Thap</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr">
         <is>
           <t>VIP Bac</t>
         </is>
       </c>
-      <c r="H63" s="3" t="inlineStr"/>
-      <c r="I63" s="3" t="inlineStr">
+      <c r="H93" s="3" t="inlineStr"/>
+      <c r="I93" s="3" t="inlineStr">
         <is>
           <t>120 m²</t>
         </is>
       </c>
-      <c r="J63" s="2" t="inlineStr">
+      <c r="J93" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K63" s="2" t="inlineStr">
+      <c r="K93" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="L63" s="3" t="inlineStr">
+      <c r="L93" s="3" t="inlineStr">
         <is>
           <t>P. Sơn Kỳ, Tan Phu</t>
         </is>
       </c>
-      <c r="M63" s="3" t="inlineStr">
+      <c r="M93" s="3" t="inlineStr">
         <is>
           <t>Tan Phu</t>
         </is>
       </c>
-      <c r="N63" s="3" t="inlineStr">
+      <c r="N93" s="3" t="inlineStr">
         <is>
           <t>Căn 3PN 3WC 120m2 view công viên cây xanh. Trả giãn 36 tháng. Nhà mới ở ngay</t>
         </is>
       </c>
-      <c r="O63" s="2" t="inlineStr"/>
-      <c r="P63" s="3" t="inlineStr"/>
-      <c r="Q63" s="5" t="inlineStr">
+      <c r="O93" s="2" t="inlineStr"/>
+      <c r="P93" s="3" t="inlineStr"/>
+      <c r="Q93" s="5" t="inlineStr">
         <is>
           <t>Xem BDS</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="6" t="n">
-        <v>63</v>
-      </c>
-      <c r="B64" s="7" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="7" t="inlineStr">
         <is>
           <t>Sky Center</t>
         </is>
       </c>
-      <c r="C64" s="7" t="inlineStr">
+      <c r="C94" s="7" t="inlineStr">
         <is>
           <t>Chung cu</t>
         </is>
       </c>
-      <c r="D64" s="7" t="inlineStr">
+      <c r="D94" s="7" t="inlineStr">
         <is>
           <t>3.65-10.9 ty</t>
         </is>
       </c>
-      <c r="E64" s="6" t="inlineStr">
+      <c r="E94" s="6" t="inlineStr">
         <is>
           <t>98.3</t>
         </is>
       </c>
-      <c r="F64" s="19" t="inlineStr">
+      <c r="F94" s="31" t="inlineStr">
         <is>
           <t>Thap</t>
         </is>
       </c>
-      <c r="G64" s="6" t="inlineStr">
+      <c r="G94" s="6" t="inlineStr">
         <is>
           <t>VIP Bac</t>
         </is>
       </c>
-      <c r="H64" s="7" t="inlineStr"/>
-      <c r="I64" s="7" t="inlineStr">
+      <c r="H94" s="7" t="inlineStr"/>
+      <c r="I94" s="7" t="inlineStr">
         <is>
           <t>74 m²</t>
         </is>
       </c>
-      <c r="J64" s="6" t="inlineStr">
+      <c r="J94" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K64" s="6" t="inlineStr">
+      <c r="K94" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="L64" s="7" t="inlineStr">
+      <c r="L94" s="7" t="inlineStr">
         <is>
           <t>Phường 2, Tan Binh</t>
         </is>
       </c>
-      <c r="M64" s="7" t="inlineStr">
+      <c r="M94" s="7" t="inlineStr">
         <is>
           <t>Tan Binh</t>
         </is>
       </c>
-      <c r="N64" s="7" t="inlineStr">
+      <c r="N94" s="7" t="inlineStr">
         <is>
           <t>Bán CC Sky Center giá cực chất 6 tỷ, 74m2, 2PN + 2WC, Phổ Quang, Tân Bình, hổ trợ vay.LH 0934 403 ***</t>
         </is>
       </c>
-      <c r="O64" s="6" t="inlineStr"/>
-      <c r="P64" s="7" t="inlineStr"/>
-      <c r="Q64" s="8" t="inlineStr">
+      <c r="O94" s="6" t="inlineStr"/>
+      <c r="P94" s="7" t="inlineStr"/>
+      <c r="Q94" s="8" t="inlineStr">
         <is>
           <t>Xem BDS</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="6" t="n">
-        <v>64</v>
-      </c>
-      <c r="B65" s="7" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="6" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="7" t="inlineStr">
         <is>
           <t>Park Legend</t>
         </is>
       </c>
-      <c r="C65" s="7" t="inlineStr">
+      <c r="C95" s="7" t="inlineStr">
         <is>
           <t>Chung cu</t>
         </is>
       </c>
-      <c r="D65" s="7" t="inlineStr">
+      <c r="D95" s="7" t="inlineStr">
         <is>
           <t>6.5 ty</t>
         </is>
       </c>
-      <c r="E65" s="6" t="inlineStr">
+      <c r="E95" s="6" t="inlineStr">
         <is>
           <t>92.9</t>
         </is>
       </c>
-      <c r="F65" s="19" t="inlineStr">
+      <c r="F95" s="31" t="inlineStr">
         <is>
           <t>Thap</t>
         </is>
       </c>
-      <c r="G65" s="6" t="inlineStr">
+      <c r="G95" s="6" t="inlineStr">
         <is>
           <t>VIP Bac</t>
         </is>
       </c>
-      <c r="H65" s="7" t="inlineStr"/>
-      <c r="I65" s="7" t="inlineStr">
+      <c r="H95" s="7" t="inlineStr"/>
+      <c r="I95" s="7" t="inlineStr">
         <is>
           <t>70 m²</t>
         </is>
       </c>
-      <c r="J65" s="6" t="inlineStr">
+      <c r="J95" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K65" s="6" t="inlineStr">
+      <c r="K95" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="L65" s="7" t="inlineStr">
+      <c r="L95" s="7" t="inlineStr">
         <is>
           <t>Phường 2, Tan Binh</t>
         </is>
       </c>
-      <c r="M65" s="7" t="inlineStr">
+      <c r="M95" s="7" t="inlineStr">
         <is>
           <t>Tan Binh</t>
         </is>
       </c>
-      <c r="N65" s="7" t="inlineStr">
+      <c r="N95" s="7" t="inlineStr">
         <is>
           <t>BÁN CĂN HỘ PARK LEGEND, 2 PHÒNG NGỦ, 2WC, GIÁ 6.5 TỶ, 120M, 3 PHÒNG GIÁ 11 TỶ DƯƠNG TUẤN 0901 499 ***</t>
         </is>
       </c>
-      <c r="O65" s="6" t="inlineStr"/>
-      <c r="P65" s="7" t="inlineStr"/>
-      <c r="Q65" s="8" t="inlineStr">
+      <c r="O95" s="6" t="inlineStr"/>
+      <c r="P95" s="7" t="inlineStr"/>
+      <c r="Q95" s="8" t="inlineStr">
         <is>
           <t>Xem BDS</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="9" t="n">
-        <v>65</v>
-      </c>
-      <c r="B66" s="10" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="9" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="10" t="inlineStr">
         <is>
           <t>Sai Gon Mia</t>
         </is>
       </c>
-      <c r="C66" s="10" t="inlineStr">
+      <c r="C96" s="10" t="inlineStr">
         <is>
           <t>Chung cu</t>
         </is>
       </c>
-      <c r="D66" s="10" t="inlineStr">
+      <c r="D96" s="10" t="inlineStr">
         <is>
           <t>5,3 tỷ</t>
         </is>
       </c>
-      <c r="E66" s="9" t="inlineStr">
+      <c r="E96" s="9" t="inlineStr">
         <is>
           <t>68.0</t>
         </is>
       </c>
-      <c r="F66" s="19" t="inlineStr">
+      <c r="F96" s="31" t="inlineStr">
         <is>
           <t>Thap</t>
         </is>
       </c>
-      <c r="G66" s="9" t="inlineStr">
+      <c r="G96" s="9" t="inlineStr">
         <is>
           <t>VIP Bac</t>
         </is>
       </c>
-      <c r="H66" s="10" t="inlineStr"/>
-      <c r="I66" s="10" t="inlineStr">
+      <c r="H96" s="10" t="inlineStr"/>
+      <c r="I96" s="10" t="inlineStr">
         <is>
           <t>78 m²</t>
         </is>
       </c>
-      <c r="J66" s="9" t="inlineStr">
+      <c r="J96" s="9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K66" s="9" t="inlineStr">
+      <c r="K96" s="9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="L66" s="10" t="inlineStr">
+      <c r="L96" s="10" t="inlineStr">
         <is>
           <t>X. Bình Hưng, Binh Chanh</t>
         </is>
       </c>
-      <c r="M66" s="10" t="inlineStr">
+      <c r="M96" s="10" t="inlineStr">
         <is>
           <t>Binh Chanh</t>
         </is>
       </c>
-      <c r="N66" s="10" t="inlineStr">
+      <c r="N96" s="10" t="inlineStr">
         <is>
           <t>BQL Sài Gòn Mia bán căn hộ 1PN 2PN 3PN 3,4 tỷ - 4,7 tỷ full nội thất, LH BQL 0935 375 ***</t>
         </is>
       </c>
-      <c r="O66" s="9" t="inlineStr"/>
-      <c r="P66" s="10" t="inlineStr"/>
-      <c r="Q66" s="11" t="inlineStr">
+      <c r="O96" s="9" t="inlineStr"/>
+      <c r="P96" s="10" t="inlineStr"/>
+      <c r="Q96" s="11" t="inlineStr">
         <is>
           <t>Xem BDS</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="6" t="n">
-        <v>66</v>
-      </c>
-      <c r="B67" s="7" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="6" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="7" t="inlineStr">
         <is>
           <t>The Everrich Infinity</t>
         </is>
       </c>
-      <c r="C67" s="7" t="inlineStr">
+      <c r="C97" s="7" t="inlineStr">
         <is>
           <t>Chung cu</t>
         </is>
       </c>
-      <c r="D67" s="7" t="inlineStr">
+      <c r="D97" s="7" t="inlineStr">
         <is>
           <t>3.3-4.5 ty</t>
         </is>
       </c>
-      <c r="E67" s="6" t="inlineStr">
+      <c r="E97" s="6" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="F67" s="19" t="inlineStr">
+      <c r="F97" s="31" t="inlineStr">
         <is>
           <t>Thap</t>
         </is>
       </c>
-      <c r="G67" s="6" t="inlineStr"/>
-      <c r="H67" s="7" t="inlineStr"/>
-      <c r="I67" s="7" t="inlineStr">
+      <c r="G97" s="6" t="inlineStr"/>
+      <c r="H97" s="7" t="inlineStr"/>
+      <c r="I97" s="7" t="inlineStr">
         <is>
           <t>33-45m2</t>
         </is>
       </c>
-      <c r="J67" s="6" t="inlineStr">
+      <c r="J97" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K67" s="6" t="inlineStr">
+      <c r="K97" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="L67" s="7" t="inlineStr">
+      <c r="L97" s="7" t="inlineStr">
         <is>
           <t>An Duong Vuong, P.4, Q.5</t>
         </is>
       </c>
-      <c r="M67" s="7" t="inlineStr">
+      <c r="M97" s="7" t="inlineStr">
         <is>
           <t>Q.5</t>
         </is>
       </c>
-      <c r="N67" s="7" t="inlineStr">
+      <c r="N97" s="7" t="inlineStr">
         <is>
           <t>Full noi that, trung tam thanh pho</t>
         </is>
       </c>
-      <c r="O67" s="6" t="inlineStr"/>
-      <c r="P67" s="7" t="inlineStr"/>
-      <c r="Q67" s="8" t="inlineStr">
+      <c r="O97" s="6" t="inlineStr"/>
+      <c r="P97" s="7" t="inlineStr"/>
+      <c r="Q97" s="8" t="inlineStr">
         <is>
           <t>Xem BDS</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="6" t="n">
-        <v>67</v>
-      </c>
-      <c r="B68" s="7" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="6" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="7" t="inlineStr">
         <is>
           <t>Legacy 66 Tan Thanh</t>
         </is>
       </c>
-      <c r="C68" s="7" t="inlineStr">
+      <c r="C98" s="7" t="inlineStr">
         <is>
           <t>Chung cu</t>
         </is>
       </c>
-      <c r="D68" s="7" t="inlineStr">
+      <c r="D98" s="7" t="inlineStr">
         <is>
           <t>4.5 ty</t>
         </is>
       </c>
-      <c r="E68" s="6" t="inlineStr">
+      <c r="E98" s="6" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="F68" s="19" t="inlineStr">
+      <c r="F98" s="31" t="inlineStr">
         <is>
           <t>Thap</t>
         </is>
       </c>
-      <c r="G68" s="6" t="inlineStr"/>
-      <c r="H68" s="7" t="inlineStr"/>
-      <c r="I68" s="7" t="inlineStr">
+      <c r="G98" s="6" t="inlineStr"/>
+      <c r="H98" s="7" t="inlineStr"/>
+      <c r="I98" s="7" t="inlineStr">
         <is>
           <t>45m2</t>
         </is>
       </c>
-      <c r="J68" s="6" t="inlineStr">
+      <c r="J98" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K68" s="6" t="inlineStr">
+      <c r="K98" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="L68" s="7" t="inlineStr">
+      <c r="L98" s="7" t="inlineStr">
         <is>
           <t>Tan Thanh, P.12, Q.5</t>
         </is>
       </c>
-      <c r="M68" s="7" t="inlineStr">
+      <c r="M98" s="7" t="inlineStr">
         <is>
           <t>Q.5</t>
         </is>
       </c>
-      <c r="N68" s="7" t="inlineStr">
+      <c r="N98" s="7" t="inlineStr">
         <is>
           <t>Mo ban 323 can, gia 80-90tr/m2</t>
         </is>
       </c>
-      <c r="O68" s="6" t="inlineStr"/>
-      <c r="P68" s="7" t="inlineStr"/>
-      <c r="Q68" s="8" t="inlineStr">
+      <c r="O98" s="6" t="inlineStr"/>
+      <c r="P98" s="7" t="inlineStr"/>
+      <c r="Q98" s="8" t="inlineStr">
         <is>
           <t>Xem BDS</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="16" t="n">
-        <v>68</v>
-      </c>
-      <c r="B69" s="17" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="16" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="17" t="inlineStr">
         <is>
           <t>Chung cu Le Thi Rieng</t>
         </is>
       </c>
-      <c r="C69" s="17" t="inlineStr">
+      <c r="C99" s="17" t="inlineStr">
         <is>
           <t>Chung cu</t>
         </is>
       </c>
-      <c r="D69" s="17" t="inlineStr">
+      <c r="D99" s="17" t="inlineStr">
         <is>
           <t>3.8 ty</t>
         </is>
       </c>
-      <c r="E69" s="16" t="inlineStr">
+      <c r="E99" s="16" t="inlineStr">
         <is>
           <t>57.1</t>
         </is>
       </c>
-      <c r="F69" s="19" t="inlineStr">
+      <c r="F99" s="31" t="inlineStr">
         <is>
           <t>Thap</t>
         </is>
       </c>
-      <c r="G69" s="16" t="inlineStr"/>
-      <c r="H69" s="17" t="inlineStr"/>
-      <c r="I69" s="17" t="inlineStr">
+      <c r="G99" s="16" t="inlineStr"/>
+      <c r="H99" s="17" t="inlineStr"/>
+      <c r="I99" s="17" t="inlineStr">
         <is>
           <t>66.5m2</t>
         </is>
       </c>
-      <c r="J69" s="16" t="inlineStr">
+      <c r="J99" s="16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K69" s="16" t="inlineStr">
+      <c r="K99" s="16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="L69" s="17" t="inlineStr">
+      <c r="L99" s="17" t="inlineStr">
         <is>
           <t>Le Thi Rieng, P.15, Q.10</t>
         </is>
       </c>
-      <c r="M69" s="17" t="inlineStr">
+      <c r="M99" s="17" t="inlineStr">
         <is>
           <t>Q.10</t>
         </is>
       </c>
-      <c r="N69" s="17" t="inlineStr">
+      <c r="N99" s="17" t="inlineStr">
         <is>
           <t>Thang may, so hong rieng, sat tuyen Metro</t>
         </is>
       </c>
-      <c r="O69" s="16" t="inlineStr"/>
-      <c r="P69" s="17" t="inlineStr"/>
-      <c r="Q69" s="18" t="inlineStr">
+      <c r="O99" s="16" t="inlineStr"/>
+      <c r="P99" s="17" t="inlineStr"/>
+      <c r="Q99" s="18" t="inlineStr">
         <is>
           <t>Xem BDS</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="16" t="n">
-        <v>69</v>
-      </c>
-      <c r="B70" s="17" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="16" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="17" t="inlineStr">
         <is>
           <t>CC Ly Thuong Kiet Q10</t>
         </is>
       </c>
-      <c r="C70" s="17" t="inlineStr">
+      <c r="C100" s="17" t="inlineStr">
         <is>
           <t>Chung cu</t>
         </is>
       </c>
-      <c r="D70" s="17" t="inlineStr">
+      <c r="D100" s="17" t="inlineStr">
         <is>
           <t>3 ty</t>
         </is>
       </c>
-      <c r="E70" s="16" t="inlineStr">
+      <c r="E100" s="16" t="inlineStr">
         <is>
           <t>60.0</t>
         </is>
       </c>
-      <c r="F70" s="19" t="inlineStr">
+      <c r="F100" s="31" t="inlineStr">
         <is>
           <t>Thap</t>
         </is>
       </c>
-      <c r="G70" s="16" t="inlineStr"/>
-      <c r="H70" s="17" t="inlineStr"/>
-      <c r="I70" s="17" t="inlineStr">
+      <c r="G100" s="16" t="inlineStr"/>
+      <c r="H100" s="17" t="inlineStr"/>
+      <c r="I100" s="17" t="inlineStr">
         <is>
           <t>50m2</t>
         </is>
       </c>
-      <c r="J70" s="16" t="inlineStr">
+      <c r="J100" s="16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K70" s="16" t="inlineStr">
+      <c r="K100" s="16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="L70" s="17" t="inlineStr">
+      <c r="L100" s="17" t="inlineStr">
         <is>
           <t>Ly Thuong Kiet, P.7, Q.10</t>
         </is>
       </c>
-      <c r="M70" s="17" t="inlineStr">
+      <c r="M100" s="17" t="inlineStr">
         <is>
           <t>Q.10</t>
         </is>
       </c>
-      <c r="N70" s="17" t="inlineStr">
+      <c r="N100" s="17" t="inlineStr">
         <is>
           <t>Thang may, chinh chu</t>
         </is>
       </c>
-      <c r="O70" s="16" t="inlineStr"/>
-      <c r="P70" s="17" t="inlineStr"/>
-      <c r="Q70" s="18" t="inlineStr">
+      <c r="O100" s="16" t="inlineStr"/>
+      <c r="P100" s="17" t="inlineStr"/>
+      <c r="Q100" s="18" t="inlineStr">
         <is>
           <t>Xem BDS</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="16" t="n">
-        <v>70</v>
-      </c>
-      <c r="B71" s="17" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="16" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="17" t="inlineStr">
         <is>
           <t>Cao oc Ngo Gia Tu</t>
         </is>
       </c>
-      <c r="C71" s="17" t="inlineStr">
+      <c r="C101" s="17" t="inlineStr">
         <is>
           <t>Chung cu</t>
         </is>
       </c>
-      <c r="D71" s="17" t="inlineStr">
+      <c r="D101" s="17" t="inlineStr">
         <is>
           <t>3.9 ty</t>
         </is>
       </c>
-      <c r="E71" s="16" t="inlineStr">
+      <c r="E101" s="16" t="inlineStr">
         <is>
           <t>59.6</t>
         </is>
       </c>
-      <c r="F71" s="19" t="inlineStr">
+      <c r="F101" s="31" t="inlineStr">
         <is>
           <t>Thap</t>
         </is>
       </c>
-      <c r="G71" s="16" t="inlineStr"/>
-      <c r="H71" s="17" t="inlineStr"/>
-      <c r="I71" s="17" t="inlineStr">
+      <c r="G101" s="16" t="inlineStr"/>
+      <c r="H101" s="17" t="inlineStr"/>
+      <c r="I101" s="17" t="inlineStr">
         <is>
           <t>65.4m2</t>
         </is>
       </c>
-      <c r="J71" s="16" t="inlineStr">
+      <c r="J101" s="16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K71" s="16" t="inlineStr">
+      <c r="K101" s="16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="L71" s="17" t="inlineStr">
+      <c r="L101" s="17" t="inlineStr">
         <is>
           <t>Ngo Gia Tu, P.3, Q.10</t>
         </is>
       </c>
-      <c r="M71" s="17" t="inlineStr">
+      <c r="M101" s="17" t="inlineStr">
         <is>
           <t>Q.10</t>
         </is>
       </c>
-      <c r="N71" s="17" t="inlineStr">
+      <c r="N101" s="17" t="inlineStr">
         <is>
           <t>Goc tang trung, cao oc 25 tang, SHR</t>
         </is>
       </c>
-      <c r="O71" s="16" t="inlineStr"/>
-      <c r="P71" s="17" t="inlineStr"/>
-      <c r="Q71" s="18" t="inlineStr">
+      <c r="O101" s="16" t="inlineStr"/>
+      <c r="P101" s="17" t="inlineStr"/>
+      <c r="Q101" s="18" t="inlineStr">
         <is>
           <t>Xem BDS</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="16" t="n">
-        <v>71</v>
-      </c>
-      <c r="B72" s="17" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="16" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="17" t="inlineStr">
         <is>
           <t>Chung cu Nguyen Kim</t>
         </is>
       </c>
-      <c r="C72" s="17" t="inlineStr">
+      <c r="C102" s="17" t="inlineStr">
         <is>
           <t>Chung cu</t>
         </is>
       </c>
-      <c r="D72" s="17" t="inlineStr">
+      <c r="D102" s="17" t="inlineStr">
         <is>
           <t>3.45 ty</t>
         </is>
       </c>
-      <c r="E72" s="16" t="inlineStr">
+      <c r="E102" s="16" t="inlineStr">
         <is>
           <t>57.5</t>
         </is>
       </c>
-      <c r="F72" s="19" t="inlineStr">
+      <c r="F102" s="31" t="inlineStr">
         <is>
           <t>Thap</t>
         </is>
       </c>
-      <c r="G72" s="16" t="inlineStr"/>
-      <c r="H72" s="17" t="inlineStr"/>
-      <c r="I72" s="17" t="inlineStr">
+      <c r="G102" s="16" t="inlineStr"/>
+      <c r="H102" s="17" t="inlineStr"/>
+      <c r="I102" s="17" t="inlineStr">
         <is>
           <t>60m2</t>
         </is>
       </c>
-      <c r="J72" s="16" t="inlineStr">
+      <c r="J102" s="16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K72" s="16" t="inlineStr">
+      <c r="K102" s="16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="L72" s="17" t="inlineStr">
+      <c r="L102" s="17" t="inlineStr">
         <is>
           <t>Nguyen Kim, P.7, Q.10</t>
         </is>
       </c>
-      <c r="M72" s="17" t="inlineStr">
+      <c r="M102" s="17" t="inlineStr">
         <is>
           <t>Q.10</t>
         </is>
       </c>
-      <c r="N72" s="17" t="inlineStr">
+      <c r="N102" s="17" t="inlineStr">
         <is>
           <t>Suat tai dinh cu Q.10</t>
         </is>
       </c>
-      <c r="O72" s="16" t="inlineStr"/>
-      <c r="P72" s="17" t="inlineStr"/>
-      <c r="Q72" s="18" t="inlineStr">
+      <c r="O102" s="16" t="inlineStr"/>
+      <c r="P102" s="17" t="inlineStr"/>
+      <c r="Q102" s="18" t="inlineStr">
         <is>
           <t>Xem BDS</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="n">
-        <v>72</v>
-      </c>
-      <c r="B73" s="3" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
         <is>
           <t>Celadon City</t>
         </is>
       </c>
-      <c r="C73" s="3" t="inlineStr">
+      <c r="C103" s="3" t="inlineStr">
         <is>
           <t>Chung cu</t>
         </is>
       </c>
-      <c r="D73" s="3" t="inlineStr">
+      <c r="D103" s="3" t="inlineStr">
         <is>
           <t>6.85-13.1 ty</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>116.9</t>
         </is>
       </c>
-      <c r="F73" s="19" t="inlineStr">
+      <c r="F103" s="31" t="inlineStr">
         <is>
           <t>Thap</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="3" t="inlineStr"/>
-      <c r="I73" s="3" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="3" t="inlineStr"/>
+      <c r="I103" s="3" t="inlineStr">
         <is>
           <t>85,3 m²</t>
         </is>
       </c>
-      <c r="J73" s="2" t="inlineStr"/>
-      <c r="K73" s="2" t="inlineStr"/>
-      <c r="L73" s="3" t="inlineStr">
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="3" t="inlineStr">
         <is>
           <t>P. Sơn Kỳ, Tan Phu</t>
         </is>
       </c>
-      <c r="M73" s="3" t="inlineStr">
+      <c r="M103" s="3" t="inlineStr">
         <is>
           <t>Tan Phu</t>
         </is>
       </c>
-      <c r="N73" s="3" t="inlineStr">
+      <c r="N103" s="3" t="inlineStr">
         <is>
           <t>Alnata Plus full NT - 85.3m2 giá 7,4 tỷ có ô xe + full NT</t>
         </is>
       </c>
-      <c r="O73" s="2" t="inlineStr"/>
-      <c r="P73" s="3" t="inlineStr"/>
-      <c r="Q73" s="5" t="inlineStr">
+      <c r="O103" s="2" t="inlineStr"/>
+      <c r="P103" s="3" t="inlineStr"/>
+      <c r="Q103" s="5" t="inlineStr">
         <is>
           <t>Xem BDS</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="B74" s="3" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
         <is>
           <t>Diamond Alnata Plus</t>
         </is>
       </c>
-      <c r="C74" s="3" t="inlineStr">
+      <c r="C104" s="3" t="inlineStr">
         <is>
           <t>Chung cu</t>
         </is>
       </c>
-      <c r="D74" s="3" t="inlineStr">
+      <c r="D104" s="3" t="inlineStr">
         <is>
           <t>7.4-7.6 ty</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>91.5</t>
         </is>
       </c>
-      <c r="F74" s="19" t="inlineStr">
+      <c r="F104" s="31" t="inlineStr">
         <is>
           <t>Thap</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="3" t="inlineStr"/>
-      <c r="I74" s="3" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="3" t="inlineStr"/>
+      <c r="I104" s="3" t="inlineStr">
         <is>
           <t>79-85m2</t>
         </is>
       </c>
-      <c r="J74" s="2" t="inlineStr">
+      <c r="J104" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K74" s="2" t="inlineStr">
+      <c r="K104" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="L74" s="3" t="inlineStr">
+      <c r="L104" s="3" t="inlineStr">
         <is>
           <t>P. Son Ky, Tan Phu</t>
         </is>
       </c>
-      <c r="M74" s="3" t="inlineStr">
+      <c r="M104" s="3" t="inlineStr">
         <is>
           <t>Tan Phu</t>
         </is>
       </c>
-      <c r="N74" s="3" t="inlineStr">
+      <c r="N104" s="3" t="inlineStr">
         <is>
           <t>Celadon City</t>
         </is>
       </c>
-      <c r="O74" s="2" t="inlineStr"/>
-      <c r="P74" s="3" t="inlineStr"/>
-      <c r="Q74" s="5" t="inlineStr">
+      <c r="O104" s="2" t="inlineStr"/>
+      <c r="P104" s="3" t="inlineStr"/>
+      <c r="Q104" s="5" t="inlineStr">
         <is>
           <t>Xem BDS</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="n">
-        <v>74</v>
-      </c>
-      <c r="B75" s="3" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
         <is>
           <t>The Glen Celadon City</t>
         </is>
       </c>
-      <c r="C75" s="3" t="inlineStr">
+      <c r="C105" s="3" t="inlineStr">
         <is>
           <t>Chung cu</t>
         </is>
       </c>
-      <c r="D75" s="3" t="inlineStr">
+      <c r="D105" s="3" t="inlineStr">
         <is>
           <t>23 ty</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>76.7</t>
         </is>
       </c>
-      <c r="F75" s="19" t="inlineStr">
+      <c r="F105" s="31" t="inlineStr">
         <is>
           <t>Thap</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="3" t="inlineStr"/>
-      <c r="I75" s="3" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="3" t="inlineStr"/>
+      <c r="I105" s="3" t="inlineStr">
         <is>
           <t>299.9m2</t>
         </is>
       </c>
-      <c r="J75" s="2" t="inlineStr">
+      <c r="J105" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="K75" s="2" t="inlineStr">
+      <c r="K105" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="L75" s="3" t="inlineStr">
+      <c r="L105" s="3" t="inlineStr">
         <is>
           <t>P. Son Ky, Tan Phu</t>
         </is>
       </c>
-      <c r="M75" s="3" t="inlineStr">
+      <c r="M105" s="3" t="inlineStr">
         <is>
           <t>Tan Phu</t>
         </is>
       </c>
-      <c r="N75" s="3" t="inlineStr">
+      <c r="N105" s="3" t="inlineStr">
         <is>
           <t>Celadon City - duplex</t>
         </is>
       </c>
-      <c r="O75" s="2" t="inlineStr"/>
-      <c r="P75" s="3" t="inlineStr"/>
-      <c r="Q75" s="5" t="inlineStr">
+      <c r="O105" s="2" t="inlineStr"/>
+      <c r="P105" s="3" t="inlineStr"/>
+      <c r="Q105" s="5" t="inlineStr">
         <is>
           <t>Xem BDS</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="B76" s="3" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
         <is>
           <t>Fortuna Vuon Lai</t>
         </is>
       </c>
-      <c r="C76" s="3" t="inlineStr">
+      <c r="C106" s="3" t="inlineStr">
         <is>
           <t>Chung cu</t>
         </is>
       </c>
-      <c r="D76" s="3" t="inlineStr">
+      <c r="D106" s="3" t="inlineStr">
         <is>
           <t>3.35 ty</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>43.4</t>
         </is>
       </c>
-      <c r="F76" s="19" t="inlineStr">
+      <c r="F106" s="31" t="inlineStr">
         <is>
           <t>Thap</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="3" t="inlineStr"/>
-      <c r="I76" s="3" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="3" t="inlineStr"/>
+      <c r="I106" s="3" t="inlineStr">
         <is>
           <t>77,2 m²</t>
         </is>
       </c>
-      <c r="J76" s="2" t="inlineStr"/>
-      <c r="K76" s="2" t="inlineStr"/>
-      <c r="L76" s="3" t="inlineStr">
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="3" t="inlineStr">
         <is>
           <t>P. Phú Thọ Hòa, Tan Phu</t>
         </is>
       </c>
-      <c r="M76" s="3" t="inlineStr">
+      <c r="M106" s="3" t="inlineStr">
         <is>
           <t>Tan Phu</t>
         </is>
       </c>
-      <c r="N76" s="3" t="inlineStr">
+      <c r="N106" s="3" t="inlineStr">
         <is>
           <t>Cần bán Fortuna Kim Hồng 77,2m2, 2pn, 3,35 tỷ đường Vườn Lài Tân Phú</t>
         </is>
       </c>
-      <c r="O76" s="2" t="inlineStr"/>
-      <c r="P76" s="3" t="inlineStr"/>
-      <c r="Q76" s="5" t="inlineStr">
+      <c r="O106" s="2" t="inlineStr"/>
+      <c r="P106" s="3" t="inlineStr"/>
+      <c r="Q106" s="5" t="inlineStr">
         <is>
           <t>Xem BDS</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="n">
-        <v>76</v>
-      </c>
-      <c r="B77" s="3" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
         <is>
           <t>Khu đô thị TOD đầu tiên tại Hồ Chí Minh chuẩn Nhật Bản. LH 0</t>
         </is>
       </c>
-      <c r="C77" s="3" t="inlineStr">
+      <c r="C107" s="3" t="inlineStr">
         <is>
           <t>Chung cu</t>
         </is>
       </c>
-      <c r="D77" s="3" t="inlineStr">
+      <c r="D107" s="3" t="inlineStr">
         <is>
           <t>Đô thị TOD One Era</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr"/>
-      <c r="F77" s="19" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr"/>
+      <c r="F107" s="31" t="inlineStr">
         <is>
           <t>Thap</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="3" t="inlineStr"/>
-      <c r="I77" s="3" t="inlineStr"/>
-      <c r="J77" s="2" t="inlineStr"/>
-      <c r="K77" s="2" t="inlineStr"/>
-      <c r="L77" s="3" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="3" t="inlineStr"/>
+      <c r="I107" s="3" t="inlineStr"/>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="3" t="inlineStr">
         <is>
           <t>Tan Phu</t>
         </is>
       </c>
-      <c r="M77" s="3" t="inlineStr">
+      <c r="M107" s="3" t="inlineStr">
         <is>
           <t>Tan Phu</t>
         </is>
       </c>
-      <c r="N77" s="3" t="inlineStr">
+      <c r="N107" s="3" t="inlineStr">
         <is>
           <t>Khu đô thị TOD đầu tiên tại Hồ Chí Minh chuẩn Nhật Bản. LH 0909268094</t>
         </is>
       </c>
-      <c r="O77" s="2" t="inlineStr"/>
-      <c r="P77" s="3" t="inlineStr"/>
-      <c r="Q77" s="5" t="inlineStr">
+      <c r="O107" s="2" t="inlineStr"/>
+      <c r="P107" s="3" t="inlineStr"/>
+      <c r="Q107" s="5" t="inlineStr">
         <is>
           <t>Xem BDS</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="6" t="n">
-        <v>77</v>
-      </c>
-      <c r="B78" s="7" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="6" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="7" t="inlineStr">
         <is>
           <t>Botanica Premier</t>
         </is>
       </c>
-      <c r="C78" s="7" t="inlineStr">
+      <c r="C108" s="7" t="inlineStr">
         <is>
           <t>Chung cu</t>
         </is>
       </c>
-      <c r="D78" s="7" t="inlineStr">
+      <c r="D108" s="7" t="inlineStr">
         <is>
           <t>4.5-7.8 ty</t>
         </is>
       </c>
-      <c r="E78" s="6" t="inlineStr">
+      <c r="E108" s="6" t="inlineStr">
         <is>
           <t>87.9</t>
         </is>
       </c>
-      <c r="F78" s="19" t="inlineStr">
+      <c r="F108" s="31" t="inlineStr">
         <is>
           <t>Thap</t>
         </is>
       </c>
-      <c r="G78" s="6" t="inlineStr"/>
-      <c r="H78" s="7" t="inlineStr"/>
-      <c r="I78" s="7" t="inlineStr">
+      <c r="G108" s="6" t="inlineStr"/>
+      <c r="H108" s="7" t="inlineStr"/>
+      <c r="I108" s="7" t="inlineStr">
         <is>
           <t>70 m²</t>
         </is>
       </c>
-      <c r="J78" s="6" t="inlineStr"/>
-      <c r="K78" s="6" t="inlineStr"/>
-      <c r="L78" s="7" t="inlineStr">
+      <c r="J108" s="6" t="inlineStr"/>
+      <c r="K108" s="6" t="inlineStr"/>
+      <c r="L108" s="7" t="inlineStr">
         <is>
           <t>Phường 2, Tan Binh</t>
         </is>
       </c>
-      <c r="M78" s="7" t="inlineStr">
+      <c r="M108" s="7" t="inlineStr">
         <is>
           <t>Tan Binh</t>
         </is>
       </c>
-      <c r="N78" s="7" t="inlineStr">
+      <c r="N108" s="7" t="inlineStr">
         <is>
           <t>Giảm 400Tr: Bán Gấp 2PN Botanica Premier - Tầng Cao+ View Hồng Hà - Chỉ 5.9 tỷ</t>
         </is>
       </c>
-      <c r="O78" s="6" t="inlineStr"/>
-      <c r="P78" s="7" t="inlineStr"/>
-      <c r="Q78" s="8" t="inlineStr">
+      <c r="O108" s="6" t="inlineStr"/>
+      <c r="P108" s="7" t="inlineStr"/>
+      <c r="Q108" s="8" t="inlineStr">
         <is>
           <t>Xem BDS</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="6" t="n">
-        <v>78</v>
-      </c>
-      <c r="B79" s="7" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="6" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="7" t="inlineStr">
         <is>
           <t>Bau Cat Ii</t>
         </is>
       </c>
-      <c r="C79" s="7" t="inlineStr">
+      <c r="C109" s="7" t="inlineStr">
         <is>
           <t>Chung cu</t>
         </is>
       </c>
-      <c r="D79" s="7" t="inlineStr">
+      <c r="D109" s="7" t="inlineStr">
         <is>
           <t>2.6 ty</t>
         </is>
       </c>
-      <c r="E79" s="6" t="inlineStr">
+      <c r="E109" s="6" t="inlineStr">
         <is>
           <t>46.8</t>
         </is>
       </c>
-      <c r="F79" s="19" t="inlineStr">
+      <c r="F109" s="31" t="inlineStr">
         <is>
           <t>Thap</t>
         </is>
       </c>
-      <c r="G79" s="6" t="inlineStr"/>
-      <c r="H79" s="7" t="inlineStr"/>
-      <c r="I79" s="7" t="inlineStr">
+      <c r="G109" s="6" t="inlineStr"/>
+      <c r="H109" s="7" t="inlineStr"/>
+      <c r="I109" s="7" t="inlineStr">
         <is>
           <t>55,55 m²</t>
         </is>
       </c>
-      <c r="J79" s="6" t="inlineStr"/>
-      <c r="K79" s="6" t="inlineStr"/>
-      <c r="L79" s="7" t="inlineStr">
+      <c r="J109" s="6" t="inlineStr"/>
+      <c r="K109" s="6" t="inlineStr"/>
+      <c r="L109" s="7" t="inlineStr">
         <is>
           <t>Phường 10, Tan Binh</t>
         </is>
       </c>
-      <c r="M79" s="7" t="inlineStr">
+      <c r="M109" s="7" t="inlineStr">
         <is>
           <t>Tan Binh</t>
         </is>
       </c>
-      <c r="N79" s="7" t="inlineStr">
+      <c r="N109" s="7" t="inlineStr">
         <is>
           <t>Thang máy - thẻ từ, cách Bàu Cát 1,5km giá chỉ 2,6 tỷ, 55.55m2, SHR</t>
         </is>
       </c>
-      <c r="O79" s="6" t="inlineStr"/>
-      <c r="P79" s="7" t="inlineStr"/>
-      <c r="Q79" s="8" t="inlineStr">
+      <c r="O109" s="6" t="inlineStr"/>
+      <c r="P109" s="7" t="inlineStr"/>
+      <c r="Q109" s="8" t="inlineStr">
         <is>
           <t>Xem BDS</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="6" t="n">
-        <v>79</v>
-      </c>
-      <c r="B80" s="7" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="6" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="7" t="inlineStr">
         <is>
           <t>Khu đô thị TOD đầu tiên tại Hồ Chí Minh chuẩn Nhật Bản. LH 0</t>
         </is>
       </c>
-      <c r="C80" s="7" t="inlineStr">
+      <c r="C110" s="7" t="inlineStr">
         <is>
           <t>Chung cu</t>
         </is>
       </c>
-      <c r="D80" s="7" t="inlineStr">
+      <c r="D110" s="7" t="inlineStr">
         <is>
           <t>Đô thị TOD One Era</t>
         </is>
       </c>
-      <c r="E80" s="6" t="inlineStr"/>
-      <c r="F80" s="19" t="inlineStr">
+      <c r="E110" s="6" t="inlineStr"/>
+      <c r="F110" s="31" t="inlineStr">
         <is>
           <t>Thap</t>
         </is>
       </c>
-      <c r="G80" s="6" t="inlineStr"/>
-      <c r="H80" s="7" t="inlineStr"/>
-      <c r="I80" s="7" t="inlineStr"/>
-      <c r="J80" s="6" t="inlineStr"/>
-      <c r="K80" s="6" t="inlineStr"/>
-      <c r="L80" s="7" t="inlineStr">
+      <c r="G110" s="6" t="inlineStr"/>
+      <c r="H110" s="7" t="inlineStr"/>
+      <c r="I110" s="7" t="inlineStr"/>
+      <c r="J110" s="6" t="inlineStr"/>
+      <c r="K110" s="6" t="inlineStr"/>
+      <c r="L110" s="7" t="inlineStr">
         <is>
           <t>Tan Binh</t>
         </is>
       </c>
-      <c r="M80" s="7" t="inlineStr">
+      <c r="M110" s="7" t="inlineStr">
         <is>
           <t>Tan Binh</t>
         </is>
       </c>
-      <c r="N80" s="7" t="inlineStr">
+      <c r="N110" s="7" t="inlineStr">
         <is>
           <t>Khu đô thị TOD đầu tiên tại Hồ Chí Minh chuẩn Nhật Bản. LH 0909268094</t>
         </is>
       </c>
-      <c r="O80" s="6" t="inlineStr"/>
-      <c r="P80" s="7" t="inlineStr"/>
-      <c r="Q80" s="8" t="inlineStr">
+      <c r="O110" s="6" t="inlineStr"/>
+      <c r="P110" s="7" t="inlineStr"/>
+      <c r="Q110" s="8" t="inlineStr">
         <is>
           <t>Xem BDS</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="9" t="n">
-        <v>80</v>
-      </c>
-      <c r="B81" s="10" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="9" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="10" t="inlineStr">
         <is>
           <t>HQC Plaza</t>
         </is>
       </c>
-      <c r="C81" s="10" t="inlineStr">
+      <c r="C111" s="10" t="inlineStr">
         <is>
           <t>Chung cu</t>
         </is>
       </c>
-      <c r="D81" s="10" t="inlineStr">
+      <c r="D111" s="10" t="inlineStr">
         <is>
           <t>1,15 tỷ</t>
         </is>
       </c>
-      <c r="E81" s="9" t="inlineStr">
+      <c r="E111" s="9" t="inlineStr">
         <is>
           <t>20.9</t>
         </is>
       </c>
-      <c r="F81" s="19" t="inlineStr">
+      <c r="F111" s="31" t="inlineStr">
         <is>
           <t>Thap</t>
         </is>
       </c>
-      <c r="G81" s="9" t="inlineStr"/>
-      <c r="H81" s="10" t="inlineStr"/>
-      <c r="I81" s="10" t="inlineStr">
+      <c r="G111" s="9" t="inlineStr"/>
+      <c r="H111" s="10" t="inlineStr"/>
+      <c r="I111" s="10" t="inlineStr">
         <is>
           <t>55 m²</t>
         </is>
       </c>
-      <c r="J81" s="9" t="inlineStr"/>
-      <c r="K81" s="9" t="inlineStr"/>
-      <c r="L81" s="10" t="inlineStr">
+      <c r="J111" s="9" t="inlineStr"/>
+      <c r="K111" s="9" t="inlineStr"/>
+      <c r="L111" s="10" t="inlineStr">
         <is>
           <t>X. An Phú Tây, Binh Chanh</t>
         </is>
       </c>
-      <c r="M81" s="10" t="inlineStr">
+      <c r="M111" s="10" t="inlineStr">
         <is>
           <t>Binh Chanh</t>
         </is>
       </c>
-      <c r="N81" s="10" t="inlineStr">
+      <c r="N111" s="10" t="inlineStr">
         <is>
           <t>Bán căn tầng 6 tại chung cư HQC Plaza, 55m2 2PN nhà đẹp, mua ở ngay, giá 1,150 tỷ full chi phí</t>
         </is>
       </c>
-      <c r="O81" s="9" t="inlineStr"/>
-      <c r="P81" s="10" t="inlineStr"/>
-      <c r="Q81" s="11" t="inlineStr">
+      <c r="O111" s="9" t="inlineStr"/>
+      <c r="P111" s="10" t="inlineStr"/>
+      <c r="Q111" s="11" t="inlineStr">
         <is>
           <t>Xem BDS</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="9" t="n">
-        <v>81</v>
-      </c>
-      <c r="B82" s="10" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="9" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="10" t="inlineStr">
         <is>
           <t>Chung cư NOXH LA Home, tổng giá trị từ 385 triệu/căn, vốn ch</t>
         </is>
       </c>
-      <c r="C82" s="10" t="inlineStr">
+      <c r="C112" s="10" t="inlineStr">
         <is>
           <t>Chung cu</t>
         </is>
       </c>
-      <c r="D82" s="10" t="inlineStr">
+      <c r="D112" s="10" t="inlineStr">
         <is>
           <t>Chủ Đầu Tư Prodezi Long An</t>
         </is>
       </c>
-      <c r="E82" s="9" t="inlineStr"/>
-      <c r="F82" s="19" t="inlineStr">
+      <c r="E112" s="9" t="inlineStr"/>
+      <c r="F112" s="31" t="inlineStr">
         <is>
           <t>Thap</t>
         </is>
       </c>
-      <c r="G82" s="9" t="inlineStr"/>
-      <c r="H82" s="10" t="inlineStr"/>
-      <c r="I82" s="10" t="inlineStr"/>
-      <c r="J82" s="9" t="inlineStr"/>
-      <c r="K82" s="9" t="inlineStr"/>
-      <c r="L82" s="10" t="inlineStr">
+      <c r="G112" s="9" t="inlineStr"/>
+      <c r="H112" s="10" t="inlineStr"/>
+      <c r="I112" s="10" t="inlineStr"/>
+      <c r="J112" s="9" t="inlineStr"/>
+      <c r="K112" s="9" t="inlineStr"/>
+      <c r="L112" s="10" t="inlineStr">
         <is>
           <t>Binh Chanh</t>
         </is>
       </c>
-      <c r="M82" s="10" t="inlineStr">
+      <c r="M112" s="10" t="inlineStr">
         <is>
           <t>Binh Chanh</t>
         </is>
       </c>
-      <c r="N82" s="10" t="inlineStr">
+      <c r="N112" s="10" t="inlineStr">
         <is>
           <t>Chung cư NOXH LA Home, tổng giá trị từ 385 triệu/căn, vốn chỉ 100 triệu</t>
         </is>
       </c>
-      <c r="O82" s="9" t="inlineStr"/>
-      <c r="P82" s="10" t="inlineStr"/>
-      <c r="Q82" s="11" t="inlineStr">
+      <c r="O112" s="9" t="inlineStr"/>
+      <c r="P112" s="10" t="inlineStr"/>
+      <c r="Q112" s="11" t="inlineStr">
         <is>
           <t>Xem BDS</t>
         </is>
       </c>
     </row>
+    <row r="113">
+      <c r="A113" s="25" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="26" t="inlineStr">
+        <is>
+          <t>H3 Hoang Dieu</t>
+        </is>
+      </c>
+      <c r="C113" s="26" t="inlineStr">
+        <is>
+          <t>Chung cu</t>
+        </is>
+      </c>
+      <c r="D113" s="26" t="inlineStr">
+        <is>
+          <t>4.3 ty</t>
+        </is>
+      </c>
+      <c r="E113" s="25" t="inlineStr">
+        <is>
+          <t>72.9</t>
+        </is>
+      </c>
+      <c r="F113" s="31" t="inlineStr">
+        <is>
+          <t>Thap</t>
+        </is>
+      </c>
+      <c r="G113" s="25" t="inlineStr"/>
+      <c r="H113" s="26" t="inlineStr"/>
+      <c r="I113" s="26" t="inlineStr">
+        <is>
+          <t>59m2</t>
+        </is>
+      </c>
+      <c r="J113" s="25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K113" s="25" t="inlineStr"/>
+      <c r="L113" s="26" t="inlineStr">
+        <is>
+          <t>Hoang Dieu, P. Khanh Hoi, Q.4</t>
+        </is>
+      </c>
+      <c r="M113" s="26" t="inlineStr">
+        <is>
+          <t>Q.4</t>
+        </is>
+      </c>
+      <c r="N113" s="26" t="inlineStr">
+        <is>
+          <t>Giap Quan 1, view thanh pho</t>
+        </is>
+      </c>
+      <c r="O113" s="25" t="inlineStr"/>
+      <c r="P113" s="26" t="inlineStr"/>
+      <c r="Q113" s="27" t="inlineStr">
+        <is>
+          <t>Xem BDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="25" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="26" t="inlineStr">
+        <is>
+          <t>The Gold View</t>
+        </is>
+      </c>
+      <c r="C114" s="26" t="inlineStr">
+        <is>
+          <t>Chung cu</t>
+        </is>
+      </c>
+      <c r="D114" s="26" t="inlineStr">
+        <is>
+          <t>3.2 ty</t>
+        </is>
+      </c>
+      <c r="E114" s="25" t="inlineStr">
+        <is>
+          <t>44.4</t>
+        </is>
+      </c>
+      <c r="F114" s="31" t="inlineStr">
+        <is>
+          <t>Thap</t>
+        </is>
+      </c>
+      <c r="G114" s="25" t="inlineStr"/>
+      <c r="H114" s="26" t="inlineStr"/>
+      <c r="I114" s="26" t="inlineStr">
+        <is>
+          <t>72m2</t>
+        </is>
+      </c>
+      <c r="J114" s="25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K114" s="25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L114" s="26" t="inlineStr">
+        <is>
+          <t>Ben Van Don, P. Vinh Hoi, Q.4</t>
+        </is>
+      </c>
+      <c r="M114" s="26" t="inlineStr">
+        <is>
+          <t>Q.4</t>
+        </is>
+      </c>
+      <c r="N114" s="26" t="inlineStr">
+        <is>
+          <t>TNR Holdings, 2PN-2WC</t>
+        </is>
+      </c>
+      <c r="O114" s="25" t="inlineStr"/>
+      <c r="P114" s="26" t="inlineStr"/>
+      <c r="Q114" s="27" t="inlineStr">
+        <is>
+          <t>Xem BDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="28" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="29" t="inlineStr">
+        <is>
+          <t>Eco Green Sai Gon</t>
+        </is>
+      </c>
+      <c r="C115" s="29" t="inlineStr">
+        <is>
+          <t>Chung cu</t>
+        </is>
+      </c>
+      <c r="D115" s="29" t="inlineStr">
+        <is>
+          <t>4.8-5 ty</t>
+        </is>
+      </c>
+      <c r="E115" s="28" t="inlineStr">
+        <is>
+          <t>93.3</t>
+        </is>
+      </c>
+      <c r="F115" s="31" t="inlineStr">
+        <is>
+          <t>Thap</t>
+        </is>
+      </c>
+      <c r="G115" s="28" t="inlineStr"/>
+      <c r="H115" s="29" t="inlineStr"/>
+      <c r="I115" s="29" t="inlineStr">
+        <is>
+          <t>52-53m2</t>
+        </is>
+      </c>
+      <c r="J115" s="28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K115" s="28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L115" s="29" t="inlineStr">
+        <is>
+          <t>Nguyen Van Linh, P. Tan Thuan Tay, Q.7</t>
+        </is>
+      </c>
+      <c r="M115" s="29" t="inlineStr">
+        <is>
+          <t>Q.7</t>
+        </is>
+      </c>
+      <c r="N115" s="29" t="inlineStr">
+        <is>
+          <t>Xuan Mai Corp</t>
+        </is>
+      </c>
+      <c r="O115" s="28" t="inlineStr"/>
+      <c r="P115" s="29" t="inlineStr"/>
+      <c r="Q115" s="30" t="inlineStr">
+        <is>
+          <t>Xem BDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="28" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="29" t="inlineStr">
+        <is>
+          <t>Sunrise City</t>
+        </is>
+      </c>
+      <c r="C116" s="29" t="inlineStr">
+        <is>
+          <t>Chung cu</t>
+        </is>
+      </c>
+      <c r="D116" s="29" t="inlineStr">
+        <is>
+          <t>3.3 ty</t>
+        </is>
+      </c>
+      <c r="E116" s="28" t="inlineStr">
+        <is>
+          <t>94.3</t>
+        </is>
+      </c>
+      <c r="F116" s="31" t="inlineStr">
+        <is>
+          <t>Thap</t>
+        </is>
+      </c>
+      <c r="G116" s="28" t="inlineStr"/>
+      <c r="H116" s="29" t="inlineStr"/>
+      <c r="I116" s="29" t="inlineStr">
+        <is>
+          <t>35m2</t>
+        </is>
+      </c>
+      <c r="J116" s="28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K116" s="28" t="inlineStr"/>
+      <c r="L116" s="29" t="inlineStr">
+        <is>
+          <t>Nguyen Huu Tho, P. Tan Hung, Q.7</t>
+        </is>
+      </c>
+      <c r="M116" s="29" t="inlineStr">
+        <is>
+          <t>Q.7</t>
+        </is>
+      </c>
+      <c r="N116" s="29" t="inlineStr">
+        <is>
+          <t>Novaland, khu North</t>
+        </is>
+      </c>
+      <c r="O116" s="28" t="inlineStr"/>
+      <c r="P116" s="29" t="inlineStr"/>
+      <c r="Q116" s="30" t="inlineStr">
+        <is>
+          <t>Xem BDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="32" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="33" t="inlineStr">
+        <is>
+          <t>The Origami (Vinhomes Grand Park)</t>
+        </is>
+      </c>
+      <c r="C117" s="33" t="inlineStr">
+        <is>
+          <t>Chung cu</t>
+        </is>
+      </c>
+      <c r="D117" s="33" t="inlineStr">
+        <is>
+          <t>3.3-4.9 ty</t>
+        </is>
+      </c>
+      <c r="E117" s="32" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="F117" s="31" t="inlineStr">
+        <is>
+          <t>Thap</t>
+        </is>
+      </c>
+      <c r="G117" s="32" t="inlineStr"/>
+      <c r="H117" s="33" t="inlineStr"/>
+      <c r="I117" s="33" t="inlineStr">
+        <is>
+          <t>59-90m2</t>
+        </is>
+      </c>
+      <c r="J117" s="32" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="K117" s="32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L117" s="33" t="inlineStr">
+        <is>
+          <t>Long Binh, TP.Thu Duc (Q.9 cu)</t>
+        </is>
+      </c>
+      <c r="M117" s="33" t="inlineStr">
+        <is>
+          <t>Q.9</t>
+        </is>
+      </c>
+      <c r="N117" s="33" t="inlineStr">
+        <is>
+          <t>Vinhomes, view vuon Nhat, ho ca Koi</t>
+        </is>
+      </c>
+      <c r="O117" s="32" t="inlineStr"/>
+      <c r="P117" s="33" t="inlineStr"/>
+      <c r="Q117" s="34" t="inlineStr">
+        <is>
+          <t>Xem BDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="32" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="33" t="inlineStr">
+        <is>
+          <t>Lumiere Boulevard</t>
+        </is>
+      </c>
+      <c r="C118" s="33" t="inlineStr">
+        <is>
+          <t>Chung cu</t>
+        </is>
+      </c>
+      <c r="D118" s="33" t="inlineStr">
+        <is>
+          <t>4.6-4.7 ty</t>
+        </is>
+      </c>
+      <c r="E118" s="32" t="inlineStr">
+        <is>
+          <t>62.8</t>
+        </is>
+      </c>
+      <c r="F118" s="31" t="inlineStr">
+        <is>
+          <t>Thap</t>
+        </is>
+      </c>
+      <c r="G118" s="32" t="inlineStr"/>
+      <c r="H118" s="33" t="inlineStr"/>
+      <c r="I118" s="33" t="inlineStr">
+        <is>
+          <t>74m2</t>
+        </is>
+      </c>
+      <c r="J118" s="32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K118" s="32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L118" s="33" t="inlineStr">
+        <is>
+          <t>Long Binh, TP.Thu Duc (Q.9 cu)</t>
+        </is>
+      </c>
+      <c r="M118" s="33" t="inlineStr">
+        <is>
+          <t>Q.9</t>
+        </is>
+      </c>
+      <c r="N118" s="33" t="inlineStr">
+        <is>
+          <t>Masterise Homes, trong Vinhomes GP</t>
+        </is>
+      </c>
+      <c r="O118" s="32" t="inlineStr"/>
+      <c r="P118" s="33" t="inlineStr"/>
+      <c r="Q118" s="34" t="inlineStr">
+        <is>
+          <t>Xem BDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="9" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="10" t="inlineStr">
+        <is>
+          <t>Trellia Cove (Mizuki Park)</t>
+        </is>
+      </c>
+      <c r="C119" s="10" t="inlineStr">
+        <is>
+          <t>Chung cu</t>
+        </is>
+      </c>
+      <c r="D119" s="10" t="inlineStr">
+        <is>
+          <t>3.9-5 ty</t>
+        </is>
+      </c>
+      <c r="E119" s="9" t="inlineStr">
+        <is>
+          <t>64.5</t>
+        </is>
+      </c>
+      <c r="F119" s="31" t="inlineStr">
+        <is>
+          <t>Thap</t>
+        </is>
+      </c>
+      <c r="G119" s="9" t="inlineStr"/>
+      <c r="H119" s="10" t="inlineStr"/>
+      <c r="I119" s="10" t="inlineStr">
+        <is>
+          <t>59-79m2</t>
+        </is>
+      </c>
+      <c r="J119" s="9" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="K119" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L119" s="10" t="inlineStr">
+        <is>
+          <t>Nguyen Van Linh, X.Binh Hung, Binh Chanh</t>
+        </is>
+      </c>
+      <c r="M119" s="10" t="inlineStr">
+        <is>
+          <t>Binh Chanh</t>
+        </is>
+      </c>
+      <c r="N119" s="10" t="inlineStr">
+        <is>
+          <t>Nam Long, phan khu moi Mizuki Park</t>
+        </is>
+      </c>
+      <c r="O119" s="9" t="inlineStr"/>
+      <c r="P119" s="10" t="inlineStr"/>
+      <c r="Q119" s="11" t="inlineStr">
+        <is>
+          <t>Xem BDS</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q82"/>
+  <autoFilter ref="A1:Q119"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId2"/>
@@ -6189,6 +8693,43 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q80" r:id="rId79"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q81" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q119" r:id="rId118"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6200,7 +8741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F82"/>
+  <dimension ref="A1:F119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6244,2270 +8785,3306 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="20" t="inlineStr">
+      <c r="A2" s="35" t="inlineStr">
         <is>
           <t>RichStar</t>
         </is>
       </c>
-      <c r="B2" s="20" t="inlineStr">
+      <c r="B2" s="35" t="inlineStr">
         <is>
           <t>Tan Phu</t>
         </is>
       </c>
-      <c r="C2" s="20" t="n">
+      <c r="C2" s="35" t="n">
         <v>10.7727625</v>
       </c>
-      <c r="D2" s="20" t="n">
+      <c r="D2" s="35" t="n">
         <v>106.6267493</v>
       </c>
-      <c r="E2" s="20" t="inlineStr">
+      <c r="E2" s="35" t="inlineStr">
         <is>
           <t>3.3-3.6 ty</t>
         </is>
       </c>
-      <c r="F2" s="20" t="inlineStr">
+      <c r="F2" s="35" t="inlineStr">
         <is>
           <t>P. Hiệp Tân, Tan Phu</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="20" t="inlineStr">
+      <c r="A3" s="35" t="inlineStr">
         <is>
           <t>Phuc Yen</t>
         </is>
       </c>
-      <c r="B3" s="20" t="inlineStr">
+      <c r="B3" s="35" t="inlineStr">
         <is>
           <t>Tan Binh</t>
         </is>
       </c>
-      <c r="C3" s="20" t="n">
+      <c r="C3" s="35" t="n">
         <v>10.813</v>
       </c>
-      <c r="D3" s="20" t="n">
+      <c r="D3" s="35" t="n">
         <v>106.65884</v>
       </c>
-      <c r="E3" s="20" t="inlineStr">
+      <c r="E3" s="35" t="inlineStr">
         <is>
           <t>4.15-5.25 ty</t>
         </is>
       </c>
-      <c r="F3" s="20" t="inlineStr">
+      <c r="F3" s="35" t="inlineStr">
         <is>
           <t>Phường 15, Tan Binh</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="20" t="inlineStr">
+      <c r="A4" s="35" t="inlineStr">
         <is>
           <t>Sai Gon Intela</t>
         </is>
       </c>
-      <c r="B4" s="20" t="inlineStr">
+      <c r="B4" s="35" t="inlineStr">
         <is>
           <t>Binh Chanh</t>
         </is>
       </c>
-      <c r="C4" s="20" t="n">
+      <c r="C4" s="35" t="n">
         <v>10.7243911</v>
       </c>
-      <c r="D4" s="20" t="n">
+      <c r="D4" s="35" t="n">
         <v>106.5986942</v>
       </c>
-      <c r="E4" s="20" t="inlineStr">
+      <c r="E4" s="35" t="inlineStr">
         <is>
           <t>2.04-2.25 ty</t>
         </is>
       </c>
-      <c r="F4" s="20" t="inlineStr">
+      <c r="F4" s="35" t="inlineStr">
         <is>
           <t>X. Phong Phú, Binh Chanh</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="20" t="inlineStr">
+      <c r="A5" s="35" t="inlineStr">
         <is>
           <t>Lovera Vista</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="35" t="inlineStr">
         <is>
           <t>Binh Chanh</t>
         </is>
       </c>
-      <c r="C5" s="20" t="n">
+      <c r="C5" s="35" t="n">
         <v>10.6919182</v>
       </c>
-      <c r="D5" s="20" t="n">
+      <c r="D5" s="35" t="n">
         <v>106.6422011</v>
       </c>
-      <c r="E5" s="20" t="inlineStr">
+      <c r="E5" s="35" t="inlineStr">
         <is>
           <t>3.1-3.65 ty</t>
         </is>
       </c>
-      <c r="F5" s="20" t="inlineStr">
+      <c r="F5" s="35" t="inlineStr">
         <is>
           <t>X. Phong Phú, Binh Chanh</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="inlineStr">
+      <c r="A6" s="35" t="inlineStr">
         <is>
           <t>Bán nhanh thu hồi vốn giỏ hàng đa dạng từ 59m2, 69m2, 85m2,</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>Binh Chanh</t>
         </is>
       </c>
-      <c r="C6" s="20" t="n">
+      <c r="C6" s="35" t="n">
         <v>10.7210978</v>
       </c>
-      <c r="D6" s="20" t="n">
+      <c r="D6" s="35" t="n">
         <v>106.5926648</v>
       </c>
-      <c r="E6" s="20" t="inlineStr">
+      <c r="E6" s="35" t="inlineStr">
         <is>
           <t>2,69 tỷ</t>
         </is>
       </c>
-      <c r="F6" s="20" t="inlineStr">
+      <c r="F6" s="35" t="inlineStr">
         <is>
           <t>TT. Tân Túc, Binh Chanh</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="A7" s="35" t="inlineStr">
         <is>
           <t>Ansana by Kita</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>Binh Tan</t>
         </is>
       </c>
-      <c r="C7" s="20" t="n">
+      <c r="C7" s="35" t="n">
         <v>10.7237099</v>
       </c>
-      <c r="D7" s="20" t="n">
+      <c r="D7" s="35" t="n">
         <v>106.6155445</v>
       </c>
-      <c r="E7" s="20" t="inlineStr">
+      <c r="E7" s="35" t="inlineStr">
         <is>
           <t>Thoa thuan</t>
         </is>
       </c>
-      <c r="F7" s="20" t="inlineStr">
+      <c r="F7" s="35" t="inlineStr">
         <is>
           <t>P. An Lac, Q. Binh Tan</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="35" t="inlineStr">
         <is>
           <t>Carillon 7</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="35" t="inlineStr">
         <is>
           <t>Tan Phu</t>
         </is>
       </c>
-      <c r="C8" s="20" t="n">
+      <c r="C8" s="35" t="n">
         <v>10.7609925</v>
       </c>
-      <c r="D8" s="20" t="n">
+      <c r="D8" s="35" t="n">
         <v>106.6300848</v>
       </c>
-      <c r="E8" s="20" t="inlineStr">
+      <c r="E8" s="35" t="inlineStr">
         <is>
           <t>3.79-3.8 ty</t>
         </is>
       </c>
-      <c r="F8" s="20" t="inlineStr">
+      <c r="F8" s="35" t="inlineStr">
         <is>
           <t>P. Tân Thới Hòa, Tan Phu</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="A9" s="35" t="inlineStr">
         <is>
           <t>An Gia Garden</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="35" t="inlineStr">
         <is>
           <t>Tan Phu</t>
         </is>
       </c>
-      <c r="C9" s="20" t="n">
+      <c r="C9" s="35" t="n">
         <v>10.8016678</v>
       </c>
-      <c r="D9" s="20" t="n">
+      <c r="D9" s="35" t="n">
         <v>106.6257359</v>
       </c>
-      <c r="E9" s="20" t="inlineStr">
+      <c r="E9" s="35" t="inlineStr">
         <is>
           <t>4.1-4.65 ty</t>
         </is>
       </c>
-      <c r="F9" s="20" t="inlineStr">
+      <c r="F9" s="35" t="inlineStr">
         <is>
           <t>P. Tân Sơn Nhì, Tan Phu</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="inlineStr">
+      <c r="A10" s="35" t="inlineStr">
         <is>
           <t>RES Green Tower</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="35" t="inlineStr">
         <is>
           <t>Tan Phu</t>
         </is>
       </c>
-      <c r="C10" s="20" t="n">
+      <c r="C10" s="35" t="n">
         <v>10.7842161</v>
       </c>
-      <c r="D10" s="20" t="n">
+      <c r="D10" s="35" t="n">
         <v>106.6397437</v>
       </c>
-      <c r="E10" s="20" t="inlineStr">
+      <c r="E10" s="35" t="inlineStr">
         <is>
           <t>3.3-3.5 ty</t>
         </is>
       </c>
-      <c r="F10" s="20" t="inlineStr">
+      <c r="F10" s="35" t="inlineStr">
         <is>
           <t>P. Hòa Thạnh, Tan Phu</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="A11" s="35" t="inlineStr">
         <is>
           <t>Investco Babylon</t>
         </is>
       </c>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="35" t="inlineStr">
         <is>
           <t>Tan Phu</t>
         </is>
       </c>
-      <c r="C11" s="20" t="n">
+      <c r="C11" s="35" t="n">
         <v>10.7889462</v>
       </c>
-      <c r="D11" s="20" t="n">
+      <c r="D11" s="35" t="n">
         <v>106.6398628</v>
       </c>
-      <c r="E11" s="20" t="inlineStr">
+      <c r="E11" s="35" t="inlineStr">
         <is>
           <t>3.15 ty</t>
         </is>
       </c>
-      <c r="F11" s="20" t="inlineStr">
+      <c r="F11" s="35" t="inlineStr">
         <is>
           <t>P. Tân Thành, Tan Phu</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="inlineStr">
+      <c r="A12" s="35" t="inlineStr">
         <is>
           <t>La Cosmo Residences</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B12" s="35" t="inlineStr">
         <is>
           <t>Tan Binh</t>
         </is>
       </c>
-      <c r="C12" s="20" t="n">
+      <c r="C12" s="35" t="n">
         <v>10.8109666</v>
       </c>
-      <c r="D12" s="20" t="n">
+      <c r="D12" s="35" t="n">
         <v>106.6599382</v>
       </c>
-      <c r="E12" s="20" t="inlineStr">
+      <c r="E12" s="35" t="inlineStr">
         <is>
           <t>Giá thỏa thuận</t>
         </is>
       </c>
-      <c r="F12" s="20" t="inlineStr">
+      <c r="F12" s="35" t="inlineStr">
         <is>
           <t>Phường 4, Tan Binh</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="20" t="inlineStr">
+      <c r="A13" s="35" t="inlineStr">
         <is>
           <t>The Botanica</t>
         </is>
       </c>
-      <c r="B13" s="20" t="inlineStr">
+      <c r="B13" s="35" t="inlineStr">
         <is>
           <t>Tan Binh</t>
         </is>
       </c>
-      <c r="C13" s="20" t="n">
+      <c r="C13" s="35" t="n">
         <v>10.805859</v>
       </c>
-      <c r="D13" s="20" t="n">
+      <c r="D13" s="35" t="n">
         <v>106.6594014</v>
       </c>
-      <c r="E13" s="20" t="inlineStr">
+      <c r="E13" s="35" t="inlineStr">
         <is>
           <t>5.6-5.85 ty</t>
         </is>
       </c>
-      <c r="F13" s="20" t="inlineStr">
+      <c r="F13" s="35" t="inlineStr">
         <is>
           <t>Phường 2, Tan Binh</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="inlineStr">
+      <c r="A14" s="35" t="inlineStr">
         <is>
           <t>Terra Luxury</t>
         </is>
       </c>
-      <c r="B14" s="20" t="inlineStr">
+      <c r="B14" s="35" t="inlineStr">
         <is>
           <t>Binh Chanh</t>
         </is>
       </c>
-      <c r="C14" s="20" t="n">
+      <c r="C14" s="35" t="n">
         <v>10.7222143</v>
       </c>
-      <c r="D14" s="20" t="n">
+      <c r="D14" s="35" t="n">
         <v>106.5979179</v>
       </c>
-      <c r="E14" s="20" t="inlineStr">
+      <c r="E14" s="35" t="inlineStr">
         <is>
           <t>3.7 ty</t>
         </is>
       </c>
-      <c r="F14" s="20" t="inlineStr">
+      <c r="F14" s="35" t="inlineStr">
         <is>
           <t>X. Phong Phú, Binh Chanh</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="20" t="inlineStr">
+      <c r="A15" s="35" t="inlineStr">
         <is>
           <t>Sổ hồng! Bán 2PN, 2WC 59m2 view công viên + ủy ban, tháp vip</t>
         </is>
       </c>
-      <c r="B15" s="20" t="inlineStr">
+      <c r="B15" s="35" t="inlineStr">
         <is>
           <t>Binh Chanh</t>
         </is>
       </c>
-      <c r="C15" s="20" t="n">
+      <c r="C15" s="35" t="n">
         <v>10.7209096</v>
       </c>
-      <c r="D15" s="20" t="n">
+      <c r="D15" s="35" t="n">
         <v>106.5998253</v>
       </c>
-      <c r="E15" s="20" t="inlineStr">
+      <c r="E15" s="35" t="inlineStr">
         <is>
           <t>2,75 tỷ</t>
         </is>
       </c>
-      <c r="F15" s="20" t="inlineStr">
+      <c r="F15" s="35" t="inlineStr">
         <is>
           <t>TT. Tân Túc, Binh Chanh</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="20" t="inlineStr">
+      <c r="A16" s="35" t="inlineStr">
         <is>
           <t>Không đăng ảo! Giá tốt 2PN 2WC có sổ, nhà mới 98%, đẹp, view</t>
         </is>
       </c>
-      <c r="B16" s="20" t="inlineStr">
+      <c r="B16" s="35" t="inlineStr">
         <is>
           <t>Binh Chanh</t>
         </is>
       </c>
-      <c r="C16" s="20" t="n">
+      <c r="C16" s="35" t="n">
         <v>10.7227706</v>
       </c>
-      <c r="D16" s="20" t="n">
+      <c r="D16" s="35" t="n">
         <v>106.5910702</v>
       </c>
-      <c r="E16" s="20" t="inlineStr">
+      <c r="E16" s="35" t="inlineStr">
         <is>
           <t>2,65 tỷ</t>
         </is>
       </c>
-      <c r="F16" s="20" t="inlineStr">
+      <c r="F16" s="35" t="inlineStr">
         <is>
           <t>TT. Tân Túc, Binh Chanh</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="20" t="inlineStr">
+      <c r="A17" s="35" t="inlineStr">
         <is>
           <t>Tan Mai</t>
         </is>
       </c>
-      <c r="B17" s="20" t="inlineStr">
+      <c r="B17" s="35" t="inlineStr">
         <is>
           <t>Binh Tan</t>
         </is>
       </c>
-      <c r="C17" s="20" t="n">
+      <c r="C17" s="35" t="n">
         <v>10.7584152</v>
       </c>
-      <c r="D17" s="20" t="n">
+      <c r="D17" s="35" t="n">
         <v>106.5932513</v>
       </c>
-      <c r="E17" s="20" t="inlineStr">
+      <c r="E17" s="35" t="inlineStr">
         <is>
           <t>1.6-1.69 ty</t>
         </is>
       </c>
-      <c r="F17" s="20" t="inlineStr">
+      <c r="F17" s="35" t="inlineStr">
         <is>
           <t>P. Tan Tao, Q. Binh Tan</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="20" t="inlineStr">
+      <c r="A18" s="35" t="inlineStr">
         <is>
           <t>Green Town Binh Tan</t>
         </is>
       </c>
-      <c r="B18" s="20" t="inlineStr">
+      <c r="B18" s="35" t="inlineStr">
         <is>
           <t>Binh Tan</t>
         </is>
       </c>
-      <c r="C18" s="20" t="n">
+      <c r="C18" s="35" t="n">
         <v>10.8096268</v>
       </c>
-      <c r="D18" s="20" t="n">
+      <c r="D18" s="35" t="n">
         <v>106.5929298</v>
       </c>
-      <c r="E18" s="20" t="inlineStr">
+      <c r="E18" s="35" t="inlineStr">
         <is>
           <t>2.6 ty</t>
         </is>
       </c>
-      <c r="F18" s="20" t="inlineStr">
+      <c r="F18" s="35" t="inlineStr">
         <is>
           <t>P. Binh Hung Hoa B, Q. Binh Tan</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="20" t="inlineStr">
+      <c r="A19" s="35" t="inlineStr">
         <is>
           <t>Sai Gon Airport Plaza</t>
         </is>
       </c>
-      <c r="B19" s="20" t="inlineStr">
+      <c r="B19" s="35" t="inlineStr">
         <is>
           <t>Tan Binh</t>
         </is>
       </c>
-      <c r="C19" s="20" t="n">
+      <c r="C19" s="35" t="n">
         <v>10.8149357</v>
       </c>
-      <c r="D19" s="20" t="n">
+      <c r="D19" s="35" t="n">
         <v>106.6662829</v>
       </c>
-      <c r="E19" s="20" t="inlineStr">
+      <c r="E19" s="35" t="inlineStr">
         <is>
           <t>5-7.8 ty</t>
         </is>
       </c>
-      <c r="F19" s="20" t="inlineStr">
+      <c r="F19" s="35" t="inlineStr">
         <is>
           <t>Phường 2, Tan Binh</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="inlineStr">
+      <c r="A20" s="35" t="inlineStr">
         <is>
           <t>Chính chủ CẦN BÁN GẤP CĂN HỘ TẦNG TRỆT + GÁC LỬNG ĐÚC SỞ HỮU</t>
         </is>
       </c>
-      <c r="B20" s="20" t="inlineStr">
+      <c r="B20" s="35" t="inlineStr">
         <is>
           <t>Tan Binh</t>
         </is>
       </c>
-      <c r="C20" s="20" t="n">
+      <c r="C20" s="35" t="n">
         <v>10.8080296</v>
       </c>
-      <c r="D20" s="20" t="n">
+      <c r="D20" s="35" t="n">
         <v>106.6633153</v>
       </c>
-      <c r="E20" s="20" t="inlineStr">
+      <c r="E20" s="35" t="inlineStr">
         <is>
           <t>6 tỷ</t>
         </is>
       </c>
-      <c r="F20" s="20" t="inlineStr">
+      <c r="F20" s="35" t="inlineStr">
         <is>
           <t>Phường 12, Tan Binh</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="20" t="inlineStr">
+      <c r="A21" s="35" t="inlineStr">
         <is>
           <t>Chính chủ gửi bán gấp căn hộ Trường Chinh, P. 12, Tân Bình c</t>
         </is>
       </c>
-      <c r="B21" s="20" t="inlineStr">
+      <c r="B21" s="35" t="inlineStr">
         <is>
           <t>Tan Binh</t>
         </is>
       </c>
-      <c r="C21" s="20" t="n">
+      <c r="C21" s="35" t="n">
         <v>10.8040983</v>
       </c>
-      <c r="D21" s="20" t="n">
+      <c r="D21" s="35" t="n">
         <v>106.6579044</v>
       </c>
-      <c r="E21" s="20" t="inlineStr">
+      <c r="E21" s="35" t="inlineStr">
         <is>
           <t>2.8 ty</t>
         </is>
       </c>
-      <c r="F21" s="20" t="inlineStr">
+      <c r="F21" s="35" t="inlineStr">
         <is>
           <t>Phường 12, Tan Binh</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="20" t="inlineStr">
+      <c r="A22" s="35" t="inlineStr">
         <is>
           <t>Chính chủ gửi bán hộ ngay ngã ba CMT8 - Trường Chinh (Tân Bì</t>
         </is>
       </c>
-      <c r="B22" s="20" t="inlineStr">
+      <c r="B22" s="35" t="inlineStr">
         <is>
           <t>Tan Binh</t>
         </is>
       </c>
-      <c r="C22" s="20" t="n">
+      <c r="C22" s="35" t="n">
         <v>10.8082178</v>
       </c>
-      <c r="D22" s="20" t="n">
+      <c r="D22" s="35" t="n">
         <v>106.6561548</v>
       </c>
-      <c r="E22" s="20" t="inlineStr">
+      <c r="E22" s="35" t="inlineStr">
         <is>
           <t>2,8 tỷ</t>
         </is>
       </c>
-      <c r="F22" s="20" t="inlineStr">
+      <c r="F22" s="35" t="inlineStr">
         <is>
           <t>Phường 12, Tan Binh</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="20" t="inlineStr">
+      <c r="A23" s="35" t="inlineStr">
         <is>
           <t>The Harmona</t>
         </is>
       </c>
-      <c r="B23" s="20" t="inlineStr">
+      <c r="B23" s="35" t="inlineStr">
         <is>
           <t>Tan Binh</t>
         </is>
       </c>
-      <c r="C23" s="20" t="n">
+      <c r="C23" s="35" t="n">
         <v>10.7965292</v>
       </c>
-      <c r="D23" s="20" t="n">
+      <c r="D23" s="35" t="n">
         <v>106.6416853</v>
       </c>
-      <c r="E23" s="20" t="inlineStr">
+      <c r="E23" s="35" t="inlineStr">
         <is>
           <t>4,9 tỷ</t>
         </is>
       </c>
-      <c r="F23" s="20" t="inlineStr">
+      <c r="F23" s="35" t="inlineStr">
         <is>
           <t>Phường 14, Tan Binh</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="20" t="inlineStr">
+      <c r="A24" s="35" t="inlineStr">
         <is>
           <t>CHCC 155 Nguyen Chi Thanh</t>
         </is>
       </c>
-      <c r="B24" s="20" t="inlineStr">
+      <c r="B24" s="35" t="inlineStr">
         <is>
           <t>Q.5</t>
         </is>
       </c>
-      <c r="C24" s="20" t="n">
+      <c r="C24" s="35" t="n">
         <v>10.7811842</v>
       </c>
-      <c r="D24" s="20" t="n">
+      <c r="D24" s="35" t="n">
         <v>106.7060405</v>
       </c>
-      <c r="E24" s="20" t="inlineStr">
+      <c r="E24" s="35" t="inlineStr">
         <is>
           <t>4.3 ty</t>
         </is>
       </c>
-      <c r="F24" s="20" t="inlineStr">
+      <c r="F24" s="35" t="inlineStr">
         <is>
           <t>155 Nguyen Chi Thanh, P.9, Q.5</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="20" t="inlineStr">
+      <c r="A25" s="35" t="inlineStr">
         <is>
           <t>Chung cu Hung Vuong (Tan Da)</t>
         </is>
       </c>
-      <c r="B25" s="20" t="inlineStr">
+      <c r="B25" s="35" t="inlineStr">
         <is>
           <t>Q.5</t>
         </is>
       </c>
-      <c r="C25" s="20" t="n">
+      <c r="C25" s="35" t="n">
         <v>10.7538946</v>
       </c>
-      <c r="D25" s="20" t="n">
+      <c r="D25" s="35" t="n">
         <v>106.6653437</v>
       </c>
-      <c r="E25" s="20" t="inlineStr">
+      <c r="E25" s="35" t="inlineStr">
         <is>
           <t>3.05-3.2 ty</t>
         </is>
       </c>
-      <c r="F25" s="20" t="inlineStr">
+      <c r="F25" s="35" t="inlineStr">
         <is>
           <t>Tan Da, P.11, Q.5</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="20" t="inlineStr">
+      <c r="A26" s="35" t="inlineStr">
         <is>
           <t>Chung cu Nguyen Trai</t>
         </is>
       </c>
-      <c r="B26" s="20" t="inlineStr">
+      <c r="B26" s="35" t="inlineStr">
         <is>
           <t>Q.5</t>
         </is>
       </c>
-      <c r="C26" s="20" t="n">
+      <c r="C26" s="35" t="n">
         <v>10.7557827</v>
       </c>
-      <c r="D26" s="20" t="n">
+      <c r="D26" s="35" t="n">
         <v>106.6690391</v>
       </c>
-      <c r="E26" s="20" t="inlineStr">
+      <c r="E26" s="35" t="inlineStr">
         <is>
           <t>3.25 ty</t>
         </is>
       </c>
-      <c r="F26" s="20" t="inlineStr">
+      <c r="F26" s="35" t="inlineStr">
         <is>
           <t>Nguyen Trai, P.1, Q.5</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="20" t="inlineStr">
+      <c r="A27" s="35" t="inlineStr">
         <is>
           <t>Can ho Lakai</t>
         </is>
       </c>
-      <c r="B27" s="20" t="inlineStr">
+      <c r="B27" s="35" t="inlineStr">
         <is>
           <t>Q.5</t>
         </is>
       </c>
-      <c r="C27" s="20" t="n">
+      <c r="C27" s="35" t="n">
         <v>10.7540121</v>
       </c>
-      <c r="D27" s="20" t="n">
+      <c r="D27" s="35" t="n">
         <v>106.6697165</v>
       </c>
-      <c r="E27" s="20" t="inlineStr">
+      <c r="E27" s="35" t="inlineStr">
         <is>
           <t>4.4 ty</t>
         </is>
       </c>
-      <c r="F27" s="20" t="inlineStr">
+      <c r="F27" s="35" t="inlineStr">
         <is>
           <t>Nguyen Tri Phuong, P.8, Q.5</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="20" t="inlineStr">
+      <c r="A28" s="35" t="inlineStr">
         <is>
           <t>CC Phan Van Tri Q5</t>
         </is>
       </c>
-      <c r="B28" s="20" t="inlineStr">
+      <c r="B28" s="35" t="inlineStr">
         <is>
           <t>Q.5</t>
         </is>
       </c>
-      <c r="C28" s="20" t="n">
+      <c r="C28" s="35" t="n">
         <v>10.7535</v>
       </c>
-      <c r="D28" s="20" t="n">
+      <c r="D28" s="35" t="n">
         <v>106.6723</v>
       </c>
-      <c r="E28" s="20" t="inlineStr">
+      <c r="E28" s="35" t="inlineStr">
         <is>
           <t>3.15 ty</t>
         </is>
       </c>
-      <c r="F28" s="20" t="inlineStr">
+      <c r="F28" s="35" t="inlineStr">
         <is>
           <t>Phan Van Tri, P.2, Q.5</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="20" t="inlineStr">
+      <c r="A29" s="35" t="inlineStr">
         <is>
           <t>Chung cu Phuc Thinh</t>
         </is>
       </c>
-      <c r="B29" s="20" t="inlineStr">
+      <c r="B29" s="35" t="inlineStr">
         <is>
           <t>Q.5</t>
         </is>
       </c>
-      <c r="C29" s="20" t="n">
+      <c r="C29" s="35" t="n">
         <v>10.7534138</v>
       </c>
-      <c r="D29" s="20" t="n">
+      <c r="D29" s="35" t="n">
         <v>106.6802515</v>
       </c>
-      <c r="E29" s="20" t="inlineStr">
+      <c r="E29" s="35" t="inlineStr">
         <is>
           <t>3.75-4.6 ty</t>
         </is>
       </c>
-      <c r="F29" s="20" t="inlineStr">
+      <c r="F29" s="35" t="inlineStr">
         <is>
           <t>Cao Dat, P.1, Q.5</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="20" t="inlineStr">
+      <c r="A30" s="35" t="inlineStr">
         <is>
           <t>CC Dao Tan Q5</t>
         </is>
       </c>
-      <c r="B30" s="20" t="inlineStr">
+      <c r="B30" s="35" t="inlineStr">
         <is>
           <t>Q.5</t>
         </is>
       </c>
-      <c r="C30" s="20" t="n">
+      <c r="C30" s="35" t="n">
         <v>10.752</v>
       </c>
-      <c r="D30" s="20" t="n">
+      <c r="D30" s="35" t="n">
         <v>106.6697</v>
       </c>
-      <c r="E30" s="20" t="inlineStr">
+      <c r="E30" s="35" t="inlineStr">
         <is>
           <t>4.66 ty</t>
         </is>
       </c>
-      <c r="F30" s="20" t="inlineStr">
+      <c r="F30" s="35" t="inlineStr">
         <is>
           <t>Dao Tan, P.5, Q.5</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="20" t="inlineStr">
+      <c r="A31" s="35" t="inlineStr">
         <is>
           <t>CC Nguyen Bieu Q5</t>
         </is>
       </c>
-      <c r="B31" s="20" t="inlineStr">
+      <c r="B31" s="35" t="inlineStr">
         <is>
           <t>Q.5</t>
         </is>
       </c>
-      <c r="C31" s="20" t="n">
+      <c r="C31" s="35" t="n">
         <v>10.7556705</v>
       </c>
-      <c r="D31" s="20" t="n">
+      <c r="D31" s="35" t="n">
         <v>106.6732042</v>
       </c>
-      <c r="E31" s="20" t="inlineStr">
+      <c r="E31" s="35" t="inlineStr">
         <is>
           <t>3 ty</t>
         </is>
       </c>
-      <c r="F31" s="20" t="inlineStr">
+      <c r="F31" s="35" t="inlineStr">
         <is>
           <t>Nguyen Bieu, P.1, Q.5</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="20" t="inlineStr">
+      <c r="A32" s="35" t="inlineStr">
         <is>
           <t>Hoa Sen - Lotus Apartment</t>
         </is>
       </c>
-      <c r="B32" s="20" t="inlineStr">
+      <c r="B32" s="35" t="inlineStr">
         <is>
           <t>Q.11</t>
         </is>
       </c>
-      <c r="C32" s="20" t="n">
+      <c r="C32" s="35" t="n">
         <v>10.7660078</v>
       </c>
-      <c r="D32" s="20" t="n">
+      <c r="D32" s="35" t="n">
         <v>106.6427565</v>
       </c>
-      <c r="E32" s="20" t="inlineStr">
+      <c r="E32" s="35" t="inlineStr">
         <is>
           <t>4.3 ty</t>
         </is>
       </c>
-      <c r="F32" s="20" t="inlineStr">
+      <c r="F32" s="35" t="inlineStr">
         <is>
           <t>Lac Long Quan, P.10, Q.11</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="20" t="inlineStr">
+      <c r="A33" s="35" t="inlineStr">
         <is>
           <t>CC Ly Thuong Kiet Q11</t>
         </is>
       </c>
-      <c r="B33" s="20" t="inlineStr">
+      <c r="B33" s="35" t="inlineStr">
         <is>
           <t>Q.11</t>
         </is>
       </c>
-      <c r="C33" s="20" t="n">
+      <c r="C33" s="35" t="n">
         <v>10.7683972</v>
       </c>
-      <c r="D33" s="20" t="n">
+      <c r="D33" s="35" t="n">
         <v>106.6618361</v>
       </c>
-      <c r="E33" s="20" t="inlineStr">
+      <c r="E33" s="35" t="inlineStr">
         <is>
           <t>3.2 ty</t>
         </is>
       </c>
-      <c r="F33" s="20" t="inlineStr">
+      <c r="F33" s="35" t="inlineStr">
         <is>
           <t>Ly Thuong Kiet, P.7, Q.11</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="20" t="inlineStr">
+      <c r="A34" s="35" t="inlineStr">
         <is>
           <t>CC Lac Long Quan Q11</t>
         </is>
       </c>
-      <c r="B34" s="20" t="inlineStr">
+      <c r="B34" s="35" t="inlineStr">
         <is>
           <t>Q.11</t>
         </is>
       </c>
-      <c r="C34" s="20" t="n">
+      <c r="C34" s="35" t="n">
         <v>10.7706699</v>
       </c>
-      <c r="D34" s="20" t="n">
+      <c r="D34" s="35" t="n">
         <v>106.6443301</v>
       </c>
-      <c r="E34" s="20" t="inlineStr">
+      <c r="E34" s="35" t="inlineStr">
         <is>
           <t>3.63 ty</t>
         </is>
       </c>
-      <c r="F34" s="20" t="inlineStr">
+      <c r="F34" s="35" t="inlineStr">
         <is>
           <t>Lac Long Quan, P.5, Q.11</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="20" t="inlineStr">
+      <c r="A35" s="35" t="inlineStr">
         <is>
           <t>RES 11</t>
         </is>
       </c>
-      <c r="B35" s="20" t="inlineStr">
+      <c r="B35" s="35" t="inlineStr">
         <is>
           <t>Q.11</t>
         </is>
       </c>
-      <c r="C35" s="20" t="n">
+      <c r="C35" s="35" t="n">
         <v>10.763534</v>
       </c>
-      <c r="D35" s="20" t="n">
+      <c r="D35" s="35" t="n">
         <v>106.6419219</v>
       </c>
-      <c r="E35" s="20" t="inlineStr">
+      <c r="E35" s="35" t="inlineStr">
         <is>
           <t>3.55-5 ty</t>
         </is>
       </c>
-      <c r="F35" s="20" t="inlineStr">
+      <c r="F35" s="35" t="inlineStr">
         <is>
           <t>Lac Long Quan, P.3, Q.11</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="20" t="inlineStr">
+      <c r="A36" s="35" t="inlineStr">
         <is>
           <t>Chung cu 312 Lac Long Quan</t>
         </is>
       </c>
-      <c r="B36" s="20" t="inlineStr">
+      <c r="B36" s="35" t="inlineStr">
         <is>
           <t>Q.11</t>
         </is>
       </c>
-      <c r="C36" s="20" t="n">
+      <c r="C36" s="35" t="n">
         <v>10.7686327</v>
       </c>
-      <c r="D36" s="20" t="n">
+      <c r="D36" s="35" t="n">
         <v>106.644232</v>
       </c>
-      <c r="E36" s="20" t="inlineStr">
+      <c r="E36" s="35" t="inlineStr">
         <is>
           <t>3.4 ty</t>
         </is>
       </c>
-      <c r="F36" s="20" t="inlineStr">
+      <c r="F36" s="35" t="inlineStr">
         <is>
           <t>312 Lac Long Quan, P.5, Q.11</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="20" t="inlineStr">
+      <c r="A37" s="35" t="inlineStr">
         <is>
           <t>Chung cu Phu Tho Q11</t>
         </is>
       </c>
-      <c r="B37" s="20" t="inlineStr">
+      <c r="B37" s="35" t="inlineStr">
         <is>
           <t>Q.11</t>
         </is>
       </c>
-      <c r="C37" s="20" t="n">
+      <c r="C37" s="35" t="n">
         <v>10.7698821</v>
       </c>
-      <c r="D37" s="20" t="n">
+      <c r="D37" s="35" t="n">
         <v>106.6534079</v>
       </c>
-      <c r="E37" s="20" t="inlineStr">
+      <c r="E37" s="35" t="inlineStr">
         <is>
           <t>3.7 ty</t>
         </is>
       </c>
-      <c r="F37" s="20" t="inlineStr">
+      <c r="F37" s="35" t="inlineStr">
         <is>
           <t>Nguyen Thi Nho, P.15, Q.11</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="20" t="inlineStr">
+      <c r="A38" s="35" t="inlineStr">
         <is>
           <t>Ehome 3</t>
         </is>
       </c>
-      <c r="B38" s="20" t="inlineStr">
+      <c r="B38" s="35" t="inlineStr">
         <is>
           <t>Binh Tan</t>
         </is>
       </c>
-      <c r="C38" s="20" t="n">
+      <c r="C38" s="35" t="n">
         <v>10.7142157</v>
       </c>
-      <c r="D38" s="20" t="n">
+      <c r="D38" s="35" t="n">
         <v>106.6097733</v>
       </c>
-      <c r="E38" s="20" t="inlineStr">
+      <c r="E38" s="35" t="inlineStr">
         <is>
           <t>2.05-2.87 ty</t>
         </is>
       </c>
-      <c r="F38" s="20" t="inlineStr">
+      <c r="F38" s="35" t="inlineStr">
         <is>
           <t>P. An Lac, Q. Binh Tan</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="20" t="inlineStr">
+      <c r="A39" s="35" t="inlineStr">
         <is>
           <t>Moonlight Park View</t>
         </is>
       </c>
-      <c r="B39" s="20" t="inlineStr">
+      <c r="B39" s="35" t="inlineStr">
         <is>
           <t>Binh Tan</t>
         </is>
       </c>
-      <c r="C39" s="20" t="n">
+      <c r="C39" s="35" t="n">
         <v>10.7519339</v>
       </c>
-      <c r="D39" s="20" t="n">
+      <c r="D39" s="35" t="n">
         <v>106.6201888</v>
       </c>
-      <c r="E39" s="20" t="inlineStr">
+      <c r="E39" s="35" t="inlineStr">
         <is>
           <t>3.5 ty</t>
         </is>
       </c>
-      <c r="F39" s="20" t="inlineStr">
+      <c r="F39" s="35" t="inlineStr">
         <is>
           <t>P. An Lac A, Q. Binh Tan</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="20" t="inlineStr">
+      <c r="A40" s="35" t="inlineStr">
         <is>
           <t>Gia Phu</t>
         </is>
       </c>
-      <c r="B40" s="20" t="inlineStr">
+      <c r="B40" s="35" t="inlineStr">
         <is>
           <t>Binh Tan</t>
         </is>
       </c>
-      <c r="C40" s="20" t="n">
+      <c r="C40" s="35" t="n">
         <v>10.8089072</v>
       </c>
-      <c r="D40" s="20" t="n">
+      <c r="D40" s="35" t="n">
         <v>106.6056454</v>
       </c>
-      <c r="E40" s="20" t="inlineStr">
+      <c r="E40" s="35" t="inlineStr">
         <is>
           <t>2.6 ty</t>
         </is>
       </c>
-      <c r="F40" s="20" t="inlineStr">
+      <c r="F40" s="35" t="inlineStr">
         <is>
           <t>P. Binh Hung Hoa, Q. Binh Tan</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="20" t="inlineStr">
+      <c r="A41" s="35" t="inlineStr">
         <is>
           <t>Ruby Celadon City</t>
         </is>
       </c>
-      <c r="B41" s="20" t="inlineStr">
+      <c r="B41" s="35" t="inlineStr">
         <is>
           <t>Tan Phu</t>
         </is>
       </c>
-      <c r="C41" s="20" t="n">
+      <c r="C41" s="35" t="n">
         <v>10.8025753</v>
       </c>
-      <c r="D41" s="20" t="n">
+      <c r="D41" s="35" t="n">
         <v>106.6147837</v>
       </c>
-      <c r="E41" s="20" t="inlineStr">
+      <c r="E41" s="35" t="inlineStr">
         <is>
           <t>4.3-5.88 ty</t>
         </is>
       </c>
-      <c r="F41" s="20" t="inlineStr">
+      <c r="F41" s="35" t="inlineStr">
         <is>
           <t>P. Sơn Kỳ, Tan Phu</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="20" t="inlineStr">
+      <c r="A42" s="35" t="inlineStr">
         <is>
           <t>Melody Residences</t>
         </is>
       </c>
-      <c r="B42" s="20" t="inlineStr">
+      <c r="B42" s="35" t="inlineStr">
         <is>
           <t>Tan Phu</t>
         </is>
       </c>
-      <c r="C42" s="20" t="n">
+      <c r="C42" s="35" t="n">
         <v>10.7963806</v>
       </c>
-      <c r="D42" s="20" t="n">
+      <c r="D42" s="35" t="n">
         <v>106.6370621</v>
       </c>
-      <c r="E42" s="20" t="inlineStr">
+      <c r="E42" s="35" t="inlineStr">
         <is>
           <t>3.85-4.1 ty</t>
         </is>
       </c>
-      <c r="F42" s="20" t="inlineStr">
+      <c r="F42" s="35" t="inlineStr">
         <is>
           <t>P. Tan Son Nhi, Tan Phu</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="20" t="inlineStr">
+      <c r="A43" s="35" t="inlineStr">
         <is>
           <t>Lotus Garden</t>
         </is>
       </c>
-      <c r="B43" s="20" t="inlineStr">
+      <c r="B43" s="35" t="inlineStr">
         <is>
           <t>Tan Phu</t>
         </is>
       </c>
-      <c r="C43" s="20" t="n">
+      <c r="C43" s="35" t="n">
         <v>10.7736303</v>
       </c>
-      <c r="D43" s="20" t="n">
+      <c r="D43" s="35" t="n">
         <v>106.6356264</v>
       </c>
-      <c r="E43" s="20" t="inlineStr">
+      <c r="E43" s="35" t="inlineStr">
         <is>
           <t>3.69-4.3 ty</t>
         </is>
       </c>
-      <c r="F43" s="20" t="inlineStr">
+      <c r="F43" s="35" t="inlineStr">
         <is>
           <t>Trinh Dinh Thao, P. Hoa Thanh, Tan Phu</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="20" t="inlineStr">
+      <c r="A44" s="35" t="inlineStr">
         <is>
           <t>Valeo Dam Sen</t>
         </is>
       </c>
-      <c r="B44" s="20" t="inlineStr">
+      <c r="B44" s="35" t="inlineStr">
         <is>
           <t>Tan Phu</t>
         </is>
       </c>
-      <c r="C44" s="20" t="n">
+      <c r="C44" s="35" t="n">
         <v>10.7776072</v>
       </c>
-      <c r="D44" s="20" t="n">
+      <c r="D44" s="35" t="n">
         <v>106.63697</v>
       </c>
-      <c r="E44" s="20" t="inlineStr">
+      <c r="E44" s="35" t="inlineStr">
         <is>
           <t>4.9-5.1 ty</t>
         </is>
       </c>
-      <c r="F44" s="20" t="inlineStr">
+      <c r="F44" s="35" t="inlineStr">
         <is>
           <t>P. Hoa Thanh, Tan Phu</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="20" t="inlineStr">
+      <c r="A45" s="35" t="inlineStr">
         <is>
           <t>Au Co Tower</t>
         </is>
       </c>
-      <c r="B45" s="20" t="inlineStr">
+      <c r="B45" s="35" t="inlineStr">
         <is>
           <t>Tan Phu</t>
         </is>
       </c>
-      <c r="C45" s="20" t="n">
+      <c r="C45" s="35" t="n">
         <v>10.7872565</v>
       </c>
-      <c r="D45" s="20" t="n">
+      <c r="D45" s="35" t="n">
         <v>106.6402867</v>
       </c>
-      <c r="E45" s="20" t="inlineStr">
+      <c r="E45" s="35" t="inlineStr">
         <is>
           <t>3-3.5 ty</t>
         </is>
       </c>
-      <c r="F45" s="20" t="inlineStr">
+      <c r="F45" s="35" t="inlineStr">
         <is>
           <t>P. Tân Thành, Tan Phu</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="20" t="inlineStr">
+      <c r="A46" s="35" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="B46" s="20" t="inlineStr">
+      <c r="B46" s="35" t="inlineStr">
         <is>
           <t>Tan Phu</t>
         </is>
       </c>
-      <c r="C46" s="20" t="n">
+      <c r="C46" s="35" t="n">
         <v>10.7838094</v>
       </c>
-      <c r="D46" s="20" t="n">
+      <c r="D46" s="35" t="n">
         <v>106.6369877</v>
       </c>
-      <c r="E46" s="20" t="inlineStr">
+      <c r="E46" s="35" t="inlineStr">
         <is>
           <t>2.25-4.55 ty</t>
         </is>
       </c>
-      <c r="F46" s="20" t="inlineStr">
+      <c r="F46" s="35" t="inlineStr">
         <is>
           <t>P. Tây Thạnh, Tan Phu</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="20" t="inlineStr">
+      <c r="A47" s="35" t="inlineStr">
         <is>
           <t>Diamond Alnata</t>
         </is>
       </c>
-      <c r="B47" s="20" t="inlineStr">
+      <c r="B47" s="35" t="inlineStr">
         <is>
           <t>Tan Phu</t>
         </is>
       </c>
-      <c r="C47" s="20" t="n">
+      <c r="C47" s="35" t="n">
         <v>10.8028969</v>
       </c>
-      <c r="D47" s="20" t="n">
+      <c r="D47" s="35" t="n">
         <v>106.6155408</v>
       </c>
-      <c r="E47" s="20" t="inlineStr">
+      <c r="E47" s="35" t="inlineStr">
         <is>
           <t>10,5 tỷ</t>
         </is>
       </c>
-      <c r="F47" s="20" t="inlineStr">
+      <c r="F47" s="35" t="inlineStr">
         <is>
           <t>P. Sơn Kỳ, Tan Phu</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="20" t="inlineStr">
+      <c r="A48" s="35" t="inlineStr">
         <is>
           <t>Tanibuilding Son Ky 2</t>
         </is>
       </c>
-      <c r="B48" s="20" t="inlineStr">
+      <c r="B48" s="35" t="inlineStr">
         <is>
           <t>Tan Phu</t>
         </is>
       </c>
-      <c r="C48" s="20" t="n">
+      <c r="C48" s="35" t="n">
         <v>10.7832356</v>
       </c>
-      <c r="D48" s="20" t="n">
+      <c r="D48" s="35" t="n">
         <v>106.6259375</v>
       </c>
-      <c r="E48" s="20" t="inlineStr">
+      <c r="E48" s="35" t="inlineStr">
         <is>
           <t>6,2 tỷ</t>
         </is>
       </c>
-      <c r="F48" s="20" t="inlineStr">
+      <c r="F48" s="35" t="inlineStr">
         <is>
           <t>P. Sơn Kỳ, Tan Phu</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="20" t="inlineStr">
+      <c r="A49" s="35" t="inlineStr">
         <is>
           <t>Tân Bình CC Bàu Cát lầu 1 SHR 2pn full nội thất giá 1,799tỷ</t>
         </is>
       </c>
-      <c r="B49" s="20" t="inlineStr">
+      <c r="B49" s="35" t="inlineStr">
         <is>
           <t>Tan Binh</t>
         </is>
       </c>
-      <c r="C49" s="20" t="n">
+      <c r="C49" s="35" t="n">
         <v>10.80625</v>
       </c>
-      <c r="D49" s="20" t="n">
+      <c r="D49" s="35" t="n">
         <v>106.6549429</v>
       </c>
-      <c r="E49" s="20" t="inlineStr">
+      <c r="E49" s="35" t="inlineStr">
         <is>
           <t>1,8 tỷ</t>
         </is>
       </c>
-      <c r="F49" s="20" t="inlineStr">
+      <c r="F49" s="35" t="inlineStr">
         <is>
           <t>Phường 14, Tan Binh</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="20" t="inlineStr">
+      <c r="A50" s="35" t="inlineStr">
         <is>
           <t>Carillon 3</t>
         </is>
       </c>
-      <c r="B50" s="20" t="inlineStr">
+      <c r="B50" s="35" t="inlineStr">
         <is>
           <t>Tan Binh</t>
         </is>
       </c>
-      <c r="C50" s="20" t="n">
+      <c r="C50" s="35" t="n">
         <v>10.8053756</v>
       </c>
-      <c r="D50" s="20" t="n">
+      <c r="D50" s="35" t="n">
         <v>106.6469127</v>
       </c>
-      <c r="E50" s="20" t="inlineStr">
+      <c r="E50" s="35" t="inlineStr">
         <is>
           <t>4,75 tỷ</t>
         </is>
       </c>
-      <c r="F50" s="20" t="inlineStr">
+      <c r="F50" s="35" t="inlineStr">
         <is>
           <t>Phường 13, Tan Binh</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="20" t="inlineStr">
+      <c r="A51" s="35" t="inlineStr">
         <is>
           <t>Hàng hiếm! Bán căn góc 85m2 3PN 2WC + view hồ bơi mát mẻ + s</t>
         </is>
       </c>
-      <c r="B51" s="20" t="inlineStr">
+      <c r="B51" s="35" t="inlineStr">
         <is>
           <t>Binh Chanh</t>
         </is>
       </c>
-      <c r="C51" s="20" t="n">
+      <c r="C51" s="35" t="n">
         <v>10.72003</v>
       </c>
-      <c r="D51" s="20" t="n">
+      <c r="D51" s="35" t="n">
         <v>106.5976883</v>
       </c>
-      <c r="E51" s="20" t="inlineStr">
+      <c r="E51" s="35" t="inlineStr">
         <is>
           <t>3,62 tỷ</t>
         </is>
       </c>
-      <c r="F51" s="20" t="inlineStr">
+      <c r="F51" s="35" t="inlineStr">
         <is>
           <t>TT. Tân Túc, Binh Chanh</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="20" t="inlineStr">
+      <c r="A52" s="35" t="inlineStr">
         <is>
           <t>Sổ hồng nhà mới bán 3PN +, 113m2, lầu đẹp, block vip C tặng</t>
         </is>
       </c>
-      <c r="B52" s="20" t="inlineStr">
+      <c r="B52" s="35" t="inlineStr">
         <is>
           <t>Binh Chanh</t>
         </is>
       </c>
-      <c r="C52" s="20" t="n">
+      <c r="C52" s="35" t="n">
         <v>10.7177394</v>
       </c>
-      <c r="D52" s="20" t="n">
+      <c r="D52" s="35" t="n">
         <v>106.597995</v>
       </c>
-      <c r="E52" s="20" t="inlineStr">
+      <c r="E52" s="35" t="inlineStr">
         <is>
           <t>4,65 tỷ</t>
         </is>
       </c>
-      <c r="F52" s="20" t="inlineStr">
+      <c r="F52" s="35" t="inlineStr">
         <is>
           <t>TT. Tân Túc, Binh Chanh</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="20" t="inlineStr">
+      <c r="A53" s="35" t="inlineStr">
         <is>
           <t>Sổ hồng! Nhà mới 100% bán 2PN, 2WC 59m2 view ủy ban, công vi</t>
         </is>
       </c>
-      <c r="B53" s="20" t="inlineStr">
+      <c r="B53" s="35" t="inlineStr">
         <is>
           <t>Binh Chanh</t>
         </is>
       </c>
-      <c r="C53" s="20" t="n">
+      <c r="C53" s="35" t="n">
         <v>10.718739</v>
       </c>
-      <c r="D53" s="20" t="n">
+      <c r="D53" s="35" t="n">
         <v>106.5959114</v>
       </c>
-      <c r="E53" s="20" t="inlineStr">
+      <c r="E53" s="35" t="inlineStr">
         <is>
           <t>2,8 tỷ</t>
         </is>
       </c>
-      <c r="F53" s="20" t="inlineStr">
+      <c r="F53" s="35" t="inlineStr">
         <is>
           <t>TT. Tân Túc, Binh Chanh</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="20" t="inlineStr">
+      <c r="A54" s="35" t="inlineStr">
         <is>
           <t>Hàng hiếm! Bán căn 59m2 2PN 2WC + view ngoại khu mát mẻ + ti</t>
         </is>
       </c>
-      <c r="B54" s="20" t="inlineStr">
+      <c r="B54" s="35" t="inlineStr">
         <is>
           <t>Binh Chanh</t>
         </is>
       </c>
-      <c r="C54" s="20" t="n">
+      <c r="C54" s="35" t="n">
         <v>10.7191957</v>
       </c>
-      <c r="D54" s="20" t="n">
+      <c r="D54" s="35" t="n">
         <v>106.593763</v>
       </c>
-      <c r="E54" s="20" t="inlineStr">
+      <c r="E54" s="35" t="inlineStr">
         <is>
           <t>2,62 tỷ</t>
         </is>
       </c>
-      <c r="F54" s="20" t="inlineStr">
+      <c r="F54" s="35" t="inlineStr">
         <is>
           <t>TT. Tân Túc, Binh Chanh</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="20" t="inlineStr">
+      <c r="A55" s="35" t="inlineStr">
+        <is>
+          <t>Topaz Elite</t>
+        </is>
+      </c>
+      <c r="B55" s="35" t="inlineStr">
+        <is>
+          <t>Q.8</t>
+        </is>
+      </c>
+      <c r="C55" s="35" t="n">
+        <v>10.7392189</v>
+      </c>
+      <c r="D55" s="35" t="n">
+        <v>106.6797322</v>
+      </c>
+      <c r="E55" s="35" t="inlineStr">
+        <is>
+          <t>3.2-4.8 ty</t>
+        </is>
+      </c>
+      <c r="F55" s="35" t="inlineStr">
+        <is>
+          <t>Cao Lo, P.4, Q.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="35" t="inlineStr">
+        <is>
+          <t>Topaz City</t>
+        </is>
+      </c>
+      <c r="B56" s="35" t="inlineStr">
+        <is>
+          <t>Q.8</t>
+        </is>
+      </c>
+      <c r="C56" s="35" t="n">
+        <v>10.7386</v>
+      </c>
+      <c r="D56" s="35" t="n">
+        <v>106.6798</v>
+      </c>
+      <c r="E56" s="35" t="inlineStr">
+        <is>
+          <t>3.0-4.5 ty</t>
+        </is>
+      </c>
+      <c r="F56" s="35" t="inlineStr">
+        <is>
+          <t>Ta Quang Buu, P.5, Q.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="35" t="inlineStr">
+        <is>
+          <t>The Pegasuite</t>
+        </is>
+      </c>
+      <c r="B57" s="35" t="inlineStr">
+        <is>
+          <t>Q.8</t>
+        </is>
+      </c>
+      <c r="C57" s="35" t="n">
+        <v>10.7342516</v>
+      </c>
+      <c r="D57" s="35" t="n">
+        <v>106.6533069</v>
+      </c>
+      <c r="E57" s="35" t="inlineStr">
+        <is>
+          <t>3.0-4.5 ty</t>
+        </is>
+      </c>
+      <c r="F57" s="35" t="inlineStr">
+        <is>
+          <t>Ta Quang Buu, P.6, Q.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="35" t="inlineStr">
+        <is>
+          <t>The Pegasuite 2</t>
+        </is>
+      </c>
+      <c r="B58" s="35" t="inlineStr">
+        <is>
+          <t>Q.8</t>
+        </is>
+      </c>
+      <c r="C58" s="35" t="n">
+        <v>10.7327</v>
+      </c>
+      <c r="D58" s="35" t="n">
+        <v>106.6501</v>
+      </c>
+      <c r="E58" s="35" t="inlineStr">
+        <is>
+          <t>3.2-5.0 ty</t>
+        </is>
+      </c>
+      <c r="F58" s="35" t="inlineStr">
+        <is>
+          <t>Ta Quang Buu, P.6, Q.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="35" t="inlineStr">
+        <is>
+          <t>D-Aqua</t>
+        </is>
+      </c>
+      <c r="B59" s="35" t="inlineStr">
+        <is>
+          <t>Q.8</t>
+        </is>
+      </c>
+      <c r="C59" s="35" t="n">
+        <v>10.7402309</v>
+      </c>
+      <c r="D59" s="35" t="n">
+        <v>106.645793</v>
+      </c>
+      <c r="E59" s="35" t="inlineStr">
+        <is>
+          <t>3.5-5.0 ty</t>
+        </is>
+      </c>
+      <c r="F59" s="35" t="inlineStr">
+        <is>
+          <t>Ben Binh Dong, P.14, Q.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="35" t="inlineStr">
+        <is>
+          <t>Aurora Residences</t>
+        </is>
+      </c>
+      <c r="B60" s="35" t="inlineStr">
+        <is>
+          <t>Q.8</t>
+        </is>
+      </c>
+      <c r="C60" s="35" t="n">
+        <v>10.7429092</v>
+      </c>
+      <c r="D60" s="35" t="n">
+        <v>106.6508679</v>
+      </c>
+      <c r="E60" s="35" t="inlineStr">
+        <is>
+          <t>3.0-4.5 ty</t>
+        </is>
+      </c>
+      <c r="F60" s="35" t="inlineStr">
+        <is>
+          <t>Ben Binh Dong, P.13, Q.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="35" t="inlineStr">
+        <is>
+          <t>Green River</t>
+        </is>
+      </c>
+      <c r="B61" s="35" t="inlineStr">
+        <is>
+          <t>Q.8</t>
+        </is>
+      </c>
+      <c r="C61" s="35" t="n">
+        <v>10.7335</v>
+      </c>
+      <c r="D61" s="35" t="n">
+        <v>106.6442</v>
+      </c>
+      <c r="E61" s="35" t="inlineStr">
+        <is>
+          <t>3.0-3.8 ty</t>
+        </is>
+      </c>
+      <c r="F61" s="35" t="inlineStr">
+        <is>
+          <t>Pham The Hien, P.7, Q.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="35" t="inlineStr">
+        <is>
+          <t>Tara Residence</t>
+        </is>
+      </c>
+      <c r="B62" s="35" t="inlineStr">
+        <is>
+          <t>Q.8</t>
+        </is>
+      </c>
+      <c r="C62" s="35" t="n">
+        <v>10.7325</v>
+      </c>
+      <c r="D62" s="35" t="n">
+        <v>106.6531</v>
+      </c>
+      <c r="E62" s="35" t="inlineStr">
+        <is>
+          <t>3.0-4.2 ty</t>
+        </is>
+      </c>
+      <c r="F62" s="35" t="inlineStr">
+        <is>
+          <t>Ta Quang Buu, P.6, Q.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="35" t="inlineStr">
+        <is>
+          <t>Saigon Skyview</t>
+        </is>
+      </c>
+      <c r="B63" s="35" t="inlineStr">
+        <is>
+          <t>Q.8</t>
+        </is>
+      </c>
+      <c r="C63" s="35" t="n">
+        <v>10.7328855</v>
+      </c>
+      <c r="D63" s="35" t="n">
+        <v>106.6557022</v>
+      </c>
+      <c r="E63" s="35" t="inlineStr">
+        <is>
+          <t>3.0-4.5 ty</t>
+        </is>
+      </c>
+      <c r="F63" s="35" t="inlineStr">
+        <is>
+          <t>Ta Quang Buu, P.6, Q.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="35" t="inlineStr">
+        <is>
+          <t>Central Premium</t>
+        </is>
+      </c>
+      <c r="B64" s="35" t="inlineStr">
+        <is>
+          <t>Q.8</t>
+        </is>
+      </c>
+      <c r="C64" s="35" t="n">
+        <v>10.7369</v>
+      </c>
+      <c r="D64" s="35" t="n">
+        <v>106.6691</v>
+      </c>
+      <c r="E64" s="35" t="inlineStr">
+        <is>
+          <t>3.5-5.0 ty</t>
+        </is>
+      </c>
+      <c r="F64" s="35" t="inlineStr">
+        <is>
+          <t>Ta Quang Buu, P.1, Q.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="35" t="inlineStr">
+        <is>
+          <t>CC Bong Sao</t>
+        </is>
+      </c>
+      <c r="B65" s="35" t="inlineStr">
+        <is>
+          <t>Q.8</t>
+        </is>
+      </c>
+      <c r="C65" s="35" t="n">
+        <v>10.7368621</v>
+      </c>
+      <c r="D65" s="35" t="n">
+        <v>106.6613181</v>
+      </c>
+      <c r="E65" s="35" t="inlineStr">
+        <is>
+          <t>3.0-3.5 ty</t>
+        </is>
+      </c>
+      <c r="F65" s="35" t="inlineStr">
+        <is>
+          <t>Ta Quang Buu, P.5, Q.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="35" t="inlineStr">
+        <is>
+          <t>Diamond Riverside</t>
+        </is>
+      </c>
+      <c r="B66" s="35" t="inlineStr">
+        <is>
+          <t>Q.8</t>
+        </is>
+      </c>
+      <c r="C66" s="35" t="n">
+        <v>10.7302</v>
+      </c>
+      <c r="D66" s="35" t="n">
+        <v>106.6248</v>
+      </c>
+      <c r="E66" s="35" t="inlineStr">
+        <is>
+          <t>3.0-4.0 ty</t>
+        </is>
+      </c>
+      <c r="F66" s="35" t="inlineStr">
+        <is>
+          <t>Vo Van Kiet, P.16, Q.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="35" t="inlineStr">
+        <is>
+          <t>Conic Riverside</t>
+        </is>
+      </c>
+      <c r="B67" s="35" t="inlineStr">
+        <is>
+          <t>Q.8</t>
+        </is>
+      </c>
+      <c r="C67" s="35" t="n">
+        <v>10.7184884</v>
+      </c>
+      <c r="D67" s="35" t="n">
+        <v>106.6371053</v>
+      </c>
+      <c r="E67" s="35" t="inlineStr">
+        <is>
+          <t>3.0-4.2 ty</t>
+        </is>
+      </c>
+      <c r="F67" s="35" t="inlineStr">
+        <is>
+          <t>Ta Quang Buu, P.7, Q.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="35" t="inlineStr">
+        <is>
+          <t>Asiana Capella</t>
+        </is>
+      </c>
+      <c r="B68" s="35" t="inlineStr">
+        <is>
+          <t>Q.6</t>
+        </is>
+      </c>
+      <c r="C68" s="35" t="n">
+        <v>10.7398895</v>
+      </c>
+      <c r="D68" s="35" t="n">
+        <v>106.6280712</v>
+      </c>
+      <c r="E68" s="35" t="inlineStr">
+        <is>
+          <t>3.5-5.0 ty</t>
+        </is>
+      </c>
+      <c r="F68" s="35" t="inlineStr">
+        <is>
+          <t>Tran Van Kieu, P.10, Q.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="35" t="inlineStr">
+        <is>
+          <t>Him Lam Cho Lon</t>
+        </is>
+      </c>
+      <c r="B69" s="35" t="inlineStr">
+        <is>
+          <t>Q.6</t>
+        </is>
+      </c>
+      <c r="C69" s="35" t="n">
+        <v>10.7466</v>
+      </c>
+      <c r="D69" s="35" t="n">
+        <v>106.6379</v>
+      </c>
+      <c r="E69" s="35" t="inlineStr">
+        <is>
+          <t>3.0-4.5 ty</t>
+        </is>
+      </c>
+      <c r="F69" s="35" t="inlineStr">
+        <is>
+          <t>Dai lo Dong Tay, P.11, Q.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="35" t="inlineStr">
+        <is>
+          <t>Viva Riverside</t>
+        </is>
+      </c>
+      <c r="B70" s="35" t="inlineStr">
+        <is>
+          <t>Q.6</t>
+        </is>
+      </c>
+      <c r="C70" s="35" t="n">
+        <v>10.7427112</v>
+      </c>
+      <c r="D70" s="35" t="n">
+        <v>106.6474475</v>
+      </c>
+      <c r="E70" s="35" t="inlineStr">
+        <is>
+          <t>3.0-4.5 ty</t>
+        </is>
+      </c>
+      <c r="F70" s="35" t="inlineStr">
+        <is>
+          <t>Vo Van Kiet, P.1, Q.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="35" t="inlineStr">
+        <is>
+          <t>Saigon Asiana</t>
+        </is>
+      </c>
+      <c r="B71" s="35" t="inlineStr">
+        <is>
+          <t>Q.6</t>
+        </is>
+      </c>
+      <c r="C71" s="35" t="n">
+        <v>10.7501021</v>
+      </c>
+      <c r="D71" s="35" t="n">
+        <v>106.6367849</v>
+      </c>
+      <c r="E71" s="35" t="inlineStr">
+        <is>
+          <t>3.0-4.2 ty</t>
+        </is>
+      </c>
+      <c r="F71" s="35" t="inlineStr">
+        <is>
+          <t>NV Luong, P.12, Q.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="35" t="inlineStr">
+        <is>
+          <t>D-Homme</t>
+        </is>
+      </c>
+      <c r="B72" s="35" t="inlineStr">
+        <is>
+          <t>Q.6</t>
+        </is>
+      </c>
+      <c r="C72" s="35" t="n">
+        <v>10.7537</v>
+      </c>
+      <c r="D72" s="35" t="n">
+        <v>106.6446</v>
+      </c>
+      <c r="E72" s="35" t="inlineStr">
+        <is>
+          <t>3.8-5.0 ty</t>
+        </is>
+      </c>
+      <c r="F72" s="35" t="inlineStr">
+        <is>
+          <t>Hong Bang, P.12, Q.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="35" t="inlineStr">
+        <is>
+          <t>Summer Square</t>
+        </is>
+      </c>
+      <c r="B73" s="35" t="inlineStr">
+        <is>
+          <t>Q.6</t>
+        </is>
+      </c>
+      <c r="C73" s="35" t="n">
+        <v>10.7593879</v>
+      </c>
+      <c r="D73" s="35" t="n">
+        <v>106.6259582</v>
+      </c>
+      <c r="E73" s="35" t="inlineStr">
+        <is>
+          <t>3.0-3.8 ty</t>
+        </is>
+      </c>
+      <c r="F73" s="35" t="inlineStr">
+        <is>
+          <t>Tan Hoa Dong, P.14, Q.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="35" t="inlineStr">
+        <is>
+          <t>Saigon Royal Residence</t>
+        </is>
+      </c>
+      <c r="B74" s="35" t="inlineStr">
+        <is>
+          <t>Q.4</t>
+        </is>
+      </c>
+      <c r="C74" s="35" t="n">
+        <v>10.7670153</v>
+      </c>
+      <c r="D74" s="35" t="n">
+        <v>106.7038674</v>
+      </c>
+      <c r="E74" s="35" t="inlineStr">
+        <is>
+          <t>4.3 ty</t>
+        </is>
+      </c>
+      <c r="F74" s="35" t="inlineStr">
+        <is>
+          <t>Ben Van Don, P. Xom Chieu, Q.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="35" t="inlineStr">
+        <is>
+          <t>River Gate</t>
+        </is>
+      </c>
+      <c r="B75" s="35" t="inlineStr">
+        <is>
+          <t>Q.4</t>
+        </is>
+      </c>
+      <c r="C75" s="35" t="n">
+        <v>10.7626586</v>
+      </c>
+      <c r="D75" s="35" t="n">
+        <v>106.6991882</v>
+      </c>
+      <c r="E75" s="35" t="inlineStr">
+        <is>
+          <t>3-4 ty</t>
+        </is>
+      </c>
+      <c r="F75" s="35" t="inlineStr">
+        <is>
+          <t>Ben Van Don, P. Khanh Hoi, Q.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="35" t="inlineStr">
+        <is>
+          <t>The Tresor</t>
+        </is>
+      </c>
+      <c r="B76" s="35" t="inlineStr">
+        <is>
+          <t>Q.4</t>
+        </is>
+      </c>
+      <c r="C76" s="35" t="n">
+        <v>10.766733</v>
+      </c>
+      <c r="D76" s="35" t="n">
+        <v>106.7032221</v>
+      </c>
+      <c r="E76" s="35" t="inlineStr">
+        <is>
+          <t>3.4 ty</t>
+        </is>
+      </c>
+      <c r="F76" s="35" t="inlineStr">
+        <is>
+          <t>Ben Van Don, P. Xom Chieu, Q.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="35" t="inlineStr">
+        <is>
+          <t>Q7 Saigon Riverside</t>
+        </is>
+      </c>
+      <c r="B77" s="35" t="inlineStr">
+        <is>
+          <t>Q.7</t>
+        </is>
+      </c>
+      <c r="C77" s="35" t="n">
+        <v>10.7229238</v>
+      </c>
+      <c r="D77" s="35" t="n">
+        <v>106.7415437</v>
+      </c>
+      <c r="E77" s="35" t="inlineStr">
+        <is>
+          <t>3.1-3.6 ty</t>
+        </is>
+      </c>
+      <c r="F77" s="35" t="inlineStr">
+        <is>
+          <t>Dao Tri, P. Phu Thuan, Q.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="35" t="inlineStr">
+        <is>
+          <t>Luxcity</t>
+        </is>
+      </c>
+      <c r="B78" s="35" t="inlineStr">
+        <is>
+          <t>Q.7</t>
+        </is>
+      </c>
+      <c r="C78" s="35" t="n">
+        <v>10.7387122</v>
+      </c>
+      <c r="D78" s="35" t="n">
+        <v>106.7299709</v>
+      </c>
+      <c r="E78" s="35" t="inlineStr">
+        <is>
+          <t>4.3-5 ty</t>
+        </is>
+      </c>
+      <c r="F78" s="35" t="inlineStr">
+        <is>
+          <t>Huynh Tan Phat, P. Binh Thuan, Q.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="35" t="inlineStr">
+        <is>
+          <t>River Panorama</t>
+        </is>
+      </c>
+      <c r="B79" s="35" t="inlineStr">
+        <is>
+          <t>Q.7</t>
+        </is>
+      </c>
+      <c r="C79" s="35" t="n">
+        <v>10.7145604</v>
+      </c>
+      <c r="D79" s="35" t="n">
+        <v>106.7415783</v>
+      </c>
+      <c r="E79" s="35" t="inlineStr">
+        <is>
+          <t>3.9-4.7 ty</t>
+        </is>
+      </c>
+      <c r="F79" s="35" t="inlineStr">
+        <is>
+          <t>Hoang Quoc Viet, P. Phu Thuan, Q.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="35" t="inlineStr">
+        <is>
+          <t>Q7 Boulevard</t>
+        </is>
+      </c>
+      <c r="B80" s="35" t="inlineStr">
+        <is>
+          <t>Q.7</t>
+        </is>
+      </c>
+      <c r="C80" s="35" t="n">
+        <v>10.7078219</v>
+      </c>
+      <c r="D80" s="35" t="n">
+        <v>106.7329454</v>
+      </c>
+      <c r="E80" s="35" t="inlineStr">
+        <is>
+          <t>3.3-3.9 ty</t>
+        </is>
+      </c>
+      <c r="F80" s="35" t="inlineStr">
+        <is>
+          <t>Nguyen Luong Bang, P. Phu My, Q.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="35" t="inlineStr">
+        <is>
+          <t>Sunshine Sky City</t>
+        </is>
+      </c>
+      <c r="B81" s="35" t="inlineStr">
+        <is>
+          <t>Q.7</t>
+        </is>
+      </c>
+      <c r="C81" s="35" t="n">
+        <v>10.7295023</v>
+      </c>
+      <c r="D81" s="35" t="n">
+        <v>106.7304584</v>
+      </c>
+      <c r="E81" s="35" t="inlineStr">
+        <is>
+          <t>4.2 ty</t>
+        </is>
+      </c>
+      <c r="F81" s="35" t="inlineStr">
+        <is>
+          <t>Phu Thuan, P. Tan Phu, Q.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="35" t="inlineStr">
+        <is>
+          <t>Jamona City</t>
+        </is>
+      </c>
+      <c r="B82" s="35" t="inlineStr">
+        <is>
+          <t>Q.7</t>
+        </is>
+      </c>
+      <c r="C82" s="35" t="n">
+        <v>10.737552</v>
+      </c>
+      <c r="D82" s="35" t="n">
+        <v>106.7374244</v>
+      </c>
+      <c r="E82" s="35" t="inlineStr">
+        <is>
+          <t>3-3.4 ty</t>
+        </is>
+      </c>
+      <c r="F82" s="35" t="inlineStr">
+        <is>
+          <t>Dao Tri, P. Phu Thuan, Q.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="35" t="inlineStr">
+        <is>
+          <t>The Era Town</t>
+        </is>
+      </c>
+      <c r="B83" s="35" t="inlineStr">
+        <is>
+          <t>Q.7</t>
+        </is>
+      </c>
+      <c r="C83" s="35" t="n">
+        <v>10.7000497</v>
+      </c>
+      <c r="D83" s="35" t="n">
+        <v>106.7330581</v>
+      </c>
+      <c r="E83" s="35" t="inlineStr">
+        <is>
+          <t>3.3 ty</t>
+        </is>
+      </c>
+      <c r="F83" s="35" t="inlineStr">
+        <is>
+          <t>P. Phu My, Q.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="35" t="inlineStr">
+        <is>
+          <t>Westgate An Gia</t>
+        </is>
+      </c>
+      <c r="B84" s="35" t="inlineStr">
+        <is>
+          <t>Binh Chanh</t>
+        </is>
+      </c>
+      <c r="C84" s="35" t="n">
+        <v>10.6892919</v>
+      </c>
+      <c r="D84" s="35" t="n">
+        <v>106.5857392</v>
+      </c>
+      <c r="E84" s="35" t="inlineStr">
+        <is>
+          <t>3.2-4.5 ty</t>
+        </is>
+      </c>
+      <c r="F84" s="35" t="inlineStr">
+        <is>
+          <t>Nguyen Van Linh, TT.Tan Tuc, Binh Chanh</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="35" t="inlineStr">
         <is>
           <t>The Privia</t>
         </is>
       </c>
-      <c r="B55" s="20" t="inlineStr">
+      <c r="B85" s="35" t="inlineStr">
         <is>
           <t>Binh Tan</t>
         </is>
       </c>
-      <c r="C55" s="20" t="n">
+      <c r="C85" s="35" t="n">
         <v>10.7365049</v>
       </c>
-      <c r="D55" s="20" t="n">
+      <c r="D85" s="35" t="n">
         <v>106.6198532</v>
       </c>
-      <c r="E55" s="20" t="inlineStr">
+      <c r="E85" s="35" t="inlineStr">
         <is>
           <t>3.35-5.13 ty</t>
         </is>
       </c>
-      <c r="F55" s="20" t="inlineStr">
+      <c r="F85" s="35" t="inlineStr">
         <is>
           <t>P. An Lac, Q. Binh Tan</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="20" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="35" t="inlineStr">
         <is>
           <t>Akari City</t>
         </is>
       </c>
-      <c r="B56" s="20" t="inlineStr">
+      <c r="B86" s="35" t="inlineStr">
         <is>
           <t>Binh Tan</t>
         </is>
       </c>
-      <c r="C56" s="20" t="n">
+      <c r="C86" s="35" t="n">
         <v>10.7180526</v>
       </c>
-      <c r="D56" s="20" t="n">
+      <c r="D86" s="35" t="n">
         <v>106.6073672</v>
       </c>
-      <c r="E56" s="20" t="inlineStr">
+      <c r="E86" s="35" t="inlineStr">
         <is>
           <t>3.5-5.2 ty</t>
         </is>
       </c>
-      <c r="F56" s="20" t="inlineStr">
+      <c r="F86" s="35" t="inlineStr">
         <is>
           <t>P. An Lac, Q. Binh Tan</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="20" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="35" t="inlineStr">
         <is>
           <t>Mizuki Park</t>
         </is>
       </c>
-      <c r="B57" s="20" t="inlineStr">
+      <c r="B87" s="35" t="inlineStr">
         <is>
           <t>Binh Chanh</t>
         </is>
       </c>
-      <c r="C57" s="20" t="n">
+      <c r="C87" s="35" t="n">
         <v>10.7143025</v>
       </c>
-      <c r="D57" s="20" t="n">
+      <c r="D87" s="35" t="n">
         <v>106.6624699</v>
       </c>
-      <c r="E57" s="20" t="inlineStr">
+      <c r="E87" s="35" t="inlineStr">
         <is>
           <t>3.7-4.9 ty</t>
         </is>
       </c>
-      <c r="F57" s="20" t="inlineStr">
+      <c r="F87" s="35" t="inlineStr">
         <is>
           <t>X. Bình Hưng, Binh Chanh</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="20" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="35" t="inlineStr">
         <is>
           <t>Trellia Cove</t>
         </is>
       </c>
-      <c r="B58" s="20" t="inlineStr">
+      <c r="B88" s="35" t="inlineStr">
         <is>
           <t>Binh Chanh</t>
         </is>
       </c>
-      <c r="C58" s="20" t="n">
+      <c r="C88" s="35" t="n">
         <v>10.7139913</v>
       </c>
-      <c r="D58" s="20" t="n">
+      <c r="D88" s="35" t="n">
         <v>106.6623822</v>
       </c>
-      <c r="E58" s="20" t="inlineStr">
+      <c r="E88" s="35" t="inlineStr">
         <is>
           <t>4-5 ty</t>
         </is>
       </c>
-      <c r="F58" s="20" t="inlineStr">
+      <c r="F88" s="35" t="inlineStr">
         <is>
           <t>X. Bình Hưng, Binh Chanh</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="20" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="35" t="inlineStr">
         <is>
           <t>Diamond Brilliant</t>
         </is>
       </c>
-      <c r="B59" s="20" t="inlineStr">
+      <c r="B89" s="35" t="inlineStr">
         <is>
           <t>Tan Phu</t>
         </is>
       </c>
-      <c r="C59" s="20" t="n">
+      <c r="C89" s="35" t="n">
         <v>10.8021735</v>
       </c>
-      <c r="D59" s="20" t="n">
+      <c r="D89" s="35" t="n">
         <v>106.615341</v>
       </c>
-      <c r="E59" s="20" t="inlineStr">
+      <c r="E89" s="35" t="inlineStr">
         <is>
           <t>7.8-8.9 ty</t>
         </is>
       </c>
-      <c r="F59" s="20" t="inlineStr">
+      <c r="F89" s="35" t="inlineStr">
         <is>
           <t>P. Sơn Kỳ, Tan Phu</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="20" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="35" t="inlineStr">
         <is>
           <t>Diamond Centery</t>
         </is>
       </c>
-      <c r="B60" s="20" t="inlineStr">
+      <c r="B90" s="35" t="inlineStr">
         <is>
           <t>Tan Phu</t>
         </is>
       </c>
-      <c r="C60" s="20" t="n">
+      <c r="C90" s="35" t="n">
         <v>10.8019565</v>
       </c>
-      <c r="D60" s="20" t="n">
+      <c r="D90" s="35" t="n">
         <v>106.6146748</v>
       </c>
-      <c r="E60" s="20" t="inlineStr">
+      <c r="E90" s="35" t="inlineStr">
         <is>
           <t>6.8-14.88 ty</t>
         </is>
       </c>
-      <c r="F60" s="20" t="inlineStr">
+      <c r="F90" s="35" t="inlineStr">
         <is>
           <t>P. Sơn Kỳ, Tan Phu</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="20" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="35" t="inlineStr">
         <is>
           <t>Emerald Celadon City</t>
         </is>
       </c>
-      <c r="B61" s="20" t="inlineStr">
+      <c r="B91" s="35" t="inlineStr">
         <is>
           <t>Tan Phu</t>
         </is>
       </c>
-      <c r="C61" s="20" t="n">
+      <c r="C91" s="35" t="n">
         <v>10.8026957</v>
       </c>
-      <c r="D61" s="20" t="n">
+      <c r="D91" s="35" t="n">
         <v>106.6147149</v>
       </c>
-      <c r="E61" s="20" t="inlineStr">
+      <c r="E91" s="35" t="inlineStr">
         <is>
           <t>4-13.9 ty</t>
         </is>
       </c>
-      <c r="F61" s="20" t="inlineStr">
+      <c r="F91" s="35" t="inlineStr">
         <is>
           <t>P. Sơn Kỳ, Tan Phu</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="20" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="35" t="inlineStr">
         <is>
           <t>Oriental Plaza</t>
         </is>
       </c>
-      <c r="B62" s="20" t="inlineStr">
+      <c r="B92" s="35" t="inlineStr">
         <is>
           <t>Tan Phu</t>
         </is>
       </c>
-      <c r="C62" s="20" t="n">
+      <c r="C92" s="35" t="n">
         <v>10.7895653</v>
       </c>
-      <c r="D62" s="20" t="n">
+      <c r="D92" s="35" t="n">
         <v>106.6393649</v>
       </c>
-      <c r="E62" s="20" t="inlineStr">
+      <c r="E92" s="35" t="inlineStr">
         <is>
           <t>4-5 ty</t>
         </is>
       </c>
-      <c r="F62" s="20" t="inlineStr">
+      <c r="F92" s="35" t="inlineStr">
         <is>
           <t>P. Tân Thành, Tan Phu</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="20" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="35" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="B63" s="20" t="inlineStr">
+      <c r="B93" s="35" t="inlineStr">
         <is>
           <t>Tan Phu</t>
         </is>
       </c>
-      <c r="C63" s="20" t="n">
+      <c r="C93" s="35" t="n">
         <v>10.7838094</v>
       </c>
-      <c r="D63" s="20" t="n">
+      <c r="D93" s="35" t="n">
         <v>106.6369877</v>
       </c>
-      <c r="E63" s="20" t="inlineStr">
+      <c r="E93" s="35" t="inlineStr">
         <is>
           <t>9,65 tỷ</t>
         </is>
       </c>
-      <c r="F63" s="20" t="inlineStr">
+      <c r="F93" s="35" t="inlineStr">
         <is>
           <t>P. Sơn Kỳ, Tan Phu</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="20" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="35" t="inlineStr">
         <is>
           <t>Sky Center</t>
         </is>
       </c>
-      <c r="B64" s="20" t="inlineStr">
+      <c r="B94" s="35" t="inlineStr">
         <is>
           <t>Tan Binh</t>
         </is>
       </c>
-      <c r="C64" s="20" t="n">
+      <c r="C94" s="35" t="n">
         <v>10.8062382</v>
       </c>
-      <c r="D64" s="20" t="n">
+      <c r="D94" s="35" t="n">
         <v>106.6662711</v>
       </c>
-      <c r="E64" s="20" t="inlineStr">
+      <c r="E94" s="35" t="inlineStr">
         <is>
           <t>3.65-10.9 ty</t>
         </is>
       </c>
-      <c r="F64" s="20" t="inlineStr">
+      <c r="F94" s="35" t="inlineStr">
         <is>
           <t>Phường 2, Tan Binh</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="20" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="35" t="inlineStr">
         <is>
           <t>Park Legend</t>
         </is>
       </c>
-      <c r="B65" s="20" t="inlineStr">
+      <c r="B95" s="35" t="inlineStr">
         <is>
           <t>Tan Binh</t>
         </is>
       </c>
-      <c r="C65" s="20" t="n">
+      <c r="C95" s="35" t="n">
         <v>10.8000536</v>
       </c>
-      <c r="D65" s="20" t="n">
+      <c r="D95" s="35" t="n">
         <v>106.6651001</v>
       </c>
-      <c r="E65" s="20" t="inlineStr">
+      <c r="E95" s="35" t="inlineStr">
         <is>
           <t>6.5 ty</t>
         </is>
       </c>
-      <c r="F65" s="20" t="inlineStr">
+      <c r="F95" s="35" t="inlineStr">
         <is>
           <t>Phường 2, Tan Binh</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="20" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="35" t="inlineStr">
         <is>
           <t>Sai Gon Mia</t>
         </is>
       </c>
-      <c r="B66" s="20" t="inlineStr">
+      <c r="B96" s="35" t="inlineStr">
         <is>
           <t>Binh Chanh</t>
         </is>
       </c>
-      <c r="C66" s="20" t="n">
+      <c r="C96" s="35" t="n">
         <v>10.7231867</v>
       </c>
-      <c r="D66" s="20" t="n">
+      <c r="D96" s="35" t="n">
         <v>106.5933435</v>
       </c>
-      <c r="E66" s="20" t="inlineStr">
+      <c r="E96" s="35" t="inlineStr">
         <is>
           <t>5,3 tỷ</t>
         </is>
       </c>
-      <c r="F66" s="20" t="inlineStr">
+      <c r="F96" s="35" t="inlineStr">
         <is>
           <t>X. Bình Hưng, Binh Chanh</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="20" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="35" t="inlineStr">
         <is>
           <t>The Everrich Infinity</t>
         </is>
       </c>
-      <c r="B67" s="20" t="inlineStr">
+      <c r="B97" s="35" t="inlineStr">
         <is>
           <t>Q.5</t>
         </is>
       </c>
-      <c r="C67" s="20" t="n">
+      <c r="C97" s="35" t="n">
         <v>10.760861</v>
       </c>
-      <c r="D67" s="20" t="n">
+      <c r="D97" s="35" t="n">
         <v>106.6806479</v>
       </c>
-      <c r="E67" s="20" t="inlineStr">
+      <c r="E97" s="35" t="inlineStr">
         <is>
           <t>3.3-4.5 ty</t>
         </is>
       </c>
-      <c r="F67" s="20" t="inlineStr">
+      <c r="F97" s="35" t="inlineStr">
         <is>
           <t>An Duong Vuong, P.4, Q.5</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="20" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="35" t="inlineStr">
         <is>
           <t>Legacy 66 Tan Thanh</t>
         </is>
       </c>
-      <c r="B68" s="20" t="inlineStr">
+      <c r="B98" s="35" t="inlineStr">
         <is>
           <t>Q.5</t>
         </is>
       </c>
-      <c r="C68" s="20" t="n">
+      <c r="C98" s="35" t="n">
         <v>10.7564974</v>
       </c>
-      <c r="D68" s="20" t="n">
+      <c r="D98" s="35" t="n">
         <v>106.6565336</v>
       </c>
-      <c r="E68" s="20" t="inlineStr">
+      <c r="E98" s="35" t="inlineStr">
         <is>
           <t>4.5 ty</t>
         </is>
       </c>
-      <c r="F68" s="20" t="inlineStr">
+      <c r="F98" s="35" t="inlineStr">
         <is>
           <t>Tan Thanh, P.12, Q.5</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="20" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="35" t="inlineStr">
         <is>
           <t>Chung cu Le Thi Rieng</t>
         </is>
       </c>
-      <c r="B69" s="20" t="inlineStr">
+      <c r="B99" s="35" t="inlineStr">
         <is>
           <t>Q.10</t>
         </is>
       </c>
-      <c r="C69" s="20" t="n">
+      <c r="C99" s="35" t="n">
         <v>10.7811901</v>
       </c>
-      <c r="D69" s="20" t="n">
+      <c r="D99" s="35" t="n">
         <v>106.6630125</v>
       </c>
-      <c r="E69" s="20" t="inlineStr">
+      <c r="E99" s="35" t="inlineStr">
         <is>
           <t>3.8 ty</t>
         </is>
       </c>
-      <c r="F69" s="20" t="inlineStr">
+      <c r="F99" s="35" t="inlineStr">
         <is>
           <t>Le Thi Rieng, P.15, Q.10</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="20" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="35" t="inlineStr">
         <is>
           <t>CC Ly Thuong Kiet Q10</t>
         </is>
       </c>
-      <c r="B70" s="20" t="inlineStr">
+      <c r="B100" s="35" t="inlineStr">
         <is>
           <t>Q.10</t>
         </is>
       </c>
-      <c r="C70" s="20" t="n">
+      <c r="C100" s="35" t="n">
         <v>10.768769</v>
       </c>
-      <c r="D70" s="20" t="n">
+      <c r="D100" s="35" t="n">
         <v>106.6617061</v>
       </c>
-      <c r="E70" s="20" t="inlineStr">
+      <c r="E100" s="35" t="inlineStr">
         <is>
           <t>3 ty</t>
         </is>
       </c>
-      <c r="F70" s="20" t="inlineStr">
+      <c r="F100" s="35" t="inlineStr">
         <is>
           <t>Ly Thuong Kiet, P.7, Q.10</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="20" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="35" t="inlineStr">
         <is>
           <t>Cao oc Ngo Gia Tu</t>
         </is>
       </c>
-      <c r="B71" s="20" t="inlineStr">
+      <c r="B101" s="35" t="inlineStr">
         <is>
           <t>Q.10</t>
         </is>
       </c>
-      <c r="C71" s="20" t="n">
+      <c r="C101" s="35" t="n">
         <v>10.7638244</v>
       </c>
-      <c r="D71" s="20" t="n">
+      <c r="D101" s="35" t="n">
         <v>106.6716585</v>
       </c>
-      <c r="E71" s="20" t="inlineStr">
+      <c r="E101" s="35" t="inlineStr">
         <is>
           <t>3.9 ty</t>
         </is>
       </c>
-      <c r="F71" s="20" t="inlineStr">
+      <c r="F101" s="35" t="inlineStr">
         <is>
           <t>Ngo Gia Tu, P.3, Q.10</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="20" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="35" t="inlineStr">
         <is>
           <t>Chung cu Nguyen Kim</t>
         </is>
       </c>
-      <c r="B72" s="20" t="inlineStr">
+      <c r="B102" s="35" t="inlineStr">
         <is>
           <t>Q.10</t>
         </is>
       </c>
-      <c r="C72" s="20" t="n">
+      <c r="C102" s="35" t="n">
         <v>10.7613175</v>
       </c>
-      <c r="D72" s="20" t="n">
+      <c r="D102" s="35" t="n">
         <v>106.6618954</v>
       </c>
-      <c r="E72" s="20" t="inlineStr">
+      <c r="E102" s="35" t="inlineStr">
         <is>
           <t>3.45 ty</t>
         </is>
       </c>
-      <c r="F72" s="20" t="inlineStr">
+      <c r="F102" s="35" t="inlineStr">
         <is>
           <t>Nguyen Kim, P.7, Q.10</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="20" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="35" t="inlineStr">
         <is>
           <t>Celadon City</t>
         </is>
       </c>
-      <c r="B73" s="20" t="inlineStr">
+      <c r="B103" s="35" t="inlineStr">
         <is>
           <t>Tan Phu</t>
         </is>
       </c>
-      <c r="C73" s="20" t="n">
+      <c r="C103" s="35" t="n">
         <v>10.8025777</v>
       </c>
-      <c r="D73" s="20" t="n">
+      <c r="D103" s="35" t="n">
         <v>106.614893</v>
       </c>
-      <c r="E73" s="20" t="inlineStr">
+      <c r="E103" s="35" t="inlineStr">
         <is>
           <t>6.85-13.1 ty</t>
         </is>
       </c>
-      <c r="F73" s="20" t="inlineStr">
+      <c r="F103" s="35" t="inlineStr">
         <is>
           <t>P. Sơn Kỳ, Tan Phu</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="20" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="35" t="inlineStr">
         <is>
           <t>Diamond Alnata Plus</t>
         </is>
       </c>
-      <c r="B74" s="20" t="inlineStr">
+      <c r="B104" s="35" t="inlineStr">
         <is>
           <t>Tan Phu</t>
         </is>
       </c>
-      <c r="C74" s="20" t="n">
+      <c r="C104" s="35" t="n">
         <v>10.8020962</v>
       </c>
-      <c r="D74" s="20" t="n">
+      <c r="D104" s="35" t="n">
         <v>106.614808</v>
       </c>
-      <c r="E74" s="20" t="inlineStr">
+      <c r="E104" s="35" t="inlineStr">
         <is>
           <t>7.4-7.6 ty</t>
         </is>
       </c>
-      <c r="F74" s="20" t="inlineStr">
+      <c r="F104" s="35" t="inlineStr">
         <is>
           <t>P. Son Ky, Tan Phu</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="20" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="35" t="inlineStr">
         <is>
           <t>The Glen Celadon City</t>
         </is>
       </c>
-      <c r="B75" s="20" t="inlineStr">
+      <c r="B105" s="35" t="inlineStr">
         <is>
           <t>Tan Phu</t>
         </is>
       </c>
-      <c r="C75" s="20" t="n">
+      <c r="C105" s="35" t="n">
         <v>10.8023127</v>
       </c>
-      <c r="D75" s="20" t="n">
+      <c r="D105" s="35" t="n">
         <v>106.6142934</v>
       </c>
-      <c r="E75" s="20" t="inlineStr">
+      <c r="E105" s="35" t="inlineStr">
         <is>
           <t>23 ty</t>
         </is>
       </c>
-      <c r="F75" s="20" t="inlineStr">
+      <c r="F105" s="35" t="inlineStr">
         <is>
           <t>P. Son Ky, Tan Phu</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="20" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="35" t="inlineStr">
         <is>
           <t>Fortuna Vuon Lai</t>
         </is>
       </c>
-      <c r="B76" s="20" t="inlineStr">
+      <c r="B106" s="35" t="inlineStr">
         <is>
           <t>Tan Phu</t>
         </is>
       </c>
-      <c r="C76" s="20" t="n">
+      <c r="C106" s="35" t="n">
         <v>10.7883906</v>
       </c>
-      <c r="D76" s="20" t="n">
+      <c r="D106" s="35" t="n">
         <v>106.6244178</v>
       </c>
-      <c r="E76" s="20" t="inlineStr">
+      <c r="E106" s="35" t="inlineStr">
         <is>
           <t>3.35 ty</t>
         </is>
       </c>
-      <c r="F76" s="20" t="inlineStr">
+      <c r="F106" s="35" t="inlineStr">
         <is>
           <t>P. Phú Thọ Hòa, Tan Phu</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="20" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="35" t="inlineStr">
         <is>
           <t>Khu đô thị TOD đầu tiên tại Hồ Chí Minh chuẩn Nhật Bản. LH 0</t>
         </is>
       </c>
-      <c r="B77" s="20" t="inlineStr">
+      <c r="B107" s="35" t="inlineStr">
         <is>
           <t>Tan Phu</t>
         </is>
       </c>
-      <c r="C77" s="20" t="n">
+      <c r="C107" s="35" t="n">
         <v>10.7900957</v>
       </c>
-      <c r="D77" s="20" t="n">
+      <c r="D107" s="35" t="n">
         <v>106.6243718</v>
       </c>
-      <c r="E77" s="20" t="inlineStr">
+      <c r="E107" s="35" t="inlineStr">
         <is>
           <t>Đô thị TOD One Era</t>
         </is>
       </c>
-      <c r="F77" s="20" t="inlineStr">
+      <c r="F107" s="35" t="inlineStr">
         <is>
           <t>Tan Phu</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="20" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="35" t="inlineStr">
         <is>
           <t>Botanica Premier</t>
         </is>
       </c>
-      <c r="B78" s="20" t="inlineStr">
+      <c r="B108" s="35" t="inlineStr">
         <is>
           <t>Tan Binh</t>
         </is>
       </c>
-      <c r="C78" s="20" t="n">
+      <c r="C108" s="35" t="n">
         <v>10.8115758</v>
       </c>
-      <c r="D78" s="20" t="n">
+      <c r="D108" s="35" t="n">
         <v>106.669586</v>
       </c>
-      <c r="E78" s="20" t="inlineStr">
+      <c r="E108" s="35" t="inlineStr">
         <is>
           <t>4.5-7.8 ty</t>
         </is>
       </c>
-      <c r="F78" s="20" t="inlineStr">
+      <c r="F108" s="35" t="inlineStr">
         <is>
           <t>Phường 2, Tan Binh</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="20" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="35" t="inlineStr">
         <is>
           <t>Bau Cat Ii</t>
         </is>
       </c>
-      <c r="B79" s="20" t="inlineStr">
+      <c r="B109" s="35" t="inlineStr">
         <is>
           <t>Tan Binh</t>
         </is>
       </c>
-      <c r="C79" s="20" t="n">
+      <c r="C109" s="35" t="n">
         <v>10.7909</v>
       </c>
-      <c r="D79" s="20" t="n">
+      <c r="D109" s="35" t="n">
         <v>106.6457395</v>
       </c>
-      <c r="E79" s="20" t="inlineStr">
+      <c r="E109" s="35" t="inlineStr">
         <is>
           <t>2.6 ty</t>
         </is>
       </c>
-      <c r="F79" s="20" t="inlineStr">
+      <c r="F109" s="35" t="inlineStr">
         <is>
           <t>Phường 10, Tan Binh</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="20" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="35" t="inlineStr">
         <is>
           <t>Khu đô thị TOD đầu tiên tại Hồ Chí Minh chuẩn Nhật Bản. LH 0</t>
         </is>
       </c>
-      <c r="B80" s="20" t="inlineStr">
+      <c r="B110" s="35" t="inlineStr">
         <is>
           <t>Tan Binh</t>
         </is>
       </c>
-      <c r="C80" s="20" t="n">
+      <c r="C110" s="35" t="n">
         <v>10.812611</v>
       </c>
-      <c r="D80" s="20" t="n">
+      <c r="D110" s="35" t="n">
         <v>106.6570097</v>
       </c>
-      <c r="E80" s="20" t="inlineStr">
+      <c r="E110" s="35" t="inlineStr">
         <is>
           <t>Đô thị TOD One Era</t>
         </is>
       </c>
-      <c r="F80" s="20" t="inlineStr">
+      <c r="F110" s="35" t="inlineStr">
         <is>
           <t>Tan Binh</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="20" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="35" t="inlineStr">
         <is>
           <t>HQC Plaza</t>
         </is>
       </c>
-      <c r="B81" s="20" t="inlineStr">
+      <c r="B111" s="35" t="inlineStr">
         <is>
           <t>Binh Chanh</t>
         </is>
       </c>
-      <c r="C81" s="20" t="n">
+      <c r="C111" s="35" t="n">
         <v>10.6945666</v>
       </c>
-      <c r="D81" s="20" t="n">
+      <c r="D111" s="35" t="n">
         <v>106.6063942</v>
       </c>
-      <c r="E81" s="20" t="inlineStr">
+      <c r="E111" s="35" t="inlineStr">
         <is>
           <t>1,15 tỷ</t>
         </is>
       </c>
-      <c r="F81" s="20" t="inlineStr">
+      <c r="F111" s="35" t="inlineStr">
         <is>
           <t>X. An Phú Tây, Binh Chanh</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="20" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="35" t="inlineStr">
         <is>
           <t>Chung cư NOXH LA Home, tổng giá trị từ 385 triệu/căn, vốn ch</t>
         </is>
       </c>
-      <c r="B82" s="20" t="inlineStr">
+      <c r="B112" s="35" t="inlineStr">
         <is>
           <t>Binh Chanh</t>
         </is>
       </c>
-      <c r="C82" s="20" t="n">
+      <c r="C112" s="35" t="n">
         <v>10.725491</v>
       </c>
-      <c r="D82" s="20" t="n">
+      <c r="D112" s="35" t="n">
         <v>106.5935197</v>
       </c>
-      <c r="E82" s="20" t="inlineStr">
+      <c r="E112" s="35" t="inlineStr">
         <is>
           <t>Chủ Đầu Tư Prodezi Long An</t>
         </is>
       </c>
-      <c r="F82" s="20" t="inlineStr">
+      <c r="F112" s="35" t="inlineStr">
         <is>
           <t>Binh Chanh</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="35" t="inlineStr">
+        <is>
+          <t>H3 Hoang Dieu</t>
+        </is>
+      </c>
+      <c r="B113" s="35" t="inlineStr">
+        <is>
+          <t>Q.4</t>
+        </is>
+      </c>
+      <c r="C113" s="35" t="n">
+        <v>10.7603234</v>
+      </c>
+      <c r="D113" s="35" t="n">
+        <v>106.6990936</v>
+      </c>
+      <c r="E113" s="35" t="inlineStr">
+        <is>
+          <t>4.3 ty</t>
+        </is>
+      </c>
+      <c r="F113" s="35" t="inlineStr">
+        <is>
+          <t>Hoang Dieu, P. Khanh Hoi, Q.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="35" t="inlineStr">
+        <is>
+          <t>The Gold View</t>
+        </is>
+      </c>
+      <c r="B114" s="35" t="inlineStr">
+        <is>
+          <t>Q.4</t>
+        </is>
+      </c>
+      <c r="C114" s="35" t="n">
+        <v>10.756248</v>
+      </c>
+      <c r="D114" s="35" t="n">
+        <v>106.6918721</v>
+      </c>
+      <c r="E114" s="35" t="inlineStr">
+        <is>
+          <t>3.2 ty</t>
+        </is>
+      </c>
+      <c r="F114" s="35" t="inlineStr">
+        <is>
+          <t>Ben Van Don, P. Vinh Hoi, Q.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="35" t="inlineStr">
+        <is>
+          <t>Eco Green Sai Gon</t>
+        </is>
+      </c>
+      <c r="B115" s="35" t="inlineStr">
+        <is>
+          <t>Q.7</t>
+        </is>
+      </c>
+      <c r="C115" s="35" t="n">
+        <v>10.7487183</v>
+      </c>
+      <c r="D115" s="35" t="n">
+        <v>106.723741</v>
+      </c>
+      <c r="E115" s="35" t="inlineStr">
+        <is>
+          <t>4.8-5 ty</t>
+        </is>
+      </c>
+      <c r="F115" s="35" t="inlineStr">
+        <is>
+          <t>Nguyen Van Linh, P. Tan Thuan Tay, Q.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="35" t="inlineStr">
+        <is>
+          <t>Sunrise City</t>
+        </is>
+      </c>
+      <c r="B116" s="35" t="inlineStr">
+        <is>
+          <t>Q.7</t>
+        </is>
+      </c>
+      <c r="C116" s="35" t="n">
+        <v>10.7437289</v>
+      </c>
+      <c r="D116" s="35" t="n">
+        <v>106.7011024</v>
+      </c>
+      <c r="E116" s="35" t="inlineStr">
+        <is>
+          <t>3.3 ty</t>
+        </is>
+      </c>
+      <c r="F116" s="35" t="inlineStr">
+        <is>
+          <t>Nguyen Huu Tho, P. Tan Hung, Q.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="35" t="inlineStr">
+        <is>
+          <t>The Origami (Vinhomes Grand Park)</t>
+        </is>
+      </c>
+      <c r="B117" s="35" t="inlineStr">
+        <is>
+          <t>Q.9</t>
+        </is>
+      </c>
+      <c r="C117" s="35" t="n">
+        <v>10.8452092</v>
+      </c>
+      <c r="D117" s="35" t="n">
+        <v>106.8378812</v>
+      </c>
+      <c r="E117" s="35" t="inlineStr">
+        <is>
+          <t>3.3-4.9 ty</t>
+        </is>
+      </c>
+      <c r="F117" s="35" t="inlineStr">
+        <is>
+          <t>Long Binh, TP.Thu Duc (Q.9 cu)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="35" t="inlineStr">
+        <is>
+          <t>Lumiere Boulevard</t>
+        </is>
+      </c>
+      <c r="B118" s="35" t="inlineStr">
+        <is>
+          <t>Q.9</t>
+        </is>
+      </c>
+      <c r="C118" s="35" t="n">
+        <v>10.8394996</v>
+      </c>
+      <c r="D118" s="35" t="n">
+        <v>106.8392649</v>
+      </c>
+      <c r="E118" s="35" t="inlineStr">
+        <is>
+          <t>4.6-4.7 ty</t>
+        </is>
+      </c>
+      <c r="F118" s="35" t="inlineStr">
+        <is>
+          <t>Long Binh, TP.Thu Duc (Q.9 cu)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="35" t="inlineStr">
+        <is>
+          <t>Trellia Cove (Mizuki Park)</t>
+        </is>
+      </c>
+      <c r="B119" s="35" t="inlineStr">
+        <is>
+          <t>Binh Chanh</t>
+        </is>
+      </c>
+      <c r="C119" s="35" t="n">
+        <v>10.7128997</v>
+      </c>
+      <c r="D119" s="35" t="n">
+        <v>106.6607158</v>
+      </c>
+      <c r="E119" s="35" t="inlineStr">
+        <is>
+          <t>3.9-5 ty</t>
+        </is>
+      </c>
+      <c r="F119" s="35" t="inlineStr">
+        <is>
+          <t>Nguyen Van Linh, X.Binh Hung, Binh Chanh</t>
         </is>
       </c>
     </row>
